--- a/regulatory-compliance/cloud-foundation/9.1/dora/vcf-91-companion-dora.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/dora/vcf-91-companion-dora.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -3956,18 +3971,15 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to asset inventory processes by maintaining a detailed, real-time inventory of technology assets across compute, storage, and networking layers.
-VMware vCenter maintains the authoritative inventory of all managed objects in the environment. The vSphere inventory organizes objects in a hierarchical structure beginning at the root folder and extending through datacenters, clusters, hosts, virtual machines, networks, and datastores. Each object carries metadata including configuration details, resource allocations, and operational state. Administrators can extend this metadata by defining custom attributes, which store organization-specific fields against any inventory object in vCenter. Custom attribute values are held centrally by vCenter rather than within the individual objects, allowing teams to annotate VMs, hosts, datastores, and other inventory items with organization-defined information such as ownership, classification, or business justification details. This inventory reflects the live state of the environment as objects are created, modified, or removed. Multiple vCenter instances can be linked for centralized inventory management across workload domains.
-Programmatic access to the full inventory is available through the vSphere Web Services API. The Property Collector service uses Property Filter Specifications to identify inventory elements either directly or through object property traversal. The RetrievePropertiesEx method collects properties from inventory objects, allowing external systems and automation scripts to enumerate assets, gather configuration details, and build reports at whatever level of granularity is needed. The SimpleClient sample application demonstrates how to connect to a vCenter instance and obtain a listing of top-level inventory entities along with their properties and references.
-VCF Operations extends inventory visibility by retrieving inventory details from each vCenter, including associated clusters, VMware ESX hosts, datastores, and virtual machines. Discovered objects are grouped logically in detailed inventory lists, and the inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group. ResourceAttribute elements define the metrics that appear in the monitoring interface, each identified by a Metric Key, providing continuous visibility into asset utilization, capacity, and health. The vSphere Compute Inventory Dashboard provides interactive views of clusters, hosts, and virtual machines associated with any selected object.
-For application-level visibility, the VCF Operations Service Discovery adapter discovers running applications and services along with their CPU and memory metrics. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be grouped by object type and selected attributes through Application Definition criteria, and the results can be exported in CSV format for use in external asset tracking systems.
-VCF Automation adds a consumption-oriented layer to asset tracking. Projects link users, catalog items, and infrastructure resources where deployments are provisioned. The Overview tab displays infrastructure and consumption metrics across the organization. Resources visible in inventory views are scoped by the rights and project roles assigned to each user, providing role-appropriate visibility for audit and review. When catalog items are deployed, they are provisioned against the infrastructure available to the selected project, creating a traceable relationship between the request, the deployment, and the underlying resources. Provider accounts can create and track assets including virtual machines, catalogs, templates, and media. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources. Tags within VCF Automation express capabilities and constraints that define deployments, and cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-For integration with external asset registries, VCF provides multiple paths. The Management Pack for ServiceNow in VCF Operations discovers and synchronizes asset details including CPU count, CPU speed, CPU type, disk space, RAM, serial number, manufacturer, model ID, OS version, IP address, and vCenter reference through the ServiceNow Table API and CMDB Meta API. These properties are marked as required discovery fields, keeping the external CMDB aligned with the actual virtual infrastructure. VCF Operations for Networks supports adding ServiceNow as a CMDB data source to fetch configuration items and their relationships. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-Software asset tracking is supported through vSphere Lifecycle Manager, where software depots contain both the payloads and metadata for software updates. VCF Lifecycle Management tracks different versions of software components to help maintain compatibility across the infrastructure. The VCF Operations API includes methods to register associated products with their product name, version, and deployment details, contributing to a software-level view of the environment.
-The Consumption layer of VCF extends asset inventory to containerized workloads running on VMware Kubernetes Service (VKS) and vSphere Supervisor. The Kubernetes API server maintains a live registry of every object within a cluster or Supervisor namespace, covering pods, deployments, services, ConfigMaps, Secrets, PersistentVolumeClaims, CustomResourceDefinitions, and other resource types. Every resource carries standard metadata including name, namespace, labels, annotations, creation timestamp, and owning references that administrators can query or export at any level of granularity. Labels and annotations allow teams to attach arbitrary metadata to any Kubernetes resource, such as application name, business unit, or data classification, and these fields are queryable via label selectors, supporting filtered inventory exports by category. Supervisor namespaces map to vCenter namespaces, associating Kubernetes workloads with the organizational units defined during provisioning, and resource quotas and limit ranges attached to each namespace record the allocated capacity and support tracking of resource consumption by application or team.
-For workloads that consume specialized hardware such as accelerators or dedicated network devices, the Kubernetes Device Plugin framework provides hardware-level asset visibility within VKS clusters. Administrators or device owners use DeviceClasses to define sets of devices available in the cluster, and workloads claim specific hardware resources by creating ResourceClaims that filter for device parameters declared in a DeviceClass. Monitoring agents for device plugin resources discover which devices are in use on each node and collect metadata that associates each device allocation with the specific container consuming it, extending hardware asset tracking to the workload level.
-The Harbor Registry Supervisor Service provides an inventory mechanism for container images and artifacts. Harbor organizes images in a Projects structure by team or application and secures them with policies and role-based access control, allowing administrators to track which container images are authorized for use within the environment. Container images deployed through VCF consumption paths should be scanned, signed, and approved according to organizational software supply chain policies before use; digital certificates and validation mechanisms support supply chain assurance of images and artifacts. Where GitOps practices are in use, the Argo CD Supervisor Service extends this inventory capability by recording application synchronization events with timestamps, capturing the resource group, kind, namespace, name, sync status, and health status of each synchronized resource. Git repositories serve as the single source of truth for desired application and infrastructure state in a GitOps workflow, and infrastructure as code stored in version control creates a durable audit log of every authorized change to that state.
-These capabilities give VCF a strong technical foundation for tracking virtual infrastructure assets with accurate, real-time data at multiple levels of granularity. However, the broader requirements of this control, including business justification tracking, organization-defined accountability information, and formal review and audit processes for the full scope of technology assets, applications, services, and data, require organizational policies and processes that operate alongside the platform's inventory capabilities.</t>
+          <t>VCF provides several capabilities that support the identification and documentation of critical technology assets, applications, services, and data within a virtualized infrastructure.
+VMware vCenter maintains a real-time inventory of all managed objects, including hosts, VMs, clusters, datastores, and networks, and supports linking multiple vCenter instances for centralized inventory management. The vCenter inventory tracks multiple instances of ClusterComputeResource, ComputeResource, Datacenter, Datastore, DistributedVirtualSwitch, and Folder objects, providing a structured view of all infrastructure components. VCF Operations can export lists of resources, such as powered-off virtual machines, to CSV files for offline documentation and review.
+VCF Operations includes a Business Applications feature that allows administrators to group related infrastructure objects and assign business criticality classifications. Each Business Application can be tagged with a criticality level of Critical, Medium, or Low, with Medium as the default. The Object Summary card within VCF Operations displays details including the application's source, application tag, environment, and business criticality rating. This classification capability allows infrastructure teams to maintain a structured view of which applications and their underlying resources are most important to the organization.
+VCF Operations Service Discovery automatically detects running services across the environment. Service Discovery displays a list of all supported services that can be discovered and those currently discovered on VMs once configured. It also discovers performance metrics for individual service objects and service type objects, maintaining a catalog of known services and their relationships to underlying infrastructure. This automated discovery reduces manual effort in maintaining an accurate asset inventory.
+VCF Operations also provides alert definitions with configurable Impact and Criticality metadata. The Impact setting can be configured to values such as Risk to indicate potential problems, while the Criticality setting can be set to values like Immediate for proper alert prioritization. Alert notifications can be filtered by impact category and criticality level, helping teams classify infrastructure resources by their importance and focus attention on the most important infrastructure components. VCF Operations Insights data tracks resource capacity and can notify project owners of changes affecting their assets.
+VCF Automation provides complementary asset identification capabilities through its resource discovery and tagging system. The discovery process automatically identifies machines, storage volumes, networks, load balancers, and security groups for each cloud account region that has been added. Once discovered, these resources can be organized using tags that facilitate search and identification. Tags placed on cloud zones, network profiles, storage profiles, and individual infrastructure resources function as capability tags that define desired capabilities and support governance by expressing capabilities and constraints. Using logical, human-readable tags for storage, network, and infrastructure items is recommended to facilitate search and identification functions.
+VCF Automation organizes infrastructure through projects, which link users, catalog items, and IaaS resources to the locations where items are deployed. The Overview tab displays infrastructure and consumption metrics, providing a consolidated view of resource usage. Resource details views support filtering based on attributes such as project membership, enabling administrators to locate and review specific subsets of the infrastructure.
+Blueprints in VCF Automation allow users to model complex IT services by visually designing infrastructure components such as VMs, networks, storage, and software components. Resource objects in blueprints represent the infrastructure components and services that are provisioned and managed, providing an architectural record of how assets support business functions.
+Together, these inventory, discovery, classification, tagging, and visualization capabilities give operations teams the tools to identify, classify, and document the technology assets that support essential business functions. However, VCF provides the technical tooling for asset identification and classification rather than the organizational processes needed to define which assets are critical to the business mission. Establishing criticality criteria, maintaining asset documentation, and conducting periodic reviews of critical asset designations require organizational processes that operate alongside the platform's capabilities.</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -3977,11 +3989,13 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Services Platform (SSP) maintains an inventory of network-visible workloads organized into a hierarchical asset collection spanning regions, zones, environments, applications, and application tiers. The Publish Inventory Assets tab in SSP displays infrastructure asset details including asset names, asset types, IP addresses, and total VM counts for assets sourced from imported CSV files, discovered services, or published infrastructure assets, providing accurate, granular records of network-visible assets.
-Platform Inventory monitoring supports ongoing inventory accuracy through several mechanisms. Administrators can filter infrastructure assets by Name and Status, identifying assets that are timed out or out of sync. The inventory hierarchy view shows regions, zones, and VMs so administrators can verify correct definition. SSP Inventory displays assigned tags for each infrastructure asset, and environment rows can be expanded to view tag assignments and confirm hierarchy accuracy. The platform also collects and displays VM tags with their respective scopes, supporting classification and tracking. Published applications and their application types are verifiable in the Inventory &gt; Applications interface.
-SSP identifies and publishes application assets, classifying them as either critical or regular applications. Application Asset Collections represent groups of workloads delivering enterprise software functions. Security Intelligence within SSP displays application associations for compute entities, indicating the tiers within each application to which a given compute entity belongs. Administering compute entity classifications in Security Intelligence requires appropriate privileges, supporting access control over classification changes. Consistent naming conventions are recommended when preparing inventory data for import, and the Asset Prefix setting enables standardized naming during segmentation planning and monitoring.
-In disconnected mode, usage files include an asset_id field providing a unique asset identifier, supporting asset tracking in environments without continuous connectivity.
-vDefend's inventory scope is limited to network-visible workloads and does not replace enterprise-wide TAASD inventory tools, authorized software catalogs with business justification records, or data asset registries required for full AST-02 compliance.</t>
+          <t>VMware vDefend contributes to identifying and documenting critical technology assets through the Security Services Platform (SSP) and its Security Intelligence feature, which provide asset inventory, classification, and visualization capabilities oriented toward network security segmentation planning.
+Security Services Platform maintains a Platform Inventory of infrastructure assets, collecting status information for each asset including identification of assets that are timed out or out of sync. The inventory view provides filtering by Name and Status to locate specific infrastructure assets and identify their operational state. Tags assigned to each infrastructure asset are displayed for verification of tag assignments.
+Security Intelligence gathers infrastructure services and servers from CSV files and discovers additional services and servers based on traffic flows analyzed from ESX hosts. During CSV import, Security Intelligence parses and validates the content format and inventory asset data. Security Intelligence also maps discovered unique assets during segmentation analysis, including workloads, groups, IP addresses, distributed virtual port groups (DVPGs), segments, tiers, infrastructure services, and infrastructure servers.
+Security Services Platform identifies and publishes application assets, classifying them as either critical or regular applications. This criticality classification supports the identification of mission-critical technology assets within the environment. The inventory hierarchy spans regions, zones, environments, applications, and tiers, with each level displaying the total number of assets within its scope.
+Security Intelligence organizes discovered and imported assets into structured Asset Collections: groups, infrastructure assets, environments (such as Production, Non-Prod, DMZ, PCI, and Development), applications, and application tiers. The Environment Asset Collection maps security zones to the operational contexts that support business functions. Application Asset Collections group workloads that provide enterprise functionalities, linking infrastructure resources to the business services they support. The Infrastructure Asset Collection node covers core networking services that enterprise workloads depend on, including LDAP, DNS, NTP, and DHCP. An Unknown Asset Collection surfaces compute entities that are not in the NSX inventory but are present in the data center and communicating to NSX entities, supporting discovery of assets that should be formally inventoried.
+Security Intelligence Workload Classification can be set to "Infrastructure Service" to indicate that a compute entity provides infrastructure services such as DNS, DHCP, LDAP, and Syslog. Inferred infrastructure classifications for compute entities can be reviewed, accepted, or modified through the Monitor &amp; Plan &gt; Security Explorer interface.
+These capabilities contribute to the control but do not fully satisfy it. vDefend's asset identification is scoped to network security segmentation planning rather than the enterprise-wide technology asset catalog this control requires. Identifying all critical technology assets, applications, services, and data across an organization requires broader inventory and configuration management capabilities within VCF, such as VCF Operations business application views, VMware vCenter inventory exports, and VCF Automation project tagging, which provide the enterprise-wide asset catalog that vDefend's security-focused inventory complements.</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -3991,11 +4005,11 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) contributes to network architecture and data flow documentation through its network mapping capabilities, which record the topology between protected and recovery sites and provide programmatic access to that information for inclusion in formal diagrams.
-PNR supports site-wide network mappings that define how networks on the protected site correspond to networks on the recovery site. These mappings can specify a different network to use during recovery plan tests, capturing the separate set of data flows that apply during DR exercises. For stretched storage environments, network mappings can be configured manually to override automatic mapping behavior between sites.
-The Protection and Recovery Plug-In for the VCF Operations orchestrator provides API workflows that enumerate these mappings programmatically. The Get Network Mappings workflow lists all networks on a local site with existing mappings. The Get Network Mapping Pairs workflow retrieves the full set of mapping pairs for a specified site. The Get Test Network Mapping Pairs workflow lists test network mappings between corresponding objects across the remote site, and can query both protected and recovery sites when both are registered as local, providing a complete picture of the site-to-site network topology. An Add Test Network Mapping to Recovery Plan workflow maps a remote network to a test network within a specific recovery plan. IP customization workflows allow per-mapping customization of IP mapping rules and can remove customization rules from existing mappings.
-The Plug-In also supports inventory mapping workflows that span folder mappings, network mappings, resource pool mappings, and test network mappings, providing a unified interface for enumerating all inter-site relationships.
-Organizations should incorporate PNR's network mapping data and Plug-In workflow outputs into their formal network architecture diagrams to document DR topology, test network configurations, and the data flows that traverse the replication paths between sites.</t>
+          <t>VCF Protection and Recovery (PNR) organizes its protection model around identifying which assets are critical enough to warrant disaster recovery protection. Protection groups are an explicit declaration of critical assets, organizing virtual machines into logical units based on their replication and recovery requirements. Placing a workload in a protection group is a deliberate act of classifying it as essential to business operations.
+Inventory mappings document how each protected-site asset (resource pools, folders, networks, datastores) corresponds to recovery-site resources, creating a structured record of the infrastructure that supports critical workloads. Site-wide inventory mappings apply defaults across all protected VMs, while per-VM customizations document specific recovery configurations for workloads with unique requirements.
+The Protection and Recovery Configuration Import/Export Tool exports a complete record of the DR asset inventory, including site names, inventory mappings, placeholder datastores, advanced settings, array managers with SRA information, protection groups, and recovery plans. This export provides a structured, portable document of which assets are protected and how they are configured for recovery. The export is produced in XML format, enabling automated processing and retention as a configuration record.
+PNR generates and exports reports documenting each run of a recovery plan, each test of a recovery plan, and each test cleanup operation. These reports provide an auditable record of which recovery plans executed and which protected workloads were involved.
+PNR tracks site metrics including paired sites, pair names, vCenter addresses, site connectivity status, and counts of protection groups, recovery plans, protected virtual machines, and array managers. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, providing consolidated visibility into the DR infrastructure as a class of managed assets.</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
@@ -4042,7 +4056,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -4057,15 +4071,12 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Services Platform (SSP) organizes inventory assets into a defined hierarchy of region, zone, environment, application, and application tier, classifying them as either critical or regular applications. This hierarchy gives administrators a structured view of which assets support critical business functions and how they relate to each other within the environment.
-Security Explorer's Applications View designates critical applications as high-priority types that receive enhanced security attention and monitoring, providing a focused view of business-critical workloads and their network security posture. The SSP Inventory monitoring function allows administrators to view the infrastructure hierarchy, including regions, zones, and virtual machines, and verify tag assignments for each infrastructure asset.
-The SSP Segmentation Monitoring capability tracks application security posture over time and allows administrators to identify and address security risks surfaced through application monitoring. The SSP also identifies vulnerable workloads that could be exploited for lateral movement, supporting assessment of which assets pose elevated risk to critical business functions. Security Intelligence provides Infrastructure, Environment, and Application Monitoring capabilities that further aid in mapping asset relationships and security posture across the environment.
-The SSP is a centralized repository that maintains the most current organizational IT assets, including servers, software, and network devices along with their configurations. These capabilities contribute to network-layer asset inventory and dependency mapping but do not replace an enterprise asset management system or provide the full business impact analysis and organizational security assessment processes that a TAAS identification program requires.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -5091,15 +5102,14 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>VCF provides several mechanisms for automatically disabling technology assets, applications, and services upon detection of incidents, while preserving the ability to perform forensic analysis.
+VMware vCenter alarms can be configured to trigger automated actions when specific conditions are detected on infrastructure objects. When an alarm fires, it can execute scripts, send SNMP traps, or invoke API-driven workflows. The AlarmSpec data object lets administrators define trigger conditions and associate them with actions that run automatically when the alarm becomes active. This allows organizations to build automated responses that power off, suspend, or isolate VMs based on their own criteria.
+VCF Operations extends this with automated remediation tied to alert definitions. When an alert's first-priority recommendation is an action, VCF Operations can execute that action automatically. Automation Central provides built-in vCenter adapter actions including Power Off VM, Suspend VM, Power On VM, and Reboot Guest OS, which can be scheduled or triggered as part of automated jobs. The Management Pack for Automation Orchestrator allows custom workflows to be mapped to alert actions, so that when VCF Operations detects a condition, it can trigger an Orchestrator workflow that performs any sequence of operations on the affected assets. Orchestrator policies can also trigger predefined workflows or scripts in response to events, providing another path for automated incident response. Administrators can build workflows that suspend a VM, take a snapshot for forensic preservation, and then isolate the workload from the network, all without manual intervention. When an application service is identified as compromised or suspect, VCF Operations can deactivate the application service to stop monitoring data collection from that service, which can be part of an automated response to isolate affected components. Maintenance schedules can be configured to account for assets intentionally taken offline during incident response, preventing misleading monitoring data from generating false alerts during forensic analysis activities.
+VCF Automation includes a policy enforcement engine that allows organization administrators to configure and enforce IaaS resource policies across various namespaces. These policies can automatically disallow provisioning of VM resources using out-of-the-box policy templates such as the disallow-vm-resource template. When an incident is detected or a policy condition is triggered, these enforcement rules restrict further resource creation without manual intervention, containing the scope of a potential incident. Organization administrators can configure these policy rules across namespaces to control whether users can create resources for all services or limit them to specific service subsets such as VM Service or Kubernetes Service.
+VCF Automation blueprints support a metadata specification with deploymentSettings that can disable or hide day-2 operations for users on affected deployments. This allows administrators to lock down operational actions on compromised or suspect resources, preserving their state for forensic examination. Deployment-level actions can also be used to power off or delete affected deployments when an incident warrants taking resources offline. VCF Automation organizations can be disabled entirely when a broader containment response is needed, and organizations must be disabled before they can be deleted, providing a controlled decommissioning path. VCF Automation for VM Apps also supports day-2 resource actions including Power Off, Suspend, Delete, Create Snapshot, and Reboot, which can be invoked programmatically through the Automation API to disable or preserve assets as part of an automated incident response workflow.
+At the Kubernetes workload layer, VMware Kubernetes Service (VKS) and vSphere Supervisor provide API-accessible mechanisms for disabling workloads and services in response to detected incidents. Kubernetes Deployments can be scaled to zero replicas through the Kubernetes API, stopping all running pod instances while preserving the Deployment object and its configuration for forensic review and later restoration, which is preferable to outright deletion when evidence preservation is required before shutdown. NetworkPolicy and Antrea NetworkPolicy objects can be applied to restrict ingress and egress traffic to a specific namespace or set of pods, isolating a workload from the network without terminating it to support forensic capture of running process state. Supervisor administrators can deactivate Supervisor Services, which blocks DevOps teams from deploying or consuming specific service versions while leaving existing instances available for investigation. For cluster-level incidents, a TanzuKubernetesCluster can be retired by setting the annotation kubernetes.vmware.com/retire-tkc=force, bypassing pre-checks when immediate action is needed. ArgoCD, when deployed as a Supervisor Service, supports disabling an ApplicationSet by setting spec.applicationSet.enabled to false, halting GitOps-driven deployments into the affected environment. All of these operations are available through the Kubernetes API and can be invoked programmatically by an external security monitoring system, SIEM, or security orchestration platform that detects the triggering incident. Supervisor's Kubernetes RBAC model supports creating service accounts with narrowly scoped permissions for incident response automation, so the automated system performs only the operations needed for disabling affected assets without broader administrative access. The Kubernetes API server records all API calls, including caller identity, the resource acted upon, and the action taken, in its audit log, creating a durable forensic trail of all disabling operations.
+At the hypervisor layer, the VMware ESX Agent Manager provides programmatic methods for disabling ESX agencies. The Agency.disable() method disables the ESX agency and powers off the ESX agent virtual machines without undeploying them, preserving the agent VM state for forensic analysis while stopping the agency from executing. vSphere also provides the isolation.device.edit.disable setting, which restricts modification of devices on virtual machines, helping to preserve the state of potentially compromised workloads during an investigation.
+For forensic preservation, vCenter supports VM snapshots that capture memory, disk, and configuration state at a point in time. Reverting to a snapshot returns all memory, disk, and settings to the state they were in when the snapshot was taken. vSAN provides immutable snapshots, which are read-only copies of data that cannot be modified or deleted, even by an administrator with elevated privileges. These immutable snapshots help protect forensic evidence from tampering during investigation.</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -5109,12 +5119,13 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>VMware vDefend contributes to the automatic disabling and isolation of technology assets upon incident detection through automated response mechanisms that operate at the network layer. VM-level disabling actions such as power off, suspend, and snapshot are handled by VMware vCenter and VCF Operations rather than by vDefend directly.
+The vDefend Distributed IDS/IPS provides automated traffic blocking when configured in Detect and Prevent mode. When intrusions are detected against known signatures, the IDS/IPS engine automatically drops or rejects the offending packets depending on the signature configuration, stopping malicious traffic from reaching or leaving affected workloads without requiring manual intervention. Administrators can configure signature actions to Alert (detection only), Drop (silently discard packets), or Reject (discard packets and send TCP reset), allowing granular control over which detected threats trigger automatic blocking. IDS/IPS event monitoring records the Signature Type for each detected event, distinguishing between System and Custom signatures, which supports post-incident investigation of the detection chain. vDefend IDS/IPS can also store matched files to disk for forensic analysis, preserving evidence of the file transfers that triggered detection.
+IDS/IPS rate filters provide threshold-based automatic escalation. When a source IP address triggers a rule more than a configurable number of times within a defined time window (default: 10 matches within 60 seconds), the rate filter automatically switches the rule action to Drop for future matching traffic. The rate filter remains active for a configurable timeout period of up to 3600 seconds before reverting. This mechanism provides automatic escalation from alerting to blocking when repeated malicious activity is detected, effectively disabling network access for the offending source without manual intervention.
+The vDefend distributed firewall and Gateway Firewall both support an Emergency rule category designed for quarantine and incident response scenarios. Administrators pre-configure quarantine rules in the Emergency category that can isolate compromised workloads by restricting their network connectivity. The Emergency category takes the highest precedence in the DFW rule table, so quarantine rules in this category override all other firewall policies when triggered. These rules restrict a workload's ability to communicate on the network while preserving the workload for forensic analysis.
+Intelligent Assist automates the creation of remediation policies in response to detected security events. When IDS/IPS, malware, or network anomaly events are detected, Intelligent Assist can automatically generate vDefend policies. For non-IDS/IPS events such as malware detections, Intelligent Assist creates policies and rules in the Emergency section of the DFW rule table. The Comprehensive remediation strategy creates DFW policies that provide broader protection against similar attacks, reducing the time between detection and network-level isolation of affected workloads.
+The Malware Prevention Service inspects files and assigns verdicts with risk scores, blocking malicious files from being transferred across the network. When configured on the Distributed Firewall, the service intercepts file transfers and subjects them to static and dynamic analysis, blocking files determined to be malicious. The service logs the full file analysis lifecycle to syslog, recording file intercepted, verdict cache hit, file sent for local static analysis, file sent for cloud dynamic analysis, verdict obtained, and policy enforced events. This chain of logged events supports audit trails and forensic investigation following a malware detection. Analysis reports categorize suspicious behaviors detected during artifact inspection into structured behavioral classifications, including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced categories, providing structured evidence of how a detected artifact behaved.
+These capabilities provide the automated network-level isolation and traffic blocking components of an incident response workflow. The broader asset disabling actions described in this control, such as powering off VMs, suspending workloads, and creating forensic snapshots, are handled by vCenter alarms and VCF Operations automated remediation actions working with vDefend's detection and network isolation capabilities.</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -5148,13 +5159,11 @@
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
+          <t>VMware Avi Load Balancer (Avi) provides automated mechanisms at the application delivery layer that contribute to the incident handling process. The Avi Controller's Alert and ControlScript framework is the primary automation vehicle: when system events occur (pool health changes, Service Engine state transitions, WAF rule matches, or traffic anomalies), Avi processes those events and metrics against user-defined rules, generating alerts that initiate configured actions such as sending an email, a syslog message, or an SNMP trap. These events serve as the building blocks of configuration automation and can trigger ControlScripts without manual administrator intervention.
+ControlScripts are Python or shell scripts executed in response to alert conditions, configured through the Avi Controller's Alert Actions settings. They support several automated response patterns relevant to incident handling: modifying pool priority to initiate failover when a pool goes down, adding or removing routes based on VIP attachment and detachment events, and performing CRUD operations against Avi infrastructure through the Avi APIs and SDKs. The SE-Log-Agent within each Service Engine maintains a queue for logs, batches them from all Service Engine processes, and forwards them to the log manager in the Avi Controller, providing a continuous log stream that underpins these automated workflows.
+At the application security layer, the Avi Web Application Firewall (WAF) feeds the incident detection pipeline. The Avi Service Engine logs events when WAF matches a transaction, and WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, including an assisted workflow for reviewing and applying those exceptions. Bot Management adds a Consolidator agent that evaluates results across all detection components, inspecting data for contradictions and irregularities, and classifies client types to provide automated threat classification that can inform incident response workflows.
+For incident documentation and external integration, the Avi Controller provides Syslog-Audit-Persistence for streaming audit compliance events to external syslog servers, supporting integration with centralized logging and SIEM platforms. Python with the Avi SDK can be integrated into CI/CD pipelines and event-driven workflows to provision Avi infrastructure, monitor load balancer events, analyze logs, and trigger alerts based on specific Avi events. Ansible modules for Avi automatically handle error reporting and retries, logging failures for graceful management within automation workflows.
+Broader incident orchestration, case management, and cross-domain response coordination depend on integrations with external SIEM, ITSM, and security orchestration platforms, and on VCF platform-level automation capabilities. Organizations are responsible for defining the ControlScript workflows, alert thresholds, and external integration endpoints that activate these automated mechanisms.</t>
         </is>
       </c>
     </row>
@@ -5482,40 +5491,27 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>VCF provides centralized software and firmware patching across the entire infrastructure stack through VCF Operations and vSphere Lifecycle Manager, which together form a unified lifecycle management plane. VCF Operations is the central orchestration point for patching and update operations, coordinating patch releases (such as 9.0.1.0100) that deliver time-sensitive fixes to security and operational issues between major, minor, and maintenance releases.
-VCF uses a desired-state model for host remediation through vSphere Lifecycle Manager (vLCM). Administrators define a software specification for each cluster, and vLCM brings all hosts into compliance with that specification during remediation. This approach applies uniformly to VMware-supplied components and third-party solutions alike. To make a third-party solution available on a cluster, administrators create a software specification containing the solution and remediate all hosts with that image. vLCM manages software updates for VMware ESX hosts, including patches of the ESX base image, OEM add-ons, components from different software vendors, and VMware Tools updates. Dynamic patch baselines automatically adjust their contents based on specified criteria each time Update Manager downloads new patches, keeping remediation current without manual baseline maintenance. Fixed baselines are also available for environments that require explicit control over which patches are applied. Hardware Support Manager (HSM) plugins extend vLCM to manage vendor-specific firmware and driver updates alongside software patches, providing unified lifecycle management for both software and firmware from within the same interface. Firmware updates through Hardware Support Manager are only available for clusters and hosts managed with vSphere Lifecycle Manager images; hosts managed with baselines do not support firmware updates through this mechanism.
-The remediation workflow is coordinated through multiple layers. Coordinator Manager runs pre-checks before remediation begins to evaluate how each host in the cluster is affected and whether additional steps are needed. Pre-checks verify component connectivity, version compatibility, and component status. The ESX Updater Manager then handles the actual remediation on each host. Coordinator Manager also allows administrators to query the status of the remediation operation for the cluster and for each individual host, providing centralized visibility into remediation progress. The VCF Operations cluster transition specification includes a remediationOptionsSpec with a configurable remediationFailureAction that supports automatic retry with adjustable retryCount and retryDelay parameters, allowing administrators to define consistent remediation behavior.
-VCF Operations extends lifecycle management with patch planner functionality for VCF core components, including the ability to download and manage upgrade, patch, and install binaries. Pre-update validation performs health checks and compatibility verification before patches are applied, and component interdependency management helps maintain compatibility and stability across the infrastructure during updates. All dependent elements related to package objects are added to packages automatically to help maintain compatibility between versions. VCF Operations also provides compliance management capabilities that detect violations, highlight risk areas, and provide actionable remediation recommendations, with out-of-the-box workflows mapped to recommendations and associated with specific alerts for automated remediation.
-VCF supports programmatic management of the patching process through multiple interfaces. The VMware vCenter patching API supports discovery of all available and applicable updates for vCenter instances in the environment, including minor in-place updates and major migration-based updates. REST API endpoints provide operations for checking pending updates, requirements checking, staging, and installation. The life cycle management API provides operations for listing all available updates and upgrades and generating a pre-check compatibility report before applying updates. The vSphere Automation REST API allows administrators to query effective global and cluster-specific remediation policies before initiating remediation, and the Update-Entity operation remediates hosts by applying baselines with configurable failure handling and retry behavior. PowerCLI provides the Update Manager module with cmdlets for downloading software patches, creating and modifying baselines, and scanning and remediating hosts, including a Test-Compliance command to verify entities against downloaded patches. The vCenter Appliance itself can be patched via the vCenter Appliance Management Interface (VAMI) or the appliance shell; VMware distributes vCenter patches in two forms, ISO-based and URL-based, and the `software-packages` utility in the appliance shell supports both methods, including staging patches from a repository URL, installing directly from a URL without staging, or installing from an attached ISO image. These interfaces enable integration with external change management and orchestration systems for automated remediation workflows.
-VCF includes several capabilities to reduce patching risk and support continuity during updates. Live Patching updates and restarts discrete components without requiring host evacuation or reboot, as vSphere Lifecycle Manager does not place hosts into maintenance mode when a Live Patch is enforced. Snapshots should be created before patching VCF Operations fleet management to provide a rollback path. VCF supports Ensure Accessibility maintenance mode for vSAN storage clusters, which evacuates data to maintain object accessibility during updates through durability components. The VCF Download Tool supports a patches-only option and offline depot configuration for managing patch binaries in air-gapped environments.
-VCF Operations complements patch application with patch-gap detection for server firmware. It monitors hardware properties across the fleet, including BIOS version and BIOS release date, and provides dashboards that flag hosts running outdated server BIOS. This detection capability helps administrators identify hosts that require firmware patching before they become a compliance or security gap.
-The VCF Consumption layer, implemented through vSphere Supervisor and VMware Kubernetes Service (VKS), extends this patching coverage to Kubernetes control plane components and cluster add-ons. VKS clusters use a rolling update model where updates are initiated by changing the cluster specification; the Supervisor reconciler applies changes node by node to maintain cluster availability during the process. This model covers control plane components including kube-apiserver, kube-controller-manager, kube-scheduler, etcd, kubelet configuration, and CoreDNS, all updated through the kubeadm upgrade mechanism. Kubeadm supports targeted patching of individual components through a patches directory; files named with the pattern `target[suffix][+patchtype].extension` (for example, `kube-apiserver0+merge.yaml` or `etcd.json`) apply strategic merge patches, merge patches, or JSON patches to the specified component. The patches mechanism is available through the InitConfiguration, JoinConfiguration, and UpgradeConfiguration APIs, providing consistent patching behavior across cluster initialization, node join, and upgrade operations. Instance-specific patches can also be applied over the base KubeletConfiguration through kubeadm customization.
-VKS clusters support add-on management that enables installation and updates of standard packages through versioned add-on repositories. Administrators can track and update packages such as istio, harbor, sriov-network-device-plugin, windows-gmsa-webhook, and vsphere-pv-csi-webhook as new versions become available. For container image currency, Harbor is available as a Supervisor service and provides vulnerability scanning and content trust capabilities to help identify images that require patching. Admission controllers, including validating webhooks and image pull policies, can be configured to restrict deployment of images that have not passed vulnerability scanning or that contain known vulnerabilities, integrating image patch compliance into the workload deployment workflow. Content library VM images deployed in the vSphere Supervisor environment should be created with the latest patches and required security settings aligned with organizational security policies. Security Technical Implementation Guides (STIGs) are available for Supervisor and VKS node releases (VKrs), providing prescriptive hardening guidance that defines what patches and configurations constitute a compliant deployment for the Kubernetes consumption layer.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to vulnerability management through network-layer detection, virtual patching, and security posture monitoring capabilities that complement traditional patch management workflows.
-vDefend Distributed IDS/IPS provides signature-based detection of vulnerability exploitation attempts across east-west traffic within the data center. When a new vulnerability is disclosed, administrators can deploy custom IDS/IPS signatures to detect and block exploitation attempts before official patches are available, a practice commonly referred to as virtual patching. In 9.1, IDS/IPS event monitoring displays Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by exploits, giving security teams direct visibility into which specific vulnerabilities are being actively targeted in their environment. The IDS/IPS dashboard provides monitoring and analysis of intrusion events, and Security Services Platform collects metrics to monitor IDS/IPS readiness and performance across the environment. Malicious IP reputation feeds, managed centrally through the Global Manager, automatically update threat intelligence so that known attacker infrastructure is blocked without manual intervention.
-The Threat Event Monitoring dashboard in Security Services Platform displays the top IPs on which an intrusion was attempted and the top VMs based on Vulnerability Severity criteria. The Threat Event Monitoring tab on the Security Overview dashboard surfaces key insights about the current state of various security issues in the data center, helping security teams understand network activity and prioritize focus areas.
-Security Intelligence, a feature within Security Services Platform, provides posture assessment and segmentation monitoring capabilities. Administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment traffic. The Security Posture dashboard presents information that can be used to plan and implement additional security policies. The Security Explorer provides a visual representation of workloads, their traffic flows, and connection status, which helps identify workloads that may be exposed to unpatched vulnerabilities. Security Services Platform also generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and traffic flows, providing the visibility needed to plan subsequent protection stages. The Security Operator role in Security Services Platform is designated to monitor security systems and respond to security incidents, supporting the operational dimension of vulnerability management monitoring.
-vDefend Advanced Threat Prevention extends detection capabilities to include behavioral analysis and sandboxing, identifying malware and exploit attempts that signature-based detection might miss. The Security Overview dashboard in Security Services Platform displays file inspection statistics organized by different ranges of threat score, giving security teams a quantitative view of file-based threats detected in their environment. This provides an additional layer of protection for systems awaiting patches.
-These capabilities address the detection and monitoring dimensions of vulnerability management. Patch deployment and software lifecycle management are handled by other VCF components such as VCF Operations and vSphere Lifecycle Manager.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -5530,34 +5526,22 @@
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L64" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides a structured update management workflow for the DSM plug-in and the database services it manages. Software updates must be obtained from the Broadcom Support Portal and uploaded into the DSM environment before deployment, establishing a controlled software intake process. Plug-in and database template software updates can be initiated by a vSphere administrator or a DSM user in the DSM Admin role.
-The update process includes a staged review step before administrators initiate installation. Updates can be checked and initiated directly from the DSM UI or managed from the vSphere Client. The upgrade process is designed to attempt at least one complete chain of software updates regardless of the configured maintenance window duration, reducing the risk of a partially applied update chain. When automatic updates are enabled, DSM retries the update a maximum of three times, with a 10-minute interval between each attempt during the configured maintenance duration. If automatic plug-in updates fail, DSM supports manual updates as a fallback.
-For automated patching, DSM provides a configurable Maintenance Policy that allows administrators to schedule automatic software updates for DSM Provider Appliances. The policy specifies a start date, a start time, and a duration window, and is accessible from both the DSM UI and the vSphere Client. The maintenance policy can be edited during the 10-minute interval between automatic update attempts, which cancels the next scheduled attempt and applies the updated configuration.
-For database engine patching, DSM supports database version upgrades, including major version upgrades of PostgreSQL. Minor version database upgrades can be configured to run automatically during maintenance windows and may include CVE fixes, bug fixes, and performance improvements. For SQL Server databases managed by DSM, administrators can define maintenance windows for operating system patching.
-When deploying DSM through the Consumption Operator, the deployment process includes Signature Verification to validate package integrity before installation.
-DSM provides the tooling to manage patching of the DSM platform and its managed database services. Patching of the underlying VCF infrastructure (VMware ESX hosts, VMware vCenter, NSX, storage systems, firmware) is handled through VCF's lifecycle management capabilities and falls outside DSM's scope. An organizational patch management program is needed to track patch applicability, establish patch windows across all technology assets, test patches before production deployment, and verify successful application across the full environment.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N64" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides dedicated patch management mechanisms for its two primary components: the Avi Controller (the management and control plane) and Service Engines (the data plane VMs that handle application traffic). The Controller is the central point through which patches are delivered and applied to both component types.
-Patch images are uploaded to the Controller via the REST API or through the CLI. Once a patch image is available, operators select from four patching modes: Controller Patch, SE Group Patch, System Patch, and Disruptive Patch. The patch segroup command accepts an se_group_refs parameter to target a specific Service Engine group for patching; when se_group_refs is not specified, all Service Engine groups are patched. If more than one Service Engine group requires patching, each group requires a separate patch command.
-A best practice in 9.1 is to apply patches only to the Service Engine groups that require them, using Service Engine group segmentation to scope patching operations rather than applying patches system-wide when not necessary. Patch packages are selected based on the current Controller and Service Engine versions.
-Before applying Controller patches, the system runs pre-checks that validate patch compatibility. These checks use the SYSERR_CHECK_CONTROLLER_PATCH_COMPATIBILITY mechanism to confirm the patch is appropriate for the installed version. Pre-check status and progress are accessible via Administration &gt; Update &gt; System, and a dry run option is available for upgrade operations to verify object operational state before the patch is applied.
-Patches within a given patch family are cumulative. Patch 1p2 contains all fixes from 1p1 plus its own new fixes, and 1p3 includes all fixes from both 1p1 and 1p2. This design means an operator applying the latest patch in a family receives all prior fixes without needing to apply them sequentially. Applying a patch from a different patch family once one family is already in place is not advisable, and once a patch from a specific series is applied, all entities in the system can only be upgraded to patches within that series or higher.
-For REST API-driven workflows, the Controller supports asynchronous patch operations that queue and consolidate patch requests at fixed intervals. This approach reduces latency during high-rate configuration updates and is recommended for large Avi deployments.
-Avi also supports virtual patching for application-layer vulnerabilities through its Web Application Firewall (WAF). Operators can import Dynamic Application Security Testing (DAST) scanner results into the WAF to identify and help block exploitation of known application vulnerabilities while formal software patches are being developed and tested.
-Patching of the underlying VCF platform infrastructure on which Avi's Controller and Service Engine VMs run, including compute hosts, storage, and networking components, is handled by VCF lifecycle management and is reflected in VCF Coverage.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -5923,15 +5907,87 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall implement the ICT business continuity policy through dedicated, appropriate and documented arrangements, plans, procedures and mechanisms aiming to:</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -5945,12 +6001,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -5959,12 +6015,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -5973,22 +6029,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K69" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L69" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M69" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N69" s="10" t="inlineStr">
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6001,33 +6057,33 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>11.2(a)</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>BCD-01</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall implement the ICT business continuity policy through dedicated, appropriate and documented arrangements, plans, procedures and mechanisms aiming to:</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Ensure the continuity of the financial entity's critical or important functions.</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -6041,12 +6097,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6055,12 +6111,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -6069,22 +6125,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N70" s="10" t="inlineStr">
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6097,33 +6153,33 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>11.2(a)</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>11.2(b)</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>BCD-01</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Ensure the continuity of the financial entity's critical or important functions.</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Quickly, appropriately and effectively respond to, and resolve, all ICT-related incidents in a way that limits damage and prioritises the resumption of activities and recovery actions.</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -6137,12 +6193,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6151,12 +6207,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J71" s="10" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -6165,22 +6221,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K71" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L71" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N71" s="10" t="inlineStr">
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M72" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6193,33 +6249,33 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>11.2(b)</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>11.2(c)</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>BCD-01</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>Quickly, appropriately and effectively respond to, and resolve, all ICT-related incidents in a way that limits damage and prioritises the resumption of activities and recovery actions.</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Activate, without delay, dedicated plans that enable containment measures, processes and technologies suited to each type of ICT-related incident and prevent further damage.</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -6233,12 +6289,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6247,12 +6303,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J72" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -6261,22 +6317,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K72" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L72" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M72" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N72" s="10" t="inlineStr">
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6289,33 +6345,177 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>11.2(c)</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>11.2(d)</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>BCD-01</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Activate, without delay, dedicated plans that enable containment measures, processes and technologies suited to each type of ICT-related incident and prevent further damage.</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Estimate preliminary impacts, damages and losses.</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M74" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>11.2(e)</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Set out communication and crisis management actions (in accordance with Article 14) and report to the competent authorities (in accordance with Article 19).</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall implement associated ICT response and recovery plans which, for entities other than microenterprises, shall be subject to independent internal audit reviews.</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -6329,12 +6529,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6343,12 +6543,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -6357,22 +6557,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K73" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L73" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M73" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6385,33 +6585,33 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>11.2(d)</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>Estimate preliminary impacts, damages and losses.</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01, BCD-04</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall put in place, maintain and periodically test appropriate ICT business continuity plans, notably with regard to critical or important functions outsourced or contracted through arrangements with ICT third-party service providers.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -6425,12 +6625,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6439,12 +6639,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -6453,22 +6653,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M74" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr">
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6481,33 +6681,33 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>11.2(e)</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>Set out communication and crisis management actions (in accordance with Article 14) and report to the competent authorities (in accordance with Article 19).</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01, RSK-08</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall conduct a business impact analysis (BIA) of their exposures to severe business disruptions, assessing the potential impact using quantitative and qualitative criteria. The BIA must consider the criticality of identified functions, processes, and dependencies, and ensure ICT assets and services are designed for redundancy.</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
 vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
@@ -6521,12 +6721,12 @@
 While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6535,12 +6735,12 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J75" s="10" t="inlineStr">
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
 Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
@@ -6549,22 +6749,22 @@
 Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
         </is>
       </c>
-      <c r="K75" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L75" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M75" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6577,52 +6777,122 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall implement associated ICT response and recovery plans which, for entities other than microenterprises, shall be subject to independent internal audit reviews.</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>RSK-01</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall, as part of their comprehensive ICT risk management:</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>11.6(a)</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01, BCD-04</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Test the ICT business continuity plans and the ICT response and recovery plans in relation to ICT systems supporting all functions at least yearly.</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides several infrastructure-level capabilities that support an organization's contingency plan testing and exercise program, though the planning, scheduling, execution, and evaluation of formal contingency tests remains an organizational responsibility.
+VCF includes built-in recovery and high-availability mechanisms that organizations can exercise during contingency tests. vSAN stretched clusters can be exercised by simulating site failures through host maintenance mode operations, validating that the surviving availability zone continues storage and compute operations. A vSAN stretched cluster continues to function if a failure or scheduled maintenance occurs at one zone, and with local fault protection enabled, the cluster can perform repairs on missing or broken components in the available site. vSphere HA can be tested by deliberately failing hosts to observe VM restart behavior and confirm that admission control policies reserve sufficient capacity. vSphere HA uses admission control so that a cluster has sufficient resources to support virtual machine recovery when a host fails.
+VCF Operations HCX supports workload migrations between sites through Mobility Groups, allowing organizations to exercise mobility procedures and validate that workloads can be moved to alternate processing locations. Migration activity, progress, and history are tracked through the Migration Planning interface, providing visibility into the results of migration exercises.
+Management component backup and restore procedures can be tested by performing restore operations for VCF Operations, VMware vCenter, and NSX components. VCF documents the prerequisites and sequencing for file-based restore of these components, allowing organizations to validate their recovery procedures against documented expectations. Changed Block Tracking (CBT) enables incremental backups through VADP-integrated solutions that can be tested independently, and VADP-based backup partner solutions can perform backup, full restore, and registration of VM Service VMs on a Supervisor.
+VCF Operations includes a What-If Analysis capability under its capacity planning module that allows administrators to model hypothetical scenarios against current infrastructure. Administrators can create, save, and run scenarios cumulatively to evaluate the demand and supply for capacity on resources and assess potential risk to current capacity. This supports both Traditional and Hyperconverged deployment models. Scenarios can be committed as planning tools for capacity analysis, helping organizations with separate capacity management and operations teams understand current capacity and upcoming capacity requirements. These what-if scenarios can be used as part of contingency testing to model failover capacity needs, validate that sufficient resources exist to absorb relocated workloads, and verify that planned recovery configurations are viable before an actual event occurs.
+To support the separation of test and production environments during contingency exercises, VCF Operations allows administrators to configure custom groups with differentiated alert thresholds and capacity calculations. This allows a test environment to operate under different operational policies than production, which is useful when conducting DR drills or failover exercises that temporarily shift workloads between sites or clusters.
+VCF also provides built-in pre-check and validation capabilities that verify component connectivity, version compatibility, and component status among other environment readiness checks. These pre-checks run automatically during lifecycle operations such as upgrades and remediation, and they help confirm that the environment is in a known-good state before changes are applied. While these are not contingency plan tests in themselves, they contribute to readiness assessment by confirming that infrastructure components are healthy and correctly configured before and after contingency exercises.
+Organizations deploying VCF should establish a formal contingency plan testing program that includes scheduled DR drills, failover exercises, backup restoration validation, and tabletop exercises. VCF's recovery mechanisms, what-if analysis, and pre-check capabilities can inform and support these activities, but the test plan itself, its schedule, success criteria, scenario design, evaluation criteria, and after-action review process must be defined and managed by the organization.</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
 The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
@@ -6631,36 +6901,36 @@
 The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
         </is>
       </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N76" s="10" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides non-disruptive testing of disaster recovery plans as a core operational capability. Recovery plans organize protected workloads into sequenced, dependency-aware execution groups, and these plans can be tested without affecting production operations on either the protected or recovery site.
+Testing a recovery plan in PNR validates that virtual machines recover correctly to the recovery site and exercises nearly every aspect of a recovery plan to validate disaster recovery readiness. Testing has no lasting effects on either the protected or recovery site, which means exercises can be repeated at any frequency without risk to production workloads. PNR requires that recovery plans be tested before use for planned migration or disaster recovery operations. Recovery plan tests can be canceled at any time; however, a successful cleanup operation must be completed before running a failover or initiating another test.
+Recovery plan test execution is tracked through the Test task in Recent Tasks, which monitors overall progress of the test operation. Recovery plans support two types of custom steps: Test Steps that run during recovery plan testing, and Recovery Steps that run during planned migration or disaster recovery operations. The Configure Test Networks step in the recovery plan workflow supports using a separate test network at the recovery site to keep test VMs isolated from production network segments during testing.
+Recovery plan testing can be automated through the VCF Operations orchestrator Plug-In for Protection and Recovery. The Initiate Test Recovery Plan workflow starts a test of a selected recovery plan and performs a state check to verify the recovery plan is in ready state before allowing test execution. The Initiate Cleanup Recovery Plan workflow cleans up a test when the recovery plan is in needsCleanup state.
+The organizational elements of contingency plan testing, including exercise scheduling, scenario design, evaluation criteria, and after-action reviews, are outside PNR's scope. Recovery plan testing supports two distinct pre-production rehearsal modes: test recovery, which validates failover into an isolated environment without disrupting production, and planned migration, which performs an orderly, validated move of workloads. Tests can be used to verify that recovery time and recovery point objectives are met, and can be run unattended through the VCF Operations Orchestrator plug-in and the REST API for scheduled or scripted execution.</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M80" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
 At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
@@ -6673,366 +6943,6 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01, BCD-04</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall put in place, maintain and periodically test appropriate ICT business continuity plans, notably with regard to critical or important functions outsourced or contracted through arrangements with ICT third-party service providers.</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L77" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N77" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01, RSK-08</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall conduct a business impact analysis (BIA) of their exposures to severe business disruptions, assessing the potential impact using quantitative and qualitative criteria. The BIA must consider the criticality of identified functions, processes, and dependencies, and ensure ICT assets and services are designed for redundancy.</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L78" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M78" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N78" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>RSK-01</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall, as part of their comprehensive ICT risk management:</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M79" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N79" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>11.6(a)</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01, BCD-04</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>Test the ICT business continuity plans and the ICT response and recovery plans in relation to ICT systems supporting all functions at least yearly.</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K80" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L80" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M80" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N80" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
@@ -7051,54 +6961,37 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
@@ -7113,19 +7006,12 @@
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N81" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -7230,54 +7116,37 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
@@ -7292,19 +7161,12 @@
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -7326,54 +7188,37 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K84" s="10" t="inlineStr">
@@ -7388,19 +7233,12 @@
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N84" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -7422,54 +7260,37 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
@@ -7484,19 +7305,12 @@
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N85" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -7518,54 +7332,37 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K86" s="10" t="inlineStr">
@@ -7580,19 +7377,12 @@
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N86" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -7614,54 +7404,37 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
@@ -7676,19 +7449,12 @@
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -7719,315 +7485,6 @@
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K88" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L88" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
-Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
-Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
-DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
-DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
-Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
-DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
-Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="M88" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N88" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>12.1(a)</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01, BCD-11</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>Backup policies and procedures specifying the scope of the data that is subject to the backup and the minimum frequency of the backup, based on the criticality of information or the confidentiality level of the data.</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K89" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L89" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
-Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
-Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
-DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
-DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
-Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
-DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
-Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="M89" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N89" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>12.1(b)</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>BCD-01, BCD-11</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>Restoration and recovery procedures and methods.</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F90" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J90" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
-        </is>
-      </c>
-      <c r="K90" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L90" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
-Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
-Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
-DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
-DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
-Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
-DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
-Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="M90" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N90" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>BCD-11, BCD-11.1, BCD-11.5</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall set up backup systems that can be activated in accordance with the backup policies and procedures, as well as restoration and recovery procedures and methods. The activation of backup systems shall not jeopardise the security of the network and information systems or the availability, authenticity, integrity or confidentiality of data. Testing of the backup procedures and restoration and recovery procedures and methods shall be undertaken periodically.</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>VCF provides built-in backup capabilities across its management components, workload layers, and storage subsystems, supporting organizations in meeting their Recovery Time Objectives (RTOs) and Recovery Point Objectives (RPOs).
 Management component backups
@@ -8050,7 +7507,352 @@
 Backup automation through APIs
 VCF exposes backup automation through its APIs, including the RecoveryBackupJobBackupRequest data structure for specifying backup location, protocol, authorization, and database scope, as well as the RecoveryBackupSchedulesUpdateSpec for programmatically managing backup schedules.
 Disaster recovery planning
-For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VMware Live Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
+For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VCF Protection and Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
+VCF directly provides the mechanisms for creating recurring backups, managing retention, and supporting RTO/RPO requirements through multiple backup and snapshot methods. However, organizations must establish backup policies, define RTO/RPO targets, schedule regular restore testing, and maintain backup infrastructure such as external storage and third-party backup solutions to fully satisfy this control.</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
+The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
+Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
+When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
+The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
+Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
+vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
+In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
+Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
+Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
+Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
+DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
+DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
+Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
+DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
+Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
+        </is>
+      </c>
+      <c r="M88" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
+At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
+Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
+At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
+For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
+Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
+In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
+Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>12.1(a)</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01, BCD-11</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Backup policies and procedures specifying the scope of the data that is subject to the backup and the minimum frequency of the backup, based on the criticality of information or the confidentiality level of the data.</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides built-in backup capabilities across its management components, workload layers, and storage subsystems, supporting organizations in meeting their Recovery Time Objectives (RTOs) and Recovery Point Objectives (RPOs).
+Management component backups
+VCF supports backup of all core management components. VMware vCenter supports both file-based and image-based backup methods, with file-based daily backups configured through the vCenter Management Interface of each vCenter instance. vCenter file-based backup and restore supports FTP, FTPS, HTTP, HTTPS, SFTP, NFS, or SMB as the backup server protocol. vCenter file-based backup optionally encrypts backup files using an encryption password that must be provided during restore; because vCenter backups contain the Key Derivation Key used for vSphere encryption, backup files should be stored on a secured backup server with appropriate access controls. VCF Operations similarly supports file-based and image-based backup methods. NSX Manager uses file-based backup, which VCF Operations configures automatically during the initial bring-up process. File-based backup jobs for VCF Operations and vCenter must be configured separately after deployment.
+Scheduled backups should be implemented to prepare for critical failure scenarios, upgrade events, or certificate updates of management components. To capture a consistent state across related components, VCF requires creating a series of coordinated backup jobs that run simultaneously across component nodes. Simultaneous backups of component nodes help ensure that the backed-up state is logically consistent, reducing the need for integrity remediation during a restore. On-demand manual backups can be taken after a successful recovery operation or after a scheduled backup failure. VCF Operations backup is also configured to take a backup on state change, providing an additional layer of protection when configuration changes occur.
+The backup file server stores backups from all NSX Manager or Global Manager nodes, and NSX includes a script to automatically delete old backups to manage storage consumption. NSX Global Manager backups should be periodically cleaned up to avoid excessive storage consumption on the backup file server. VCF Operations for Networks can store backups on local storage, retaining up to five backup files, or upload them to SSH or FTP servers. An initial on-demand backup should be performed after configuring VCF Operations to verify that backups complete successfully before relying on scheduled jobs. Sufficient storage capacity must be provisioned to accommodate backup data across all components.
+Backup integrity and restore procedures
+Backup integrity verification in VCF centers on version compatibility. When restoring a vCenter instance from a file-based backup, administrators must have a valid backup that matches the exact version of the vCenter appliance being restored to. VCF Operations must be available before restoring vCenter, and vCenter must be available before restoring VCF Operations, establishing a defined dependency order for restore operations. These dependencies require careful sequencing during recovery to restore the management plane to a consistent state.
+Workload-level data protection
+For workload-level data protection, VCF provides several mechanisms. Changed Block Tracking (CBT) tracks modified disk blocks on virtual machines, enabling incremental backups that reduce backup windows and storage requirements. VMware vSphere Storage APIs for Data Protection (VADP) provide a standardized interface for third-party backup solutions to integrate with VCF. vSphere Supervisor supports backup of VM Service VMs through backup partner solutions based on VADP, and if a VADP-based backup solution is deployed on the default management cluster, the solution must be properly started and operational before starting up or shutting down VCF. Quiesced snapshots are appropriate for automated or periodic backups of VM Service virtual machines, as they capture a consistent state before the backup operation proceeds. VCF Automation supports snapshotting a VM group to create an object that references distinct snapshots for each member VM; restoring a VM group snapshot restores each member of the group.
+vSphere Supervisor control plane backup and restore can be performed using vCenter file-based backup and restore from the Workload Management UI. For applications that provide their own backup capabilities, VCF documentation recommends using application-specific backup methods rather than relying on filesystem backup alone.
+vSAN data protection and snapshots
+vSAN Data Protection allows snapshots to be managed through protection groups with configurable snapshot retention policies and scheduling intervals. The native Snapshot Service is supported by vSAN Express Storage Architecture (ESA) but not by vSAN Original Storage Architecture (OSA). Native snapshots in vSAN ESA are much faster than traditional vSphere snapshots because a base VMDK and its snapshots are contained in one vSAN object rather than being separate objects, allowing more frequent backups and faster recovery. In vSAN OSA, snapshots are separate vSAN objects. The vSAN Distributed File System Snapshot can be used by third-party backup vendors to copy changed files incrementally to a different physical location. The vSAN Snapshot Service API provides programmatic access for operations including creating linked clones from snapshots and restoring deleted virtual machines.
+VMware Kubernetes Service backup
+VMware Kubernetes Service (VKS) and the Supervisor layer extend VCF's backup capabilities to containerized workloads, cluster state, and persistent volume data. VKS Supervisor backup and restore for cluster node VMs is activated through the vCenter backup feature available in the vCenter Management Interface, integrating Kubernetes cluster state backup with the same management-plane backup infrastructure used for other VCF components.
+For workload-level backup of VKS clusters, the platform supports three complementary methods: vSphere Plugin Snapshot (CSI Snapshot), File System Backup (FSB), and the Velero Plugin for vSphere. The vSphere Plugin Snapshot method produces crash-consistent, block-level backups of persistent volumes through the Container Storage Interface (CSI) layer and supports snapshot direct access and network traffic offload; it is faster and less resource-intensive than filesystem backup for complex filesystems with large numbers of small files, making it well-suited for production databases and high-IOPS applications. The File System Backup method operates at the filesystem level, supports NFS volumes and incremental backups where unchanged files are not re-transferred between runs, and offers backup repository features including deduplication, compression, and encryption; it is appropriate for legacy volumes with non-CSI storage. The Velero Plugin for vSphere can back up and restore both stateless and stateful applications running on vSphere Pods in the Supervisor. Platform teams can use both FSB and CSI Volume Snapshots within a single protection strategy to maximize data durability across workload types. VKS cluster backup supports opt-in and opt-out approaches for FSB volume backup, giving operators control over which volumes are included in filesystem-level operations. Third-party backup software can also integrate with VKS clusters using the standard Kubernetes CSI snapshot API: tools create a VolumeSnapshot object from the target PVC, materialize a temporary PVC from the snapshot, and use a Data Mover pod to transfer data to the backup destination. Kubernetes implements Persistent Volume Claim as Snapshot Source Protection, which blocks deletion of in-use API objects while a snapshot is in progress, reducing the risk of partial or inconsistent backup data. Kubernetes also supports provisioning a new PersistentVolumeClaim directly from a VolumeSnapshot by specifying the snapshot as the dataSource, enabling volume-level point-in-time recovery without requiring a full application restore workflow.
+VKS cluster management provides a Create backup wizard that allows users to create backups immediately or schedule backups of specified data resources in a cluster. Backup scheduling supports immediate execution, recurring schedule formats with targeted start times, or custom cron expressions; automated backup scheduling can also be configured using the Velero CLI with the velero schedule create command, specifying the interval or cron expression for recurring backup operations. For on-demand backups outside a scheduled window, the velero backup create command backs up Kubernetes resources and persistent volume data for stateful workloads, with support for per-namespace targeting and volume snapshot inclusion. VKS cluster backups can retain a maximum of 720 backups per backup schedule; when high-frequency schedules are required, the retention period should be reduced to remain within this limit. Backup schedules can be edited, paused, or deleted through the management interface. File system backups are included in the restore by default, and snapshot data can be moved to a separate backup storage location. Before defining a backup, a target location and credential must be created; if a data protection credential is deleted, scheduled backups relying on that credential will fail on their next execution, creating a detectable gap in backup execution history that administrators should monitor. Creating a backup schedule requires the Organization Administrator or Project Administrator role.
+VKS cluster backup and restore operations are managed through the VCF Automation Tenant Portal under Manage &amp; Govern &gt; VCF Services &gt; Kubernetes Management &gt; Clusters &gt; Data Protection. The portal provides restore operations on specific backups, and a dedicated cross-cluster restore capability in the Data Protection tab enables restoring backups from a source cluster to a different target cluster. VKS cluster management supports backup and restore of an entire cluster, selected namespaces from the backup, or specific resources identified by a label. The CloneFromSnapshot CRD includes a status.phase field that tracks restore progress through multiple phases, providing operational visibility during restore operations.
+For Kubernetes cluster state, etcd is the backing store for all Kubernetes objects, and clusters using etcd should have a backup plan. etcd backup can be performed using the built-in etcdctl snapshot save command by specifying the endpoint, CA certificate, and client credentials, or by taking a volume snapshot of the etcd storage volume when the underlying storage supports it. etcd snapshots can be restored from a previous snapshot file or from the remaining data directory, and cross-patch-version restores are supported. During kubeadm upgrades, automatic backup folders are written to /etc/kubernetes/tmp containing etcd data and manifests as a recovery point.
+Backup automation through APIs
+VCF exposes backup automation through its APIs, including the RecoveryBackupJobBackupRequest data structure for specifying backup location, protocol, authorization, and database scope, as well as the RecoveryBackupSchedulesUpdateSpec for programmatically managing backup schedules.
+Disaster recovery planning
+For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VCF Protection and Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
+VCF directly provides the mechanisms for creating recurring backups, managing retention, and supporting RTO/RPO requirements through multiple backup and snapshot methods. However, organizations must establish backup policies, define RTO/RPO targets, schedule regular restore testing, and maintain backup infrastructure such as external storage and third-party backup solutions to fully satisfy this control.</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend's Security Services Platform (SSP) provides backup and restore capabilities for the vDefend control plane, covering firewall rules, microsegmentation policies, IDS/IPS configurations, Bare Metal server information, tokens, and all associated security data managed by the platform. These backups protect against data loss from hardware or software malfunctions, data corruption, malware incidents, or unintentional deletion.
+SSP supports recurring backup schedules configurable through the Backup Schedule interface, with frequency options ranging from 6 hours to 720 hours (30 days), as well as weekly scheduling by selecting the day and time. Recurring backups can be activated or deactivated by toggling the Recurring setting. Best practice guidance recommends scheduling backups during periods of low platform usage to minimize operational impact. A backup should also be performed before executing scale-out operations on the SSP cluster, to preserve the current configuration state before significant topology changes. Backup data is encrypted with a passphrase and transmitted to an SFTP server. Adequate storage must be verified on the backup server before activating recurring backups, and the platform must be in a healthy state for backup operations to proceed. Backup is also blocked if NSX is not onboarded to SSP.
+SSP maintains a Backup History section that displays the status of each backup operation, showing "Completed" when the operation succeeds. When backup or restore operations enter a failed state, pod logs provide detailed error messages, including database query failures and volume attachment errors, to support troubleshooting. Restoration supports deploying the backed-up configuration onto the same SSP instance or a new instance, enabling recovery when the current instance is in a non-recoverable state. Restoration requires that the same NSX instance that was onboarded at the time of backup be used, and that the platform be deployed on the same vSAN datastore and build version as the initial installation. Certificate consistency between backup and restored environments must be maintained to avoid disruptions to NDR Sensor connectivity.
+These capabilities address the backup component of this control for vDefend's own configuration and policy data. vDefend does not back up general workload data or application-level information; those responsibilities fall to the broader VCF platform's replication, snapshot, and backup mechanisms, including vSAN Data Protection, Protection and Recovery (PNR), and integration with third-party backup providers. vDefend's contribution is limited to protecting the security policy and configuration data that defines the network security posture of the environment.</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides replication, snapshot, and recovery testing capabilities that support recovery point and recovery time objectives for protected workloads.
+vSphere Replication delivers host-based continuous replication with RPO configurable from 1 minute to 24 hours, set via a slider during replication configuration. PNR uses the configured RPO to determine the most recent available state to which virtual machines are recovered during disaster recovery. vSAN snapshots and replication is a native, integrated snapshot-based backup solution for VMs running on vSAN datastores, managed through the vSphere Client, and supports RPO as low as 1 minute. Snapshot retention schedules support hourly, daily, weekly, and monthly snapshots with a maximum retention duration of three years. Predefined retention templates are available for quick configuration of RPO and snapshot retention parameters. Array-based replication supports configuring replication schedule, frequency, and RPO through VM storage policies, depending on the storage array's implementation.
+PNR replication classes are preconfigured with an RPO that defines the acceptable amount of data loss after a disaster. In deployments using VCF Automation integration, replication classes can be assigned at the organization level.
+Cyber Recovery, the cloud-based recovery component within PNR, uses incremental snapshots that transfer only modified or new data to cloud backup. This design enables detection of ransomware encryption by comparing entropy rates between normal snapshots and snapshots containing suspect data. Ransomware recovery plans in Cyber Recovery support predefined retention templates for configuring snapshot RPO and retention parameters.
+PNR's own configuration is protected through backup settings that specify a datastore path, enable or disable the backup scheduler, set a retention period, and schedule backup frequency and time. PNR REST APIs can be configured to export and upload configuration data to a datastore on a daily basis. PNR also maintains internal database backups for audit and recovery purposes, covering the replication manager database (srmdb), recovery manager database (vrmsdb), and snapshot service database (snapservice).
+Recovery plan testing is the integrity verification mechanism for protected data. During disaster recovery execution, PNR first attempts storage synchronization; if that succeeds, it uses the synchronized storage state to recover virtual machines to their most recent available state per the configured RPO. RPO violation dashboards in VCF Operations report violation counts for incoming and outgoing replications, enabling monitoring of whether replication is meeting defined targets.</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
+Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
+Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
+DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
+DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
+Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
+DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
+Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
+        </is>
+      </c>
+      <c r="M89" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) includes a built-in backup and restore capability for the Avi Controller configuration database. The configuration database defines all clouds, virtual services, users, tenants, and related entities. Protecting it is the primary mechanism for recovering the Avi control plane after a Controller failure.
+Backup operations can be created on-demand or on a recurring schedule via the Controller web UI, CLI (using the export command), or REST API (using the /api/scheduler/ endpoint). The scheduler supports configurable frequency units, including hourly, daily, and weekly intervals, with the run mode set to periodic. For single-node Controller deployments, enabling periodic external configuration backups is mandatory; the product documentation states that external backups are required to handle recovery from a complete VM or disk failure.
+Avi supports multiple backup storage targets. Local backups are stored directly on the Controller with a configurable retention count, configured via the "Enable Local Backups (On Controller)" setting. Remote backups are transferred over Secure Copy Protocol (SCP) or Secure File Transfer Protocol (SFTP) to an off-Controller server, configured via the "Enable Remote Server Backup" setting. In 9.1, configuration backups can also be stored in Amazon S3 buckets as an additional remote storage target. When deployed as part of VCF, Avi backups are stored by default on the same server used for VCF Operations appliance backups; the recommended best practice is to configure an external SFTP server as the backup destination. VCF Operations can be used to configure the external backup server and storage path for Avi backups. Product guidance also recommends storing backups with clear labeling that includes version and date information.
+Before a restore proceeds, Avi performs a set of pre-restore checks to validate the backup image. In 9.1, these checks include verification of backup configuration version compatibility, presence of all file objects from the configuration on the Controller, FIPS mode consistency between the backup and the current Controller environment, Service Engine attachment verification, system configuration validation, and patch verification. All checks must pass before the restore operation is allowed to proceed.
+Restore operations can be performed via the CLI (import command with the keep_uuid option to restore configuration to an empty Controller), the web UI, or the REST API restore endpoint. The API method accepts a configuration file and a passphrase parameter to decrypt an encrypted backup; the passphrase must match the one used when creating the backup. Restore operations generate system reports tracking operation state, start time, end time, duration, and total checks completed. The Controller metrics database can also be exported and imported separately to prevent loss of metrics data during version rollbacks. If all three nodes of a Controller cluster are permanently unavailable, recovery must be performed using a backup and restore procedure.
+For multi-site deployments, Avi GSLB (Global Server Load Balancing) supports an Active disaster recovery deployment mode, enabling traffic redirection to a healthy site when a primary site fails. Avi GSLB adaptive replication mode also protects against configuration errors propagating across data centers by preventing faulty configuration objects from being replicated to follower sites.
+The Avi backup and restore capability covers the Controller configuration plane. Application data, workload VM images, and the broader RTO/RPO framework depend on organizational process decisions and on the underlying VCF platform for VM-level data protection (see VCF Coverage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>12.1(b)</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>BCD-01, BCD-11</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Restoration and recovery procedures and methods.</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides built-in backup capabilities across its management components, workload layers, and storage subsystems, supporting organizations in meeting their Recovery Time Objectives (RTOs) and Recovery Point Objectives (RPOs).
+Management component backups
+VCF supports backup of all core management components. VMware vCenter supports both file-based and image-based backup methods, with file-based daily backups configured through the vCenter Management Interface of each vCenter instance. vCenter file-based backup and restore supports FTP, FTPS, HTTP, HTTPS, SFTP, NFS, or SMB as the backup server protocol. vCenter file-based backup optionally encrypts backup files using an encryption password that must be provided during restore; because vCenter backups contain the Key Derivation Key used for vSphere encryption, backup files should be stored on a secured backup server with appropriate access controls. VCF Operations similarly supports file-based and image-based backup methods. NSX Manager uses file-based backup, which VCF Operations configures automatically during the initial bring-up process. File-based backup jobs for VCF Operations and vCenter must be configured separately after deployment.
+Scheduled backups should be implemented to prepare for critical failure scenarios, upgrade events, or certificate updates of management components. To capture a consistent state across related components, VCF requires creating a series of coordinated backup jobs that run simultaneously across component nodes. Simultaneous backups of component nodes help ensure that the backed-up state is logically consistent, reducing the need for integrity remediation during a restore. On-demand manual backups can be taken after a successful recovery operation or after a scheduled backup failure. VCF Operations backup is also configured to take a backup on state change, providing an additional layer of protection when configuration changes occur.
+The backup file server stores backups from all NSX Manager or Global Manager nodes, and NSX includes a script to automatically delete old backups to manage storage consumption. NSX Global Manager backups should be periodically cleaned up to avoid excessive storage consumption on the backup file server. VCF Operations for Networks can store backups on local storage, retaining up to five backup files, or upload them to SSH or FTP servers. An initial on-demand backup should be performed after configuring VCF Operations to verify that backups complete successfully before relying on scheduled jobs. Sufficient storage capacity must be provisioned to accommodate backup data across all components.
+Backup integrity and restore procedures
+Backup integrity verification in VCF centers on version compatibility. When restoring a vCenter instance from a file-based backup, administrators must have a valid backup that matches the exact version of the vCenter appliance being restored to. VCF Operations must be available before restoring vCenter, and vCenter must be available before restoring VCF Operations, establishing a defined dependency order for restore operations. These dependencies require careful sequencing during recovery to restore the management plane to a consistent state.
+Workload-level data protection
+For workload-level data protection, VCF provides several mechanisms. Changed Block Tracking (CBT) tracks modified disk blocks on virtual machines, enabling incremental backups that reduce backup windows and storage requirements. VMware vSphere Storage APIs for Data Protection (VADP) provide a standardized interface for third-party backup solutions to integrate with VCF. vSphere Supervisor supports backup of VM Service VMs through backup partner solutions based on VADP, and if a VADP-based backup solution is deployed on the default management cluster, the solution must be properly started and operational before starting up or shutting down VCF. Quiesced snapshots are appropriate for automated or periodic backups of VM Service virtual machines, as they capture a consistent state before the backup operation proceeds. VCF Automation supports snapshotting a VM group to create an object that references distinct snapshots for each member VM; restoring a VM group snapshot restores each member of the group.
+vSphere Supervisor control plane backup and restore can be performed using vCenter file-based backup and restore from the Workload Management UI. For applications that provide their own backup capabilities, VCF documentation recommends using application-specific backup methods rather than relying on filesystem backup alone.
+vSAN data protection and snapshots
+vSAN Data Protection allows snapshots to be managed through protection groups with configurable snapshot retention policies and scheduling intervals. The native Snapshot Service is supported by vSAN Express Storage Architecture (ESA) but not by vSAN Original Storage Architecture (OSA). Native snapshots in vSAN ESA are much faster than traditional vSphere snapshots because a base VMDK and its snapshots are contained in one vSAN object rather than being separate objects, allowing more frequent backups and faster recovery. In vSAN OSA, snapshots are separate vSAN objects. The vSAN Distributed File System Snapshot can be used by third-party backup vendors to copy changed files incrementally to a different physical location. The vSAN Snapshot Service API provides programmatic access for operations including creating linked clones from snapshots and restoring deleted virtual machines.
+VMware Kubernetes Service backup
+VMware Kubernetes Service (VKS) and the Supervisor layer extend VCF's backup capabilities to containerized workloads, cluster state, and persistent volume data. VKS Supervisor backup and restore for cluster node VMs is activated through the vCenter backup feature available in the vCenter Management Interface, integrating Kubernetes cluster state backup with the same management-plane backup infrastructure used for other VCF components.
+For workload-level backup of VKS clusters, the platform supports three complementary methods: vSphere Plugin Snapshot (CSI Snapshot), File System Backup (FSB), and the Velero Plugin for vSphere. The vSphere Plugin Snapshot method produces crash-consistent, block-level backups of persistent volumes through the Container Storage Interface (CSI) layer and supports snapshot direct access and network traffic offload; it is faster and less resource-intensive than filesystem backup for complex filesystems with large numbers of small files, making it well-suited for production databases and high-IOPS applications. The File System Backup method operates at the filesystem level, supports NFS volumes and incremental backups where unchanged files are not re-transferred between runs, and offers backup repository features including deduplication, compression, and encryption; it is appropriate for legacy volumes with non-CSI storage. The Velero Plugin for vSphere can back up and restore both stateless and stateful applications running on vSphere Pods in the Supervisor. Platform teams can use both FSB and CSI Volume Snapshots within a single protection strategy to maximize data durability across workload types. VKS cluster backup supports opt-in and opt-out approaches for FSB volume backup, giving operators control over which volumes are included in filesystem-level operations. Third-party backup software can also integrate with VKS clusters using the standard Kubernetes CSI snapshot API: tools create a VolumeSnapshot object from the target PVC, materialize a temporary PVC from the snapshot, and use a Data Mover pod to transfer data to the backup destination. Kubernetes implements Persistent Volume Claim as Snapshot Source Protection, which blocks deletion of in-use API objects while a snapshot is in progress, reducing the risk of partial or inconsistent backup data. Kubernetes also supports provisioning a new PersistentVolumeClaim directly from a VolumeSnapshot by specifying the snapshot as the dataSource, enabling volume-level point-in-time recovery without requiring a full application restore workflow.
+VKS cluster management provides a Create backup wizard that allows users to create backups immediately or schedule backups of specified data resources in a cluster. Backup scheduling supports immediate execution, recurring schedule formats with targeted start times, or custom cron expressions; automated backup scheduling can also be configured using the Velero CLI with the velero schedule create command, specifying the interval or cron expression for recurring backup operations. For on-demand backups outside a scheduled window, the velero backup create command backs up Kubernetes resources and persistent volume data for stateful workloads, with support for per-namespace targeting and volume snapshot inclusion. VKS cluster backups can retain a maximum of 720 backups per backup schedule; when high-frequency schedules are required, the retention period should be reduced to remain within this limit. Backup schedules can be edited, paused, or deleted through the management interface. File system backups are included in the restore by default, and snapshot data can be moved to a separate backup storage location. Before defining a backup, a target location and credential must be created; if a data protection credential is deleted, scheduled backups relying on that credential will fail on their next execution, creating a detectable gap in backup execution history that administrators should monitor. Creating a backup schedule requires the Organization Administrator or Project Administrator role.
+VKS cluster backup and restore operations are managed through the VCF Automation Tenant Portal under Manage &amp; Govern &gt; VCF Services &gt; Kubernetes Management &gt; Clusters &gt; Data Protection. The portal provides restore operations on specific backups, and a dedicated cross-cluster restore capability in the Data Protection tab enables restoring backups from a source cluster to a different target cluster. VKS cluster management supports backup and restore of an entire cluster, selected namespaces from the backup, or specific resources identified by a label. The CloneFromSnapshot CRD includes a status.phase field that tracks restore progress through multiple phases, providing operational visibility during restore operations.
+For Kubernetes cluster state, etcd is the backing store for all Kubernetes objects, and clusters using etcd should have a backup plan. etcd backup can be performed using the built-in etcdctl snapshot save command by specifying the endpoint, CA certificate, and client credentials, or by taking a volume snapshot of the etcd storage volume when the underlying storage supports it. etcd snapshots can be restored from a previous snapshot file or from the remaining data directory, and cross-patch-version restores are supported. During kubeadm upgrades, automatic backup folders are written to /etc/kubernetes/tmp containing etcd data and manifests as a recovery point.
+Backup automation through APIs
+VCF exposes backup automation through its APIs, including the RecoveryBackupJobBackupRequest data structure for specifying backup location, protocol, authorization, and database scope, as well as the RecoveryBackupSchedulesUpdateSpec for programmatically managing backup schedules.
+Disaster recovery planning
+For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VCF Protection and Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
+VCF directly provides the mechanisms for creating recurring backups, managing retention, and supporting RTO/RPO requirements through multiple backup and snapshot methods. However, organizations must establish backup policies, define RTO/RPO targets, schedule regular restore testing, and maintain backup infrastructure such as external storage and third-party backup solutions to fully satisfy this control.</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend's Security Services Platform (SSP) provides backup and restore capabilities for the vDefend control plane, covering firewall rules, microsegmentation policies, IDS/IPS configurations, Bare Metal server information, tokens, and all associated security data managed by the platform. These backups protect against data loss from hardware or software malfunctions, data corruption, malware incidents, or unintentional deletion.
+SSP supports recurring backup schedules configurable through the Backup Schedule interface, with frequency options ranging from 6 hours to 720 hours (30 days), as well as weekly scheduling by selecting the day and time. Recurring backups can be activated or deactivated by toggling the Recurring setting. Best practice guidance recommends scheduling backups during periods of low platform usage to minimize operational impact. A backup should also be performed before executing scale-out operations on the SSP cluster, to preserve the current configuration state before significant topology changes. Backup data is encrypted with a passphrase and transmitted to an SFTP server. Adequate storage must be verified on the backup server before activating recurring backups, and the platform must be in a healthy state for backup operations to proceed. Backup is also blocked if NSX is not onboarded to SSP.
+SSP maintains a Backup History section that displays the status of each backup operation, showing "Completed" when the operation succeeds. When backup or restore operations enter a failed state, pod logs provide detailed error messages, including database query failures and volume attachment errors, to support troubleshooting. Restoration supports deploying the backed-up configuration onto the same SSP instance or a new instance, enabling recovery when the current instance is in a non-recoverable state. Restoration requires that the same NSX instance that was onboarded at the time of backup be used, and that the platform be deployed on the same vSAN datastore and build version as the initial installation. Certificate consistency between backup and restored environments must be maintained to avoid disruptions to NDR Sensor connectivity.
+These capabilities address the backup component of this control for vDefend's own configuration and policy data. vDefend does not back up general workload data or application-level information; those responsibilities fall to the broader VCF platform's replication, snapshot, and backup mechanisms, including vSAN Data Protection, Protection and Recovery (PNR), and integration with third-party backup providers. vDefend's contribution is limited to protecting the security policy and configuration data that defines the network security posture of the environment.</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
+Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
+vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
+In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
+Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+        </is>
+      </c>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
+Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
+Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
+DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
+DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
+Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
+DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
+Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
+        </is>
+      </c>
+      <c r="M90" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N90" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) includes a built-in backup and restore capability for the Avi Controller configuration database. The configuration database defines all clouds, virtual services, users, tenants, and related entities. Protecting it is the primary mechanism for recovering the Avi control plane after a Controller failure.
+Backup operations can be created on-demand or on a recurring schedule via the Controller web UI, CLI (using the export command), or REST API (using the /api/scheduler/ endpoint). The scheduler supports configurable frequency units, including hourly, daily, and weekly intervals, with the run mode set to periodic. For single-node Controller deployments, enabling periodic external configuration backups is mandatory; the product documentation states that external backups are required to handle recovery from a complete VM or disk failure.
+Avi supports multiple backup storage targets. Local backups are stored directly on the Controller with a configurable retention count, configured via the "Enable Local Backups (On Controller)" setting. Remote backups are transferred over Secure Copy Protocol (SCP) or Secure File Transfer Protocol (SFTP) to an off-Controller server, configured via the "Enable Remote Server Backup" setting. In 9.1, configuration backups can also be stored in Amazon S3 buckets as an additional remote storage target. When deployed as part of VCF, Avi backups are stored by default on the same server used for VCF Operations appliance backups; the recommended best practice is to configure an external SFTP server as the backup destination. VCF Operations can be used to configure the external backup server and storage path for Avi backups. Product guidance also recommends storing backups with clear labeling that includes version and date information.
+Before a restore proceeds, Avi performs a set of pre-restore checks to validate the backup image. In 9.1, these checks include verification of backup configuration version compatibility, presence of all file objects from the configuration on the Controller, FIPS mode consistency between the backup and the current Controller environment, Service Engine attachment verification, system configuration validation, and patch verification. All checks must pass before the restore operation is allowed to proceed.
+Restore operations can be performed via the CLI (import command with the keep_uuid option to restore configuration to an empty Controller), the web UI, or the REST API restore endpoint. The API method accepts a configuration file and a passphrase parameter to decrypt an encrypted backup; the passphrase must match the one used when creating the backup. Restore operations generate system reports tracking operation state, start time, end time, duration, and total checks completed. The Controller metrics database can also be exported and imported separately to prevent loss of metrics data during version rollbacks. If all three nodes of a Controller cluster are permanently unavailable, recovery must be performed using a backup and restore procedure.
+For multi-site deployments, Avi GSLB (Global Server Load Balancing) supports an Active disaster recovery deployment mode, enabling traffic redirection to a healthy site when a primary site fails. Avi GSLB adaptive replication mode also protects against configuration errors propagating across data centers by preventing faulty configuration objects from being replicated to follower sites.
+The Avi backup and restore capability covers the Controller configuration plane. Application data, workload VM images, and the broader RTO/RPO framework depend on organizational process decisions and on the underlying VCF platform for VM-level data protection (see VCF Coverage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>BCD-11, BCD-11.1, BCD-11.5</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall set up backup systems that can be activated in accordance with the backup policies and procedures, as well as restoration and recovery procedures and methods. The activation of backup systems shall not jeopardise the security of the network and information systems or the availability, authenticity, integrity or confidentiality of data. Testing of the backup procedures and restoration and recovery procedures and methods shall be undertaken periodically.</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides built-in backup capabilities across its management components, workload layers, and storage subsystems, supporting organizations in meeting their Recovery Time Objectives (RTOs) and Recovery Point Objectives (RPOs).
+Management component backups
+VCF supports backup of all core management components. VMware vCenter supports both file-based and image-based backup methods, with file-based daily backups configured through the vCenter Management Interface of each vCenter instance. vCenter file-based backup and restore supports FTP, FTPS, HTTP, HTTPS, SFTP, NFS, or SMB as the backup server protocol. vCenter file-based backup optionally encrypts backup files using an encryption password that must be provided during restore; because vCenter backups contain the Key Derivation Key used for vSphere encryption, backup files should be stored on a secured backup server with appropriate access controls. VCF Operations similarly supports file-based and image-based backup methods. NSX Manager uses file-based backup, which VCF Operations configures automatically during the initial bring-up process. File-based backup jobs for VCF Operations and vCenter must be configured separately after deployment.
+Scheduled backups should be implemented to prepare for critical failure scenarios, upgrade events, or certificate updates of management components. To capture a consistent state across related components, VCF requires creating a series of coordinated backup jobs that run simultaneously across component nodes. Simultaneous backups of component nodes help ensure that the backed-up state is logically consistent, reducing the need for integrity remediation during a restore. On-demand manual backups can be taken after a successful recovery operation or after a scheduled backup failure. VCF Operations backup is also configured to take a backup on state change, providing an additional layer of protection when configuration changes occur.
+The backup file server stores backups from all NSX Manager or Global Manager nodes, and NSX includes a script to automatically delete old backups to manage storage consumption. NSX Global Manager backups should be periodically cleaned up to avoid excessive storage consumption on the backup file server. VCF Operations for Networks can store backups on local storage, retaining up to five backup files, or upload them to SSH or FTP servers. An initial on-demand backup should be performed after configuring VCF Operations to verify that backups complete successfully before relying on scheduled jobs. Sufficient storage capacity must be provisioned to accommodate backup data across all components.
+Backup integrity and restore procedures
+Backup integrity verification in VCF centers on version compatibility. When restoring a vCenter instance from a file-based backup, administrators must have a valid backup that matches the exact version of the vCenter appliance being restored to. VCF Operations must be available before restoring vCenter, and vCenter must be available before restoring VCF Operations, establishing a defined dependency order for restore operations. These dependencies require careful sequencing during recovery to restore the management plane to a consistent state.
+Workload-level data protection
+For workload-level data protection, VCF provides several mechanisms. Changed Block Tracking (CBT) tracks modified disk blocks on virtual machines, enabling incremental backups that reduce backup windows and storage requirements. VMware vSphere Storage APIs for Data Protection (VADP) provide a standardized interface for third-party backup solutions to integrate with VCF. vSphere Supervisor supports backup of VM Service VMs through backup partner solutions based on VADP, and if a VADP-based backup solution is deployed on the default management cluster, the solution must be properly started and operational before starting up or shutting down VCF. Quiesced snapshots are appropriate for automated or periodic backups of VM Service virtual machines, as they capture a consistent state before the backup operation proceeds. VCF Automation supports snapshotting a VM group to create an object that references distinct snapshots for each member VM; restoring a VM group snapshot restores each member of the group.
+vSphere Supervisor control plane backup and restore can be performed using vCenter file-based backup and restore from the Workload Management UI. For applications that provide their own backup capabilities, VCF documentation recommends using application-specific backup methods rather than relying on filesystem backup alone.
+vSAN data protection and snapshots
+vSAN Data Protection allows snapshots to be managed through protection groups with configurable snapshot retention policies and scheduling intervals. The native Snapshot Service is supported by vSAN Express Storage Architecture (ESA) but not by vSAN Original Storage Architecture (OSA). Native snapshots in vSAN ESA are much faster than traditional vSphere snapshots because a base VMDK and its snapshots are contained in one vSAN object rather than being separate objects, allowing more frequent backups and faster recovery. In vSAN OSA, snapshots are separate vSAN objects. The vSAN Distributed File System Snapshot can be used by third-party backup vendors to copy changed files incrementally to a different physical location. The vSAN Snapshot Service API provides programmatic access for operations including creating linked clones from snapshots and restoring deleted virtual machines.
+VMware Kubernetes Service backup
+VMware Kubernetes Service (VKS) and the Supervisor layer extend VCF's backup capabilities to containerized workloads, cluster state, and persistent volume data. VKS Supervisor backup and restore for cluster node VMs is activated through the vCenter backup feature available in the vCenter Management Interface, integrating Kubernetes cluster state backup with the same management-plane backup infrastructure used for other VCF components.
+For workload-level backup of VKS clusters, the platform supports three complementary methods: vSphere Plugin Snapshot (CSI Snapshot), File System Backup (FSB), and the Velero Plugin for vSphere. The vSphere Plugin Snapshot method produces crash-consistent, block-level backups of persistent volumes through the Container Storage Interface (CSI) layer and supports snapshot direct access and network traffic offload; it is faster and less resource-intensive than filesystem backup for complex filesystems with large numbers of small files, making it well-suited for production databases and high-IOPS applications. The File System Backup method operates at the filesystem level, supports NFS volumes and incremental backups where unchanged files are not re-transferred between runs, and offers backup repository features including deduplication, compression, and encryption; it is appropriate for legacy volumes with non-CSI storage. The Velero Plugin for vSphere can back up and restore both stateless and stateful applications running on vSphere Pods in the Supervisor. Platform teams can use both FSB and CSI Volume Snapshots within a single protection strategy to maximize data durability across workload types. VKS cluster backup supports opt-in and opt-out approaches for FSB volume backup, giving operators control over which volumes are included in filesystem-level operations. Third-party backup software can also integrate with VKS clusters using the standard Kubernetes CSI snapshot API: tools create a VolumeSnapshot object from the target PVC, materialize a temporary PVC from the snapshot, and use a Data Mover pod to transfer data to the backup destination. Kubernetes implements Persistent Volume Claim as Snapshot Source Protection, which blocks deletion of in-use API objects while a snapshot is in progress, reducing the risk of partial or inconsistent backup data. Kubernetes also supports provisioning a new PersistentVolumeClaim directly from a VolumeSnapshot by specifying the snapshot as the dataSource, enabling volume-level point-in-time recovery without requiring a full application restore workflow.
+VKS cluster management provides a Create backup wizard that allows users to create backups immediately or schedule backups of specified data resources in a cluster. Backup scheduling supports immediate execution, recurring schedule formats with targeted start times, or custom cron expressions; automated backup scheduling can also be configured using the Velero CLI with the velero schedule create command, specifying the interval or cron expression for recurring backup operations. For on-demand backups outside a scheduled window, the velero backup create command backs up Kubernetes resources and persistent volume data for stateful workloads, with support for per-namespace targeting and volume snapshot inclusion. VKS cluster backups can retain a maximum of 720 backups per backup schedule; when high-frequency schedules are required, the retention period should be reduced to remain within this limit. Backup schedules can be edited, paused, or deleted through the management interface. File system backups are included in the restore by default, and snapshot data can be moved to a separate backup storage location. Before defining a backup, a target location and credential must be created; if a data protection credential is deleted, scheduled backups relying on that credential will fail on their next execution, creating a detectable gap in backup execution history that administrators should monitor. Creating a backup schedule requires the Organization Administrator or Project Administrator role.
+VKS cluster backup and restore operations are managed through the VCF Automation Tenant Portal under Manage &amp; Govern &gt; VCF Services &gt; Kubernetes Management &gt; Clusters &gt; Data Protection. The portal provides restore operations on specific backups, and a dedicated cross-cluster restore capability in the Data Protection tab enables restoring backups from a source cluster to a different target cluster. VKS cluster management supports backup and restore of an entire cluster, selected namespaces from the backup, or specific resources identified by a label. The CloneFromSnapshot CRD includes a status.phase field that tracks restore progress through multiple phases, providing operational visibility during restore operations.
+For Kubernetes cluster state, etcd is the backing store for all Kubernetes objects, and clusters using etcd should have a backup plan. etcd backup can be performed using the built-in etcdctl snapshot save command by specifying the endpoint, CA certificate, and client credentials, or by taking a volume snapshot of the etcd storage volume when the underlying storage supports it. etcd snapshots can be restored from a previous snapshot file or from the remaining data directory, and cross-patch-version restores are supported. During kubeadm upgrades, automatic backup folders are written to /etc/kubernetes/tmp containing etcd data and manifests as a recovery point.
+Backup automation through APIs
+VCF exposes backup automation through its APIs, including the RecoveryBackupJobBackupRequest data structure for specifying backup location, protocol, authorization, and database scope, as well as the RecoveryBackupSchedulesUpdateSpec for programmatically managing backup schedules.
+Disaster recovery planning
+For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VCF Protection and Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
 VCF directly provides the mechanisms for creating recurring backups, managing retention, and supporting RTO/RPO requirements through multiple backup and snapshot methods. However, organizations must establish backup policies, define RTO/RPO targets, schedule regular restore testing, and maintain backup infrastructure such as external storage and third-party backup solutions to fully satisfy this control.</t>
         </is>
       </c>
@@ -8243,16 +8045,16 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of real-time and near-real-time failover capability across compute, storage, networking, and management components, directly addressing this control's requirements for maintaining availability of critical technology assets, applications, services, and data.
-At the compute layer, vSphere High Availability (HA) monitors host health and automatically restarts virtual machines on surviving hosts when a failure is detected. Automatic failover shifts resources to healthy nodes in the cluster without manual intervention. For workloads requiring zero downtime, vSphere Fault Tolerance maintains a live shadow instance of a protected virtual machine, so that any hardware failure results in no data loss and no service interruption. Proactive HA integrates with hardware partner monitoring through vSAN Proactive Hardware Management (PHM), which detects degrading components via predictive failure events generated by the OEM vendor. When a predictive failure is identified, Proactive HA places the affected host into maintenance mode, evacuating VMs before a failure occurs. A supported Hardware Support Manager (HSM) must be configured and registered to VMware vCenter for this capability.
-vSphere HA admission control can be configured to reserve a percentage of the cluster's aggregate CPU and memory resources specifically for failover capacity. Three admission control policy types are available: cluster resource percentage, slot policy, and dedicated failover hosts. The "Host failure cluster tolerates" admission control setting defines how many simultaneous host failures the cluster can absorb while still restarting all affected workloads. Remediation mode can be set to Quarantine mode, Maintenance mode, or Mixed mode to control how host failures are handled. For vSAN stretched clusters, admission control should reserve 50% of the cluster's aggregate CPU and memory resources so that all virtual machines from one site can be restarted on the other. vSphere HA can also use DRS to bring hosts out of standby mode and migrate virtual machines to defragment cluster resources, so that failover capacity remains available when aggregate resources are fragmented across the cluster.
-vMotion enables live migration of running virtual machines to a new host without interruption in availability. VCF Operations HCX extends this mobility to remote sites for cross-site workload movement. HCX Network Extension High Availability provides failover protection for extended networks. Network Extension appliances operate in active-standby pairs through role negotiation, and during a failover event the standby pair takes over the Network Extension service from the active pair. After the failed appliance recovers, the pair renegotiates roles and returns to a healthy state, providing self-healing behavior.
-For site-level failover, vSAN stretched clusters span two geographically separated sites with a witness host, enabling VCF to tolerate an entire site failure. When one site becomes unavailable, vSphere HA restarts affected virtual machines on the remaining active site. The storage policy "Site disaster tolerance" rule, when configured for site mirroring, allows the stretched cluster to tolerate a witness host failure even when one site is already unavailable. Site-specific isolation response addresses should be configured so that vSphere HA can validate host isolation even during a network failure between sites. Both availability zones must contain an equal number of hosts to provide failover capacity when either zone goes down.
-At the storage layer, vSAN provides storage-level resilience through multiple mechanisms. vSAN fault domains enable the environment to tolerate entire rack failures in addition to single host, storage disk, or network failures, by organizing hosts into separate fault domains so that vSAN distributes object replicas across different physical racks. Configuring fault domains of smaller sizes reduces the impact of a potential rack failure. vSAN Express Storage Architecture (ESA) supports disaggregated storage clusters that pool storage devices across dedicated hosts, separating storage resources from compute hosts. Storage multipathing provides path selection policies with automatic failover to maintain storage access during path failures, and NFS 4.1 datastores support multipathing for redundant storage connectivity. Path policies must be consistent within a cluster. vSAN network implementations should typically use four physical uplinks for full redundancy, with additional failover NICs provisioned for the vSAN network. The teaming and failover policy configured on the backing virtual switch provides network redundancy for vSAN traffic.
-At the networking layer, multi-NIC teaming, Link Aggregation Control Protocol (LACP), and failover policies handle network-level failover. Advanced NIC teaming can implement an air gap so that a failure on one network path does not affect the other. NSX tier-0 gateways support active-standby high availability mode with configurable failover behavior (preemptive or nonpreemptive). NSX Edge nodes perform graceful failover to a peer Edge when a failure or maintenance event occurs. For multi-site NSX deployments, the NSX Global Manager can be deployed in a highly available cluster model with a standby cluster ready for manual failover. In unplanned switchover scenarios where a primary site becomes unavailable, a forced failover can be initiated to restore networking services at the surviving site.
-VCF also provides failover capabilities for its management and operations components. vCenter supports native high availability through vCenter High Availability, which deploys Active, Passive, and Witness nodes; when the Active node becomes unavailable, the Passive node automatically assumes the active role, preserving management plane operations without manual intervention. The Continuous Availability VCF Operations Model deploys a highly available cluster with data redundancy across different availability zones, maintaining service during a single availability zone failure. VCF Operations failover server sets establish server connections in a defined order and can link separate server sets, providing high availability for monitoring infrastructure in complex environments. Application monitoring high availability with activated collector groups in failover mode can continue monitoring applications without losing data or metrics even when a cloud proxy is down or its components fail. Cloud proxy itself supports high availability. The High Availability VCF Automation Model supports use of an external load balancer for management service resilience.
-The VCF platform's Kubernetes consumption layer, provided by vSphere Supervisor and VMware Kubernetes Service (VKS), extends these failover mechanisms to containerized workloads. Supervisor requires vSphere HA and fully-automated DRS on the underlying vSphere cluster, so VKS node virtual machines benefit from the same automatic restart and workload balancing that protects traditional VMs. In a zoned Supervisor deployment, Supervisor stretches across three vSphere clusters, with each cluster assigned to a vSphere Zone that represents a distinct failure domain; a failure in one zone does not automatically affect workloads running in the other zones. Starting with VCF and VKS 3.6, Node Auto Placement allows the VKS placement engine to automatically manage resource distribution across failure domains, spreading node pools across zones using failure domain specifications in the cluster topology. Before any zone is taken out of service, control plane nodes must be relocated to a different zone to maintain cluster availability, supporting planned maintenance without workload interruption. Kubernetes provides self-healing behavior at the workload layer: the platform automatically replaces failed containers, reschedules workloads when nodes become unavailable, and continuously reconciles the system toward its desired state. VKS cluster version updates use a rolling model in which control plane nodes are updated first, followed by worker nodes one at a time per node pool starting with the Zone-A pool, keeping the cluster operational throughout planned maintenance. For stateful workloads, VKS clusters use the VMware vSphere Container Storage Interface (CSI) driver to provision persistent volumes backed by vSAN datastores, anchoring data durability in the same vSAN fault-tolerance mechanisms described above. High-availability applications on VKS must be deployed as replicated stateless or stateful workloads to take advantage of these self-healing mechanisms at the application layer.
-For planned migrations and disaster recovery workflows, vSphere Replication supports configurable Recovery Point Objectives (RPO) for near-real-time data replication. Planned failover on a replication group allows recovery of workloads on a target site and then reverses the direction of replication, making the target site the new source. The recommended approach is to combine real-time availability through HA with site-wide disaster recovery for maximum resilience.</t>
+          <t>VCF provides failover capabilities across compute, storage, network, and management layers that can be deployed at sites separate from the primary infrastructure, maintaining operations with minimal data loss and disruption.
+At the compute layer, vSphere High Availability (HA) automatically restarts virtual machines on surviving hosts after a host failure. Admission control policies reserve sufficient capacity for restart operations, and dedicated failover hosts can be reserved exclusively for this purpose. For workloads requiring zero downtime, vSphere Fault Tolerance maintains a live shadow instance of a virtual machine on a separate host, providing continuous availability with no data loss during a hardware failure. Proactive HA integrates with hardware health providers to detect degrading components and place hosts into maintenance mode before a failure occurs, with vSAN supporting Proactive HA using maintenance mode as the remediation method for all failure types.
+The primary mechanism for site-level failover is vSAN stretched clusters, which extend a single vSAN cluster across two geographically separated sites with a witness host at a third location. vSAN stretched clusters use a site mirroring storage policy that maintains synchronized copies of data at both sites. When a site failure occurs, vSphere HA restarts affected virtual machines on the remaining active site. The site disaster tolerance storage policy rule, configured to "Site mirroring - stretched cluster," allows the cluster to tolerate both a site failure and a witness host failure simultaneously. To support failover with minimal resource contention, vSphere HA admission control can be configured to reserve 50% of the cluster's aggregate CPU and memory resources, so that all virtual machines from one site can be restarted on the other site during a site failure. The host failure cluster tolerates setting should be updated to reflect the number of hosts in each availability zone after cluster expansion. For network partition detection, administrators should specify two additional site-specific isolation response addresses, one in each site, so that vSphere HA can validate host isolation even when the inter-site network link fails.
+Within vSAN clusters, fault domains provide an additional layer of resilience by grouping hosts according to their physical location. Storage policies reference fault domains to distribute data replicas across separate failure boundaries, so that a failure in one physical location does not result in data loss. vSAN storage policies allow administrators to define the level of data redundancy, from no redundancy to full site mirroring, based on availability requirements.
+VCF supports an Availability Zone fault tolerant deployment model that distributes workloads across availability zones for resilience. This model requires the physical fabric to extend uplink VLANs, edge TEP VLANs, and edge management VLANs across zones. When stretching a cluster in a workload domain, the default management vSphere cluster must already be stretched, establishing a foundation of cross-site redundancy before extending it to additional workload domains. For Kubernetes workloads, vSphere HA can be configured for a Supervisor running on a vSAN stretched cluster, providing high availability for containerized applications.
+VMware Kubernetes Service (VKS) running on the VCF platform extends these availability principles to containerized workloads through vSphere Zone-based failure domain separation. In a zoned Supervisor deployment, Supervisor stretches across three vSphere clusters, each assigned to a distinct vSphere Zone that represents an independent failure domain, and vSphere HA and fully-automated DRS are prerequisites for all Supervisor deployments. VKS cluster control planes are configured with three replicas distributed across these failure zones so that a single zone outage does not interrupt cluster scheduling or operations. Node auto-placement provisions worker nodes across zones using failureDomain specifications in the cluster topology, distributing workloads so that a zone failure does not take an application entirely offline; zone evacuation procedures support relocating control plane nodes from a zone before it is removed from service, allowing planned maintenance without disruption. During version updates, the VKS rolling update model updates control plane nodes first, then rolls worker nodes one at a time starting with the Zone-A node pool, limiting the number of nodes simultaneously unavailable. At the application layer, Kubernetes PodDisruptionBudget (PDB) resources protect deployed workloads by specifying the minimum number of pods that must remain available during voluntary disruptions, and cluster operators are required to respect these budgets; ReplicaSets, Deployments, and StatefulSets distribute application replicas across nodes and zones to tolerate individual node failures. Persistent volumes for VKS workloads are provisioned through the vSphere CSI driver and can be protected using vSphere Plugin Snapshot, CSI Snapshot, or File System Backup methods, providing crash-consistent recovery points for stateful applications.
+For disaster recovery scenarios beyond stretched clusters, VCF provides Application Disaster Recovery, which supports failover to a secondary site to maintain operations during major disruptions. vSphere Replication supports configurable Recovery Point Objective (RPO) settings that define the maximum acceptable data loss window during failover. VCF Operations HCX provides workload mobility services including Bulk Migration, Replication Assisted vMotion, cross-cloud vMotion, and OS Assisted Migration for moving workloads to remote sites. HCX Network Extension High Availability creates redundant pairs of network extension appliances that automatically fail over, maintaining extended network connectivity. Network Extension HA protects against individual appliance failures within an HA group, and after recovery, appliances renegotiate roles and the group returns to a healthy state.
+Network resilience is built through multi-NIC teaming, Link Aggregation Control Protocol (LACP), and failover policies that maintain connectivity during link failures. Network adapter teaming provides redundancy such that if a NIC fails, the remaining NICs in the team continue to pass traffic. NSX tier-0 gateways support active-active and active-standby high availability modes, with services such as SNAT, DNAT, load balancing, and VPN supported in active-standby mode. Storage multipathing provides failover for storage connectivity, including NFS 4.1 datastores that support multipathing for redundant storage paths.
+VCF Operations supports a Continuous Availability deployment model that provides a highly available cluster with data redundancy across different availability zones. In this architecture, each object is stored on two nodes (primary and replica) distributed across fault domains, providing redundancy in the event of a fault domain failure. VMware vCenter itself also supports a High Availability deployment, in which an Active node, Passive node, and Witness node form a three-node cluster; the Passive node receives continuous configuration replication from the Active node and automatically takes over the active role if the Active node fails, providing management plane continuity without manual intervention.
+VCF's identity infrastructure also supports failover through secondary domain controllers that act as a backup for the VCF Identity Broker when the primary domain controller is not reachable.</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -8262,11 +8064,13 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) implements failover capabilities for its own security infrastructure to maintain continuous network security enforcement during component failures.
-The vDefend gateway firewall operates in primary-passive high availability mode with non-preemptive failover. When all uplink routing links go down on the active Edge node, failover is triggered and the standby node assumes the active role. Firewall flow state is synchronized between Edge nodes, so existing sessions are preserved across failover events without requiring re-establishment. Sessions resume after a brief convergence period during Edge node failover. This flow synchronization allows security policy enforcement to continue through a Gateway Firewall failover without leaving traffic unprotected during the transition.
-The Security Services Platform (SSP), which hosts vDefend's advanced threat detection functions including IDS/IPS, Malware Prevention, and Network Detection and Response, has built-in high availability by default. Enabling vSphere HA is recommended for the vSphere cluster hosting the Security Services Platform. When a host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster. Admission Control should be configured with sufficient resource reservations so that recovery capacity is available. Configuring a storage policy with RAID provides datastore-level failure tolerance alongside vSphere HA. In environments using vSAN stretched clusters, the Security Services Platform benefits from storage replication across two physically distinct sites, providing site-level resilience and protection against multiple host failures within a single site. The License Hub component also supports vSphere HA for host-level failure recovery.
-The Distributed Firewall operates at the hypervisor kernel level on every host, providing inherent distribution with no single point of failure for workload security policy enforcement. One operational characteristic to note: when vSphere HA is enabled and workload VMs restart on a new recovery host after a failure, all flows from those HA-impacted VMs are reinspected by the Distributed Firewall because vDefend cannot migrate Flow Table contents during host recovery. Policy enforcement applies to these VMs immediately upon restart on the recovery host.
-These failover capabilities help vDefend's security enforcement layer remain operational during infrastructure failures. Network security policy enforcement, threat detection, and microsegmentation continue to function as the underlying compute and storage infrastructure undergoes failover events.</t>
+          <t>VMware vDefend includes high availability and failover capabilities for its own security services, helping maintain network security enforcement during site failures and infrastructure disruptions.
+Security Services Platform (SSP), which hosts vDefend's centralized security functions including Security Intelligence, Network Detection and Response, and Malware Prevention, has high availability capabilities enabled by default. For production deployments, a minimum of three controller nodes and four worker nodes is required. Enabling vSphere HA on the cluster hosting SSP is recommended; when vSphere HA is configured and a host becomes unhealthy, it migrates the affected virtual machines to healthy hosts in the cluster. Admission Control should be configured with sufficient resources for recovery operations. SSP's internal infrastructure runs distributed instances of MinIO for object storage and Kafka for event streaming, providing in-cluster redundancy for the analytics pipeline.
+In vSAN stretched cluster configurations, SSP replicates data across two physically distinct sites to maintain continuity during a site failure. A vSAN stretched cluster allows a single cluster to span two physically distinct sites and requires a minimum of two sites, each with a high-bandwidth or low-latency inter-site link for effective data replication, along with a witness host to resolve network partition conflicts. Control plane and worker node VMs are distributed across primary and secondary VM groups aligned to their respective sites. Stretched configurations also protect data from multiple host failures within a single site.
+The vDefend gateway firewall supports primary-passive and secondary-active high availability modes with non-preemptive failover. When the active gateway node fails, the standby assumes the active role and continues enforcing gateway firewall policies. Edge node failover is triggered when all uplink routing links are down on the active node; the new active Edge node takes over all existing flows because flows are synchronized between both nodes, preserving connection state through the transition.
+The vDefend distributed firewall enforces security policy at the vNIC level on every ESX host and is inherently distributed, with no single point of failure for policy enforcement. Each host maintains its own firewall rules and continues enforcing them independently even if management plane connectivity is temporarily lost. This distributed architecture means that when host-level failover occurs through vSphere HA, Distributed Firewall policy enforcement continues on surviving hosts. One operational characteristic to note: when VMs are restarted on a recovery host, the Distributed Firewall reinspects all flows from those VMs because Flow Table contents cannot be moved during host recovery. Policy enforcement is continuous, but established session state is not carried over across host failovers.
+SSP supports backup and restore functionality, allowing recovery of a platform instance to its previous configuration when the current instance is in a non-recoverable state. Administrators should back up SSP before maintenance operations such as scale-out.
+When VCF infrastructure is configured for cross-site failover, vDefend's security enforcement survives the failover along with the workloads it protects, maintaining network security posture at the secondary site.</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -8276,12 +8080,12 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) implements site-level failover capabilities to maintain availability of critical virtual machine workloads after a disruption.
-Recovery plans automate the failover process between protected and recovery sites. During disaster recovery failover, if an error occurs on the protected site, the failover continues without interruption, prioritizing workload recovery. Recovery plans support both planned migration for orderly, scheduled failover and disaster recovery for unplanned site failures. PNR provides an API workflow through the VCF Operations Orchestrator Plug-In for PNR to initiate failover programmatically, enabling integration with automated orchestration frameworks.
-PNR supports multiple replication methods that underpin the failover capability. vSphere Replication provides host-based replication with configurable recovery point objectives. A recovery option allows vSphere Replication to synchronize recent changes from the source site to the target before recovering virtual machines, reducing data loss during recovery operations. vSphere Replication supports up to 200 recovery points when using the Latest instances option, enabling selection of a specific point in time for recovery. Replication continues at the defined recovery point objective after vSphere High Availability restarts a virtual machine. Array-based replication leverages storage vendor capabilities for datastore-level failover, with a configurable option to wait for device rediscovery after failover. Automated failback is supported only for array-based replication. Virtual Volumes policy-driven replication provides a third replication method.
-Failover and failback can be performed independently on sites, allowing isolated recovery operations without affecting other recovery sites. For stretched storage environments, PNR requires that the failover command isolate devices at the recovery site. IP customization is applied during the failover process, supporting DHCP, static IPv4, and IPv6 addressing so that recovered virtual machines are reachable on the recovery site network. Inventory mappings translate protected site resources to their recovery site equivalents.
-PNR supports failover even when operating in degraded mode, though test failover and reprotect operations are not available in that state. Test failover allows organizations to validate their failover procedures without disrupting production replication. After a successful failover, the reprotect process reverses the direction of protection, making the recovery site the new protected site and restoring replication to prepare for failback.
-PNR supports failover for Windows Server Failover Clustering (WSFC) workloads. The Cyber Recovery capability enables scheduled snapshot management through vSAN Data Protection groups for VM-level protection that integrates with the broader failover workflow.</t>
+          <t>VCF Protection and Recovery (PNR) is the product that provides geographically separate failover capabilities for virtual infrastructure within VCF environments. PNR orchestrates both planned migration and disaster recovery failover between a protected site and a non-collocated recovery site. Single-fleet, single-instance deployment configurations are documented as appropriate only for testing and evaluation where reduced resilience to disaster events is acceptable, not for production disaster recovery.
+PNR supports multiple replication methods to maintain synchronized data between sites. vSphere Replication provides individual virtual machine replication and supports up to 200 point-in-time recovery instances using the Latest instances option; these instances are presented as standard snapshots on the recovered virtual machine, allowing administrators to choose a specific recovery point. Recovery point objective configuration balances storage consumption against snapshot consolidation time after recovery and should be set to the lowest value that satisfies business requirements. Array-based replication is also supported and enables automated failback.
+vSphere Replication provides an option to synchronize recent changes from the source site to the target site before recovering a virtual machine, which reduces data loss during the recovery operation. If an error occurs on the protected site during recovery plan execution, PNR's disaster recovery failover continues without failing, allowing recovery operations to proceed even when the primary site is experiencing disruptions. Recovery plans automate the failover sequence, including virtual machine power-on ordering and dependency sequencing.
+For stretched storage configurations, PNR's failover command isolates devices at the recovery site to prevent file lock conflicts during virtual machine failover. Failover and failback can be performed independently on each site, allowing isolated recovery operations without affecting other recovery sites. After failover, PNR reverses the roles of the recovery and protected sites to enable reprotection and restoration of bidirectional protection.
+PNR includes a VCF Operations orchestrator plug-in that provides API workflows to initiate failover to a recovery site, enabling integration with broader automation frameworks.
+vSphere Replication is compatible with vSphere High Availability; replication continues at the defined recovery point objective after HA restarts a virtual machine, providing an additional layer of within-site resilience. Recovery capabilities can be validated through non-disruptive test failover before an actual disaster event.</t>
         </is>
       </c>
       <c r="K93" s="10" t="inlineStr">
@@ -8291,12 +8095,13 @@
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides built-in high availability and failover mechanisms for PostgreSQL, MySQL, and SQL Server database workloads through two HA topologies that organizations can select based on their availability requirements.
-The Single vSphere Cluster HA topology co-locates all database nodes within one vSphere cluster. For PostgreSQL, DSM deploys a primary instance, one database-level synchronous replica, and a dedicated monitor node. The monitor node orchestrates automatic database-level failover: when the primary fails, the monitor detects the failure and promotes the synchronous streaming replica to the primary role without requiring manual intervention. MySQL under this topology uses a three-node configuration with a single primary and two database-level synchronous replicas sharing the same cluster. SQL Server uses a three-node configuration with Microsoft Always On availability groups, two synchronous replicas, and one configuration-only replica. After a SQL Server failover, the new primary maintains the security and management configurations from the previous primary instance. In all cases, DSM database nodes also rely on the underlying VCF platform for VM-level recovery through vSphere HA and Distributed Resource Scheduler, and on platform storage redundancy.
-The Cross vSphere Cluster HA topology distributes database nodes across three separate vSphere clusters, reducing the blast radius of a single cluster failure. For PostgreSQL, this topology places a primary, a database-level replica, and a monitor on distinct clusters. For MySQL, a primary, a replica, and a monitor are distributed across three clusters. For SQL Server, Always On availability groups are configured with two synchronous replicas and one configuration-only replica, with each replica node in a separate vSphere cluster. Cross vSphere Cluster HA provides the highest availability and resilience for environments that require high availability across multiple failure domains. When configuring Cross-Cluster HA in an infrastructure policy, three clusters must be selected from the same datacenter and must share the same storage policies and distributed port group. The Enable-Cross-Cluster-HA infrastructure policy setting activates this topology. DSM raises a compliance alert if vSphere HA is not active on a cluster referenced by an infrastructure policy.
-The DSM Provider Appliance management plane also relies on vSphere High Availability so the control plane can recover from a host failure without manual intervention.
-For cross-site disaster recovery, DSM supports a multi-site deployment model for PostgreSQL that replicates data to a secondary site. When a failover to the secondary site is needed, DSM provides a switchover workflow to promote the secondary instance to the primary role. After the original site recovers, a failback switchover reverses the roles to restore the original topology. DSM also provides the ability to copy replication user connection strings from a primary instance so that secondary instances can be redirected to the new primary during failover operations. One documented limitation applies: PostgreSQL logical replication requires manual intervention to resume replication after the source cluster experiences a failover. When a MySQL HA cluster is used as the replication source, automatic source failover for read replicas requires the allocation of additional IP addresses from the IP pool for each HA node, and read replicas reconnect to another cluster member after several failed attempts, which can take a few minutes before the switch completes. For SQL Server, during a failover new writes are not protected with a second copy until the failed node rejoins the cluster.
-DSM HA clusters require automated backups to be enabled in order to provision databases. DSM provides real-time alerts for resource and connectivity issues together with continuous performance monitoring, which supports operators in detecting conditions that may require a failover response. Webhook notifications can also be configured so that external systems are alerted on data service operation failures.</t>
+          <t>VMware Data Services Manager (DSM) provides database replication and high availability topologies that contribute to maintaining a redundant secondary system, though the full requirement for a non-collocated, activatable failover capability also depends on how administrators plan and deploy the underlying infrastructure.
+DSM offers two high availability topologies for managed databases. The Single vSphere Cluster HA topology deploys a primary database, a synchronous database-level replica, and a monitor node within a single vSphere cluster, with database nodes protected through vSphere HA, Distributed Resource Scheduler, and underlying storage redundancy. The monitor node orchestrates automatic failover so that a replica is promoted without manual intervention when the primary fails. DSM requires vSphere HA to be active on VMware vCenter (vCenter) clusters as a condition of infrastructure policy compliance, and the documentation specifies that vSphere HA and DRS should be enabled on all clusters used in infrastructure policies.
+The Cross vSphere Cluster HA topology distributes database nodes across three separate vSphere clusters. For PostgreSQL, this places the primary, database-level replica, and monitor across three distinct clusters. For MySQL, the primary and two database-level synchronous replicas are distributed across three clusters. This topology provides resilience against the failure of any single vSphere cluster and is the highest-availability configuration available within a DSM deployment.
+DSM adds SQL Server cluster support, with three-node High Availability configurations that use Microsoft Always On availability groups for data redundancy and automatic failover. Both Single vSphere Cluster HA and Cross vSphere Cluster HA topologies are available for SQL Server, configured with two synchronous replicas and one configuration-only replica. In the Cross vSphere Cluster HA topology for SQL Server, each replica node runs in a separate vSphere cluster. After a SQL Server failover, the new primary instance maintains the security and management configurations from the previous primary. HA clusters require automated backups to be enabled in order to provision databases.
+For geographically distributed disaster recovery, DSM supports a multi-site deployment model for PostgreSQL. A secondary PostgreSQL instance at a separate site maintains continuous replication from the primary, and administrators can promote the secondary to primary status using DSM's switchover workflow; the promoted instance becomes a standalone primary with independent read and write capabilities. DSM also provides a failback workflow to reverse the roles of primary and secondary instances once the original site is restored, and a demoted primary can rejoin the topology as a read-only secondary. DSM also integrates with VCF Automation as a tenant, allowing PostgreSQL and MySQL databases with high availability topologies to be created and cloned through VCF Automation self-service workflows.
+Several limitations apply to these failover capabilities. The Single vSphere Cluster HA topology keeps all nodes within the same availability zone and does not address geographic non-colocation on its own. The Single Server topology has no secondary instance to take over and experiences brief downtime during maintenance operations and updates. During a SQL Server failover, the system does not protect new writes with a second copy until the failed node rejoins the cluster. If a secondary PostgreSQL instance was created using the Consumption Operator, manual trust establishment between the primary and secondary instances is required for multi-site disaster recovery.
+To satisfy this control, organizations must make architectural decisions about the physical location of secondary vSphere clusters or multi-site secondary instances so that they are genuinely not collocated with the primary. DSM provides the technical framework for synchronous replication, automatic promotion within a cluster, and manual switchover across sites. The organizational process for selecting, configuring, and testing the secondary site, and for coordinating a failover when needed, remains an administrative responsibility.</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
@@ -8459,6 +8264,94 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
+          <t>VCF Protection and Recovery (PNR) builds its disaster recovery model on the separation of protected and recovery sites. In a typical installation, the protected site provides business-critical datacenter services and the recovery site is an alternative infrastructure to which PNR can migrate these services. This two-site architecture supports the operational separation between distinct environments needed to reduce susceptibility to threats that affect a single location. The placement of the recovery site at a physically separate facility is an organizational decision that PNR documentation recommends rather than enforces, with guidance that recovery sites be located in a facility unlikely to be affected by the same environmental, infrastructure, or other disturbances as the protected site.
+PNR supports logical isolation between sites at the storage layer. Array-based replication can be configured with two separate storage arrays for two PNR instances to achieve full logical isolation. Host-based replication operates independently of the storage array, so the two sites do not share storage failure domains.
+Bidirectional protection configurations reinforce operational independence: each site can serve as the recovery site for the other's workloads, and each site must include at least one datacenter for protection and recovery. Each site maintains its own infrastructure and can function as an alternate processing environment.
+PNR supports topologies where the same VM is protected to two different sites simultaneously, enabling physical isolation of the disaster recovery site from the clean room site when an organization wants dedicated environments for different recovery scenarios.
+Network isolation between sites is supported through isolated test networks during recovery plan exercises, separating test operations from production networks at each site.
+In shared recovery site configurations, PNR implements resource isolation to enforce separation between different organizations' virtual machines. Each organization's protected site resources are mapped to dedicated datacenters, networks, folders, and datastores on the shared recovery site, and the service controller manages multi-tenant isolation across protection components. Virtual machines belonging to different customer organizations should be kept separate from each other.
+The Cyber Recovery feature provides a clean room as an additional separation model for ransomware recovery. The clean room is configured with dedicated compute resources and isolated networks. PNR supports VCF deployment topologies for cyber recovery where the workload domain is isolated from the management domain, providing strict separation between management and user workloads in the clean room environment. Private connections between production environments and the clean room should be avoided to preserve isolation.
+For VCF Automation deployments, PNR supports a topology with separate management domains for each region, designed to contain the impact of a disaster event to a single region. PNR deployments can span multiple cloud regions and include both on-premises and cloud-based site pairs.
+PNR detects split-brain scenarios where production virtual machines are running on both the protected site and recovery site after the protected site comes back online following disaster recovery.</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M95" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>12.5(b)</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>BCD-09</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>The site shall be capable of ensuring the continuity of critical or important functions identically to the primary site, or providing the necessary service level within the recovery objectives.</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides several infrastructure capabilities that support the establishment and operation of alternate processing sites with consistent security and operational controls, though the organizational decisions around site selection, physical facility provisioning, and operational procedures fall outside the platform's scope.
+VCF supports stretched compute clusters across two geographically separated sites. This architecture allows workloads to run across both locations simultaneously, providing a foundation for alternate site processing. Administrators configure a stretched compute cluster when hosts are available at two sites, with hosts placed in separate sites. Both availability zones must contain an equal number of hosts to allow failover if either zone goes down. vSAN stretched clusters extend a single logical cluster across the two sites, with data mirrored between them. When the site disaster tolerance storage policy is configured for site mirroring, the cluster can tolerate a complete site failure while keeping data accessible. A witness host provides quorum for split-brain scenarios when one site becomes unavailable.
+For workload mobility between sites, VCF Operations HCX provides bi-directional migration technologies that move virtual machines between data centers. Workloads can be migrated between private and public cloud sites depending on the deployment model. HCX establishes site pairs where both the source and destination sites work together to provide migration and network extension services, and the destination site can also act as the source of a site pair in bi-directional installations. This allows flexible failover and failback workflows. The HCX Compute Profile configuration with a dedicated Deployment Cluster provides control over site-to-site migration egress traffic, and administrators can customize services between paired sites through the Compute Profile. VMware vMotion provides live migration of powered-on virtual machines to new hosts without service interruption, supporting workload redistribution within and between sites.
+NSX Federation provides centralized network configuration across multiple locations. A Global Manager component manages multiple locations, propagating configurations to Local Managers at each site while allowing overrides at individual locations when needed. Active and Standby Global Manager clusters at separate locations synchronize network configuration across sites. In a disaster recovery deployment, NSX at the primary site handles networking for the enterprise, and the secondary site stands by to take over if a catastrophic failure occurs at the primary site. NSX Federation supports recovery of stretched tier-0 and tier-1 gateways to a secondary site using a network recovery workflow. NSX Edge Availability Zone fault-tolerant configurations provide fast network failover across availability zones with no dependency on the physical fabric.
+To help maintain consistent security posture across multiple sites, VCF Operations supports single-source configuration for identity and access management across VCF components and multiple geolocations. This capability allows organizations to apply uniform authentication and authorization policies at both primary and alternate sites, reducing the risk of configuration drift between locations. The VCF security baseline can be applied to both default and non-default configurations at any site, helping organizations maintain equivalent security measures across deployments. VCF Operations also includes compliance and security dashboard capabilities that surface core aspects of VCF security in a centralized view. These tools can be used to monitor and compare the security posture of primary and alternate sites, helping administrators identify discrepancies in configuration or policy enforcement. vSphere Host Profiles allow administrators to capture a reference host's configuration, including storage, networking, and security settings, and apply it consistently to all hosts across both sites, so that any drift from the security baseline can be detected and remediated.
+vSphere HA with admission control policies helps ensure that clusters have sufficient resources to recover virtual machines when a host fails. For vSAN stretched clusters, admission control should be configured with CPU and memory reservations set to 50% each, reserving capacity at each site to accommodate workload restart during a site failure. Network redundancy through NIC teaming and LACP load balancing provides resilient connectivity at both sites.
+VCF provides the infrastructure capabilities for running workloads at alternate sites with consistent security configurations and automated failover, but establishing the physical alternate processing facility, selecting the site, and defining the associated operational agreements remain organizational responsibilities.</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend (DFW) with Federation supports scoping security and network policies across multiple locations using Security Services Platform (SSP) region-based grouping. In a multi-site deployment, SSP regions can be associated with Security and Network policies to control policy scope across those locations, and each location can belong to one customized region. This allows consistent DFW policy enforcement at both primary and alternate processing sites as workloads operate or migrate across them.
+When SSP flow processing capacity at a site is insufficient, administrators can scale out worker nodes based on available storage capacity, or add control plane and worker node resources to the deployment, supporting capacity planning for alternate site configurations. These mechanisms allow the vDefend network security layer to be sized appropriately at the alternate site so that distributed firewall, IDS/IPS, and related enforcement operate with equivalent policy coverage.
+vDefend contributes the network security policy layer for alternate site scenarios. Broader alternate site infrastructure provisioning, data replication, physical facility requirements, and the organizational governance needed to establish a fully equivalent alternate processing site fall outside vDefend's scope.</t>
+        </is>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
           <t>VCF Protection and Recovery (PNR) provides the orchestration platform for establishing and operating an alternate processing site for disaster recovery. In a typical PNR installation, the protected site provides business-critical datacenter services and the recovery site is an alternative infrastructure to which PNR can migrate these services. The Protection and Recovery Appliance must be deployed on both the primary site and the recovery site to enable replication and recovery capabilities.
 PNR supports both planned migration and unplanned disaster recovery to the alternate processing site. Planned migration validates orderly workload evacuation between sites. Disaster recovery handles unplanned site failures by starting protected virtual machines at the recovery site. After a disaster recovery operation, a planned migration must be executed when both sites are running again to re-establish the normal operational state.
 Bidirectional protection allows each site to serve as both a protected and recovery location for different sets of virtual machines, so both sites operate as fully capable processing environments. Each site must have at least one datacenter configured for protection and recovery. Placeholder datastores must be configured on both sites to support planned migration and reprotect workflows, reinforcing the requirement for equivalent storage infrastructure at the alternate site.
@@ -8468,162 +8361,77 @@
 The security measures at the alternate site, including equivalent network policies, access controls, and security baselines, are provided by the underlying VCF platform infrastructure at each site. PNR provides the workload migration and recovery orchestration that operates within those environments.</t>
         </is>
       </c>
-      <c r="K95" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L95" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M95" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N95" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>12.5(b)</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>BCD-09</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>The site shall be capable of ensuring the continuity of critical or important functions identically to the primary site, or providing the necessary service level within the recovery objectives.</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides several infrastructure capabilities that support the establishment and operation of alternate processing sites with consistent security and operational controls, though the organizational decisions around site selection, physical facility provisioning, and operational procedures fall outside the platform's scope.
-VCF supports stretched compute clusters across two geographically separated sites. This architecture allows workloads to run across both locations simultaneously, providing a foundation for alternate site processing. Administrators configure a stretched compute cluster when hosts are available at two sites, with hosts placed in separate sites. Both availability zones must contain an equal number of hosts to allow failover if either zone goes down. vSAN stretched clusters extend a single logical cluster across the two sites, with data mirrored between them. When the site disaster tolerance storage policy is configured for site mirroring, the cluster can tolerate a complete site failure while keeping data accessible. A witness host provides quorum for split-brain scenarios when one site becomes unavailable.
-For workload mobility between sites, VCF Operations HCX provides bi-directional migration technologies that move virtual machines between data centers. Workloads can be migrated between private and public cloud sites depending on the deployment model. HCX establishes site pairs where both the source and destination sites work together to provide migration and network extension services, and the destination site can also act as the source of a site pair in bi-directional installations. This allows flexible failover and failback workflows. The HCX Compute Profile configuration with a dedicated Deployment Cluster provides control over site-to-site migration egress traffic, and administrators can customize services between paired sites through the Compute Profile. VMware vMotion provides live migration of powered-on virtual machines to new hosts without service interruption, supporting workload redistribution within and between sites.
-NSX Federation provides centralized network configuration across multiple locations. A Global Manager component manages multiple locations, propagating configurations to Local Managers at each site while allowing overrides at individual locations when needed. Active and Standby Global Manager clusters at separate locations synchronize network configuration across sites. In a disaster recovery deployment, NSX at the primary site handles networking for the enterprise, and the secondary site stands by to take over if a catastrophic failure occurs at the primary site. NSX Federation supports recovery of stretched tier-0 and tier-1 gateways to a secondary site using a network recovery workflow. NSX Edge Availability Zone fault-tolerant configurations provide fast network failover across availability zones with no dependency on the physical fabric.
-To help maintain consistent security posture across multiple sites, VCF Operations supports single-source configuration for identity and access management across VCF components and multiple geolocations. This capability allows organizations to apply uniform authentication and authorization policies at both primary and alternate sites, reducing the risk of configuration drift between locations. The VCF security baseline can be applied to both default and non-default configurations at any site, helping organizations maintain equivalent security measures across deployments. VCF Operations also includes compliance and security dashboard capabilities that surface core aspects of VCF security in a centralized view. These tools can be used to monitor and compare the security posture of primary and alternate sites, helping administrators identify discrepancies in configuration or policy enforcement. vSphere Host Profiles allow administrators to capture a reference host's configuration, including storage, networking, and security settings, and apply it consistently to all hosts across both sites, so that any drift from the security baseline can be detected and remediated.
-vSphere HA with admission control policies helps ensure that clusters have sufficient resources to recover virtual machines when a host fails. For vSAN stretched clusters, admission control should be configured with CPU and memory reservations set to 50% each, reserving capacity at each site to accommodate workload restart during a site failure. Network redundancy through NIC teaming and LACP load balancing provides resilient connectivity at both sites.
-VCF provides the infrastructure capabilities for running workloads at alternate sites with consistent security configurations and automated failover, but establishing the physical alternate processing facility, selecting the site, and defining the associated operational agreements remain organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="K96" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>12.5(c)</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>BCD-09, BCD-09.2</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>The site shall be immediately accessible to the financial entity's staff.</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides several technical capabilities that support alternate processing site accessibility planning, though the organizational processes of identifying physical site risks, selecting alternate locations, and developing mitigation plans remain outside the platform's scope.
+VCF includes application disaster recovery functionality that enables failover to a secondary site to maintain operations during major disruptions. This capability allows workloads to be redirected to an alternate processing location when the primary site becomes unavailable due to an area-wide event. The platform recommends combining real-time high availability with sitewide disaster recovery for maximum resilience, which directly supports maintaining access to alternate processing resources during extended outages. Disaster recovery may also be implemented for fleet-level components, extending protection beyond individual workloads to the management infrastructure itself. For large clusters, VCF documentation recommends having a disaster recovery plan in place, as an unexpected cluster-wide outage can impact many virtual machines simultaneously.
+For environments requiring continuous availability across geographically separated locations, vSAN stretched clusters provide site-level disaster tolerance. A vSAN stretched cluster consists of two data sites and a witness host, with ESX hosts distributed evenly between sites. Each site resides in a separate fault domain, and the site disaster tolerance storage policy rule can be set to site mirroring so that data remains accessible even when one entire site fails. Stretched clusters require independent routing and connectivity between the data sites and the witness host. When a site goes down or loses network connectivity, the surviving site can continue to serve workloads and perform component repairs locally. If one site goes down due to maintenance or failure and the witness host also fails, objects become non-compliant but remain accessible at the surviving site, preserving workload availability during partial failures. Administrators should be aware that selecting the "Ensure accessibility" evacuation mode does not reprotect data during failure, and unexpected data loss may occur under certain conditions. vSAN monitors connectivity between sites and provides monitoring capabilities that allow administrators to examine cluster performance and virtual machine accessibility to diagnose problems. This visibility into object accessibility status helps identify when workloads may be at risk and supports proactive mitigation before a full site failure occurs.
+VCF supports distributing compute resources across different fault domains, which helps manage workload placement during site failure. This fault domain architecture allows administrators to map infrastructure to physical locations, making the relationship between compute resources and site accessibility visible and manageable.
+NSX supports multisite networking deployments where a secondary site stands by to take over if a catastrophic failure occurs at the primary site. NSX Federation allows stretched tier-0 and tier-1 gateways to be moved between sites using a network recovery workflow, maintaining network connectivity for recovered workloads. This networking layer is important for alternate site accessibility because workloads recovered at a secondary site need functioning network paths to remain reachable.
+VCF Operations HCX provides workload mobility capabilities, supporting migrations between sites through Mobility Groups. The Migration interface allows administrators to select sets of virtual machines, configure transfer and placement, and monitor migration progress and history. This supports planned migrations to alternate processing sites and can assist with workload redistribution during disruption scenarios.
+VCF Operations offers what-if analysis that can model workload planning scenarios for capacity changes, including traditional and hyperconverged deployments. By committing a scenario, administrators can determine capacity requirements before implementing actual changes. Saved scenarios can be edited and run again cumulatively, providing an iterative planning capability. This helps identify potential accessibility problems at recovery sites before a disruption occurs, such as whether the alternate site has sufficient compute, memory, and storage resources to absorb relocated workloads.
+VCF provides monitoring, multi-site architecture, workload mobility, and capacity planning tools that collectively help identify and mitigate accessibility problems at alternate processing sites. However, the organizational activities of site risk assessment, alternate site selection, physical accessibility evaluation, and mitigation plan development require processes and decision-making that fall outside VCF's scope.</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend (DFW) with Federation supports scoping security and network policies across multiple locations using Security Services Platform (SSP) region-based grouping. In a multi-site deployment, SSP regions can be associated with Security and Network policies to control policy scope across those locations, and each location can belong to one customized region. This allows consistent DFW policy enforcement at both primary and alternate processing sites as workloads operate or migrate across them.
 When SSP flow processing capacity at a site is insufficient, administrators can scale out worker nodes based on available storage capacity, or add control plane and worker node resources to the deployment, supporting capacity planning for alternate site configurations. These mechanisms allow the vDefend network security layer to be sized appropriately at the alternate site so that distributed firewall, IDS/IPS, and related enforcement operate with equivalent policy coverage.
 vDefend contributes the network security policy layer for alternate site scenarios. Broader alternate site infrastructure provisioning, data replication, physical facility requirements, and the organizational governance needed to establish a fully equivalent alternate processing site fall outside vDefend's scope.</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J96" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides the orchestration platform for establishing and operating an alternate processing site for disaster recovery. In a typical PNR installation, the protected site provides business-critical datacenter services and the recovery site is an alternative infrastructure to which PNR can migrate these services. The Protection and Recovery Appliance must be deployed on both the primary site and the recovery site to enable replication and recovery capabilities.
-PNR supports both planned migration and unplanned disaster recovery to the alternate processing site. Planned migration validates orderly workload evacuation between sites. Disaster recovery handles unplanned site failures by starting protected virtual machines at the recovery site. After a disaster recovery operation, a planned migration must be executed when both sites are running again to re-establish the normal operational state.
-Bidirectional protection allows each site to serve as both a protected and recovery location for different sets of virtual machines, so both sites operate as fully capable processing environments. Each site must have at least one datacenter configured for protection and recovery. Placeholder datastores must be configured on both sites to support planned migration and reprotect workflows, reinforcing the requirement for equivalent storage infrastructure at the alternate site.
-vSphere Replication maintains current copies of protected workloads at the alternate site through continuous host-based replication. In a typical vSphere Replication installation, the local site provides business-critical datacenter services and the remote site is an alternative facility to which services can be migrated.
-PNR supports shared recovery site configurations where multiple protected sites share a single recovery site, with concurrent recoveries from multiple sites supported simultaneously.
-In PNR, the VCF Operations orchestrator plug-in for Protection and Recovery provides workflow automation for site configuration tasks. The Configure Local Sites workflow validates the PNR connection, imports the site certificate, and registers local sites on both the protected and recovery sites. When both sites are registered as local sites, the plug-in can verify all resource mappings across the site pair, supporting consistent configuration validation.
-The security measures at the alternate site, including equivalent network policies, access controls, and security baselines, are provided by the underlying VCF platform infrastructure at each site. PNR provides the workload migration and recovery orchestration that operates within those environments.</t>
-        </is>
-      </c>
-      <c r="K96" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L96" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M96" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N96" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>12.5(c)</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>BCD-09, BCD-09.2</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>The site shall be immediately accessible to the financial entity's staff.</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides several infrastructure capabilities that support the establishment and operation of alternate processing sites with consistent security and operational controls, though the organizational decisions around site selection, physical facility provisioning, and operational procedures fall outside the platform's scope.
-VCF supports stretched compute clusters across two geographically separated sites. This architecture allows workloads to run across both locations simultaneously, providing a foundation for alternate site processing. Administrators configure a stretched compute cluster when hosts are available at two sites, with hosts placed in separate sites. Both availability zones must contain an equal number of hosts to allow failover if either zone goes down. vSAN stretched clusters extend a single logical cluster across the two sites, with data mirrored between them. When the site disaster tolerance storage policy is configured for site mirroring, the cluster can tolerate a complete site failure while keeping data accessible. A witness host provides quorum for split-brain scenarios when one site becomes unavailable.
-For workload mobility between sites, VCF Operations HCX provides bi-directional migration technologies that move virtual machines between data centers. Workloads can be migrated between private and public cloud sites depending on the deployment model. HCX establishes site pairs where both the source and destination sites work together to provide migration and network extension services, and the destination site can also act as the source of a site pair in bi-directional installations. This allows flexible failover and failback workflows. The HCX Compute Profile configuration with a dedicated Deployment Cluster provides control over site-to-site migration egress traffic, and administrators can customize services between paired sites through the Compute Profile. VMware vMotion provides live migration of powered-on virtual machines to new hosts without service interruption, supporting workload redistribution within and between sites.
-NSX Federation provides centralized network configuration across multiple locations. A Global Manager component manages multiple locations, propagating configurations to Local Managers at each site while allowing overrides at individual locations when needed. Active and Standby Global Manager clusters at separate locations synchronize network configuration across sites. In a disaster recovery deployment, NSX at the primary site handles networking for the enterprise, and the secondary site stands by to take over if a catastrophic failure occurs at the primary site. NSX Federation supports recovery of stretched tier-0 and tier-1 gateways to a secondary site using a network recovery workflow. NSX Edge Availability Zone fault-tolerant configurations provide fast network failover across availability zones with no dependency on the physical fabric.
-To help maintain consistent security posture across multiple sites, VCF Operations supports single-source configuration for identity and access management across VCF components and multiple geolocations. This capability allows organizations to apply uniform authentication and authorization policies at both primary and alternate sites, reducing the risk of configuration drift between locations. The VCF security baseline can be applied to both default and non-default configurations at any site, helping organizations maintain equivalent security measures across deployments. VCF Operations also includes compliance and security dashboard capabilities that surface core aspects of VCF security in a centralized view. These tools can be used to monitor and compare the security posture of primary and alternate sites, helping administrators identify discrepancies in configuration or policy enforcement. vSphere Host Profiles allow administrators to capture a reference host's configuration, including storage, networking, and security settings, and apply it consistently to all hosts across both sites, so that any drift from the security baseline can be detected and remediated.
-vSphere HA with admission control policies helps ensure that clusters have sufficient resources to recover virtual machines when a host fails. For vSAN stretched clusters, admission control should be configured with CPU and memory reservations set to 50% each, reserving capacity at each site to accommodate workload restart during a site failure. Network redundancy through NIC teaming and LACP load balancing provides resilient connectivity at both sites.
-VCF provides the infrastructure capabilities for running workloads at alternate sites with consistent security configurations and automated failover, but establishing the physical alternate processing facility, selecting the site, and defining the associated operational agreements remain organizational responsibilities.</t>
-        </is>
-      </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (DFW) with Federation supports scoping security and network policies across multiple locations using Security Services Platform (SSP) region-based grouping. In a multi-site deployment, SSP regions can be associated with Security and Network policies to control policy scope across those locations, and each location can belong to one customized region. This allows consistent DFW policy enforcement at both primary and alternate processing sites as workloads operate or migrate across them.
-When SSP flow processing capacity at a site is insufficient, administrators can scale out worker nodes based on available storage capacity, or add control plane and worker node resources to the deployment, supporting capacity planning for alternate site configurations. These mechanisms allow the vDefend network security layer to be sized appropriately at the alternate site so that distributed firewall, IDS/IPS, and related enforcement operate with equivalent policy coverage.
-vDefend contributes the network security policy layer for alternate site scenarios. Broader alternate site infrastructure provisioning, data replication, physical facility requirements, and the organizational governance needed to establish a fully equivalent alternate processing site fall outside vDefend's scope.</t>
-        </is>
-      </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
           <t>Contributes</t>
@@ -8631,13 +8439,11 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the orchestration platform for establishing and operating an alternate processing site for disaster recovery. In a typical PNR installation, the protected site provides business-critical datacenter services and the recovery site is an alternative infrastructure to which PNR can migrate these services. The Protection and Recovery Appliance must be deployed on both the primary site and the recovery site to enable replication and recovery capabilities.
-PNR supports both planned migration and unplanned disaster recovery to the alternate processing site. Planned migration validates orderly workload evacuation between sites. Disaster recovery handles unplanned site failures by starting protected virtual machines at the recovery site. After a disaster recovery operation, a planned migration must be executed when both sites are running again to re-establish the normal operational state.
-Bidirectional protection allows each site to serve as both a protected and recovery location for different sets of virtual machines, so both sites operate as fully capable processing environments. Each site must have at least one datacenter configured for protection and recovery. Placeholder datastores must be configured on both sites to support planned migration and reprotect workflows, reinforcing the requirement for equivalent storage infrastructure at the alternate site.
-vSphere Replication maintains current copies of protected workloads at the alternate site through continuous host-based replication. In a typical vSphere Replication installation, the local site provides business-critical datacenter services and the remote site is an alternative facility to which services can be migrated.
-PNR supports shared recovery site configurations where multiple protected sites share a single recovery site, with concurrent recoveries from multiple sites supported simultaneously.
-In PNR, the VCF Operations orchestrator plug-in for Protection and Recovery provides workflow automation for site configuration tasks. The Configure Local Sites workflow validates the PNR connection, imports the site certificate, and registers local sites on both the protected and recovery sites. When both sites are registered as local sites, the plug-in can verify all resource mappings across the site pair, supporting consistent configuration validation.
-The security measures at the alternate site, including equivalent network policies, access controls, and security baselines, are provided by the underlying VCF platform infrastructure at each site. PNR provides the workload migration and recovery orchestration that operates within those environments.</t>
+          <t>VCF Protection and Recovery (PNR) provides mechanisms that help identify and mitigate accessibility problems at the alternate processing site before and during area-wide disruptions.
+PNR supports recovery plan execution under both planned and unplanned circumstances. Planned migration exercises let organizations validate that the recovery site is accessible and replication infrastructure is functioning before an actual disruption occurs. Recovery plans can be configured with different steps for emergency scenarios versus planned migration of services from one site to another, allowing administrators to account for the distinct operational conditions of each. When the protected site goes offline unexpectedly during disaster recovery operations, failures on the protected site are reported but otherwise ignored, allowing recovery to proceed without requiring both sites to be simultaneously available. PNR documentation also acknowledges that connectivity between sites can be lost, preventing status determination; administrators should account for this when designing recovery procedures.
+PNR's multi-region topology design addresses area-wide disruption containment. Deploying with separate management domains for each region is designed to contain the impact of a disaster event to one particular region. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so users can recover workloads. This cross-domain recovery capability extends accessibility mitigation beyond individual site failover.
+The recovery site must have hardware, network, and storage resources capable of supporting the same virtual machines and workloads as the protected site. PNR documentation states that recovery sites should be located in a facility unlikely to be affected by environmental, infrastructure, or other disturbances that affect the protected site, directly addressing area-wide disruption scenarios. In shared recovery site configurations, users with appropriate permissions must be able to access the site to create, test, and run recovery plans. Advanced configuration options let administrators customize PNR to support a broader range of site recovery requirements beyond the default configuration.
+Broader accessibility planning, including physical network path redundancy, physical site selection, and capacity modeling for large-scale disruption scenarios, is provided by the underlying VCF platform or remains an organizational planning responsibility.</t>
         </is>
       </c>
       <c r="K97" s="10" t="inlineStr">
@@ -8690,7 +8496,7 @@
       <c r="F98" s="10" t="inlineStr">
         <is>
           <t>VCF provides multiple recovery technologies with configurable Recovery Time Objective (RTO) and Recovery Point Objective (RPO) settings, enabling organizations to align disaster recovery operations with their specific continuity requirements.
-VCF natively provides vSphere Replication, which allows administrators to configure RPO targets, enable network compression, enable multiple point-in-time (MPIT) instances with configurable retention periods, and control automatic replication of new disks. For lower recovery point objectives and orchestrated site failover, Live Site Recovery, part of VMware Live Recovery and licensed separately within the Protection and Recovery portfolio, supports replication with an RPO as low as 60 seconds. These granular settings allow recovery configurations to be tuned to match organizational RTO and RPO requirements for protected workloads. VMware Live Recovery also supports periodic test runs to verify that existing recovery plans function correctly with the underlying infrastructure, allowing organizations to validate that their RTO and RPO targets are realistic and achievable before an actual disruption occurs.
+VCF natively provides vSphere Replication, which allows administrators to configure RPO targets, enable network compression, enable multiple point-in-time (MPIT) instances with configurable retention periods, and control automatic replication of new disks. For lower recovery point objectives and orchestrated site failover, Live Site Recovery, part of VCF Protection and Recovery and licensed separately within the Protection and Recovery portfolio, supports replication with an RPO as low as 60 seconds. These granular settings allow recovery configurations to be tuned to match organizational RTO and RPO requirements for protected workloads. VCF Protection and Recovery also supports periodic test runs to verify that existing recovery plans function correctly with the underlying infrastructure, allowing organizations to validate that their RTO and RPO targets are realistic and achievable before an actual disruption occurs.
 vSAN stretched clusters extend a single logical cluster across two availability zones with synchronous data mirroring between sites. When the site disaster tolerance parameter is set to site mirroring, the cluster can tolerate one site failure and data remains accessible from the surviving site. This architecture provides near-zero RPO for site-level events, since data is written to both sites before acknowledging the write. When a site fails, vSphere HA restarts any virtual machines that require restart on the remaining active site, providing both minimal RPO and RTO for site-level failures.
 vSAN Data Protection provides snapshot-based recovery with configurable retention duration and scheduling intervals. Protection groups define snapshot policies with retention periods and snapshot intervals, giving administrators fine-grained control over recovery point granularity. For example, protection groups can be configured for hourly snapshots with hour-based retention. Snapshots can be replicated to external targets for offsite protection.
 vSphere Replication provides an additional replication mechanism with configurable RPO parameters set through the replication specification. For VCF Operations for Networks deployments, replication can be configured for each node that requires protection, with recommended RPO values varying by deployment size. A medium-size deployment with single platform and collector nodes uses a recommended RPO of 45 minutes.
@@ -9685,15 +9491,1632 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J111" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K111" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M111" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N111" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-02, IRO-07, IRO-10, IRO-11</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall implement communication policies for internal staff and for external stakeholders, differentiating between staff roles (e.g., those involved in response vs. those needing information).</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J112" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K112" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M112" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N112" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-02, IRO-07, IRO-10, IRO-11</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>At least one person in the financial entity shall be tasked with implementing the communication strategy for ICT-related incidents and fulfill the public and media function.</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K113" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L113" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M113" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N113" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>16.1(a)</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall put in place and maintain a sound and documented ICT risk management framework that details the mechanisms and measures aimed at a quick, efficient and comprehensive management of ICT risk.</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J114" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K114" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L114" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M114" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N114" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>16.1(b)</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall continuously monitor the security and functioning of all ICT systems.</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G115" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K115" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L115" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M115" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N115" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>16.1(c)</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall minimize the impact of ICT risk through the use of sound, resilient and updated ICT systems, protocols and tools.</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J116" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K116" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N116" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>16.1(d)</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall allow sources of ICT risk and anomalies to be promptly identified and detected and ICT-related incidents to be swiftly handled.</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K117" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L117" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M117" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>16.1(e)</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall identify key dependencies on ICT third-party service providers.</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>16.1(f)</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall ensure the continuity of critical or important functions, through business continuity plans and response and recovery measures, which include, at least, back-up and restoration measures.</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>16.1(g)</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall test, on a regular basis, the plans and measures referred to in point (f), as well as the effectiveness of the controls.</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>16.1(h)</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Entities shall implement relevant operational conclusions resulting from the tests and post-incident analysis, and develop, according to needs, ICT security awareness programmes and digital operational resilience training for staff and management.</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>GOV-01</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>The simplified ICT risk management framework shall be documented and reviewed periodically and upon the occurrence of major ICT-related incidents, and continuously improved. A report on the review shall be submitted to the competent authority upon request.</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N122" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall define, establish and implement an ICT-related incident management process to detect, manage and notify ICT-related incidents.</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N123" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall record all ICT-related incidents and significant cyber threats, and establish procedures to ensure consistent monitoring, handling, and follow-up to prevent recurrence.</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>The ICT-related incident management process shall:</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>17.3(a)</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Put in place early warning indicators.</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M126" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N126" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>17.3(b)</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Establish procedures to identify, track, log, categorise and classify ICT-related incidents according to their priority, severity, and criticality of services impacted.</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L127" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M127" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N127" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>17.3(c)</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Assign roles and responsibilities that need to be activated for different incident types.</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M128" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>17.3(d)</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Set out plans for communication to staff, external stakeholders, and media, notification to clients, for internal escalation, and provision of information to counterparts.</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L129" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N129" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>17.3(e)</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Ensure that at least major ICT-related incidents are reported to relevant senior management and inform the management body.</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L130" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N130" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>17.3(f)</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>IRO-01, IRO-04</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Establish ICT-related incident response procedures to mitigate impacts and ensure that services become operational and secure in a timely manner.</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L131" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M131" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N131" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>IRO-02</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities shall classify ICT-related incidents and shall determine their impact based on the following criteria:</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E132" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F132" s="10" t="inlineStr">
         <is>
           <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
 For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
@@ -9706,12 +11129,12 @@
 While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
         </is>
       </c>
-      <c r="G111" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
 For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
@@ -9721,12 +11144,12 @@
 Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
         </is>
       </c>
-      <c r="I111" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J111" s="10" t="inlineStr">
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J132" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
 Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
@@ -9735,22 +11158,22 @@
 PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
         </is>
       </c>
-      <c r="K111" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L111" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M111" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N111" s="10" t="inlineStr">
+      <c r="K132" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L132" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M132" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N132" s="10" t="inlineStr">
         <is>
           <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
 For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
@@ -9762,33 +11185,105 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-02, IRO-07, IRO-10, IRO-11</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall implement communication policies for internal staff and for external stakeholders, differentiating between staff roles (e.g., those involved in response vs. those needing information).</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E112" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F112" s="10" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>18.1(a)</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>IRO-02</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>The number and/or relevance of clients or financial counterparts affected, amount/number of transactions affected, and reputational impact.</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L133" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M133" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N133" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>18.1(b)</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>IRO-02</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>The duration of the ICT-related incident, including the service downtime.</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
         <is>
           <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
 For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
@@ -9801,12 +11296,12 @@
 While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
         </is>
       </c>
-      <c r="G112" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H112" s="10" t="inlineStr">
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
 For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
@@ -9816,12 +11311,12 @@
 Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
         </is>
       </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J112" s="10" t="inlineStr">
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J134" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
 Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
@@ -9830,22 +11325,22 @@
 PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
         </is>
       </c>
-      <c r="K112" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L112" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M112" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N112" s="10" t="inlineStr">
+      <c r="K134" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M134" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N134" s="10" t="inlineStr">
         <is>
           <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
 For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
@@ -9857,33 +11352,105 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-02, IRO-07, IRO-10, IRO-11</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>At least one person in the financial entity shall be tasked with implementing the communication strategy for ICT-related incidents and fulfill the public and media function.</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>18.1(c)</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>IRO-02</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>The geographical spread with regard to the areas affected by the ICT-related incident, particularly if it affects more than two Member States.</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K135" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L135" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M135" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N135" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>18.1(d)</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>IRO-02</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>The data losses that the ICT-related incident entails, in relation to availability, authenticity, integrity or confidentiality of data.</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
 For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
@@ -9896,12 +11463,12 @@
 While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
         </is>
       </c>
-      <c r="G113" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H113" s="10" t="inlineStr">
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
 For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
@@ -9911,12 +11478,12 @@
 Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
         </is>
       </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J113" s="10" t="inlineStr">
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
 Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
@@ -9925,22 +11492,22 @@
 PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
         </is>
       </c>
-      <c r="K113" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L113" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M113" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N113" s="10" t="inlineStr">
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L136" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N136" s="10" t="inlineStr">
         <is>
           <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
 For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
@@ -9952,1434 +11519,33 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>16.1(a)</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C114" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall put in place and maintain a sound and documented ICT risk management framework that details the mechanisms and measures aimed at a quick, efficient and comprehensive management of ICT risk.</t>
-        </is>
-      </c>
-      <c r="D114" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E114" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F114" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G114" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H114" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I114" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J114" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K114" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L114" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M114" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N114" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>16.1(b)</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall continuously monitor the security and functioning of all ICT systems.</t>
-        </is>
-      </c>
-      <c r="D115" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G115" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J115" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K115" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L115" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M115" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N115" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>16.1(c)</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall minimize the impact of ICT risk through the use of sound, resilient and updated ICT systems, protocols and tools.</t>
-        </is>
-      </c>
-      <c r="D116" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E116" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G116" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J116" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K116" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L116" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M116" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N116" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>16.1(d)</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall allow sources of ICT risk and anomalies to be promptly identified and detected and ICT-related incidents to be swiftly handled.</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G117" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J117" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K117" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L117" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M117" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N117" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>16.1(e)</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall identify key dependencies on ICT third-party service providers.</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G118" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H118" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J118" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K118" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L118" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M118" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N118" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="10" t="inlineStr">
-        <is>
-          <t>16.1(f)</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall ensure the continuity of critical or important functions, through business continuity plans and response and recovery measures, which include, at least, back-up and restoration measures.</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G119" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H119" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I119" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J119" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K119" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L119" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M119" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N119" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>16.1(g)</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall test, on a regular basis, the plans and measures referred to in point (f), as well as the effectiveness of the controls.</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G120" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H120" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J120" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K120" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L120" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M120" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N120" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="10" t="inlineStr">
-        <is>
-          <t>16.1(h)</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>Entities shall implement relevant operational conclusions resulting from the tests and post-incident analysis, and develop, according to needs, ICT security awareness programmes and digital operational resilience training for staff and management.</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G121" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I121" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J121" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K121" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L121" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M121" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N121" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t>GOV-01</t>
-        </is>
-      </c>
-      <c r="C122" s="10" t="inlineStr">
-        <is>
-          <t>The simplified ICT risk management framework shall be documented and reviewed periodically and upon the occurrence of major ICT-related incidents, and continuously improved. A report on the review shall be submitted to the competent authority upon request.</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E122" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F122" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G122" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H122" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J122" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K122" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L122" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M122" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N122" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall define, establish and implement an ICT-related incident management process to detect, manage and notify ICT-related incidents.</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E123" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F123" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G123" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H123" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J123" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K123" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L123" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M123" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N123" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall record all ICT-related incidents and significant cyber threats, and establish procedures to ensure consistent monitoring, handling, and follow-up to prevent recurrence.</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E124" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F124" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G124" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H124" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I124" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J124" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K124" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L124" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M124" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N124" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="10" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
-        <is>
-          <t>The ICT-related incident management process shall:</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E125" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F125" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G125" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H125" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J125" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K125" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L125" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M125" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N125" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>17.3(a)</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>Put in place early warning indicators.</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E126" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G126" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J126" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K126" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L126" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M126" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N126" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>17.3(b)</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
-        <is>
-          <t>Establish procedures to identify, track, log, categorise and classify ICT-related incidents according to their priority, severity, and criticality of services impacted.</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E127" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G127" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H127" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J127" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K127" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L127" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M127" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N127" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="10" t="inlineStr">
-        <is>
-          <t>17.3(c)</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>Assign roles and responsibilities that need to be activated for different incident types.</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E128" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F128" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G128" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H128" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I128" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J128" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K128" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L128" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M128" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N128" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>17.3(d)</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>Set out plans for communication to staff, external stakeholders, and media, notification to clients, for internal escalation, and provision of information to counterparts.</t>
-        </is>
-      </c>
-      <c r="D129" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E129" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F129" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G129" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H129" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I129" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J129" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K129" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L129" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M129" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N129" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="10" t="inlineStr">
-        <is>
-          <t>17.3(e)</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C130" s="10" t="inlineStr">
-        <is>
-          <t>Ensure that at least major ICT-related incidents are reported to relevant senior management and inform the management body.</t>
-        </is>
-      </c>
-      <c r="D130" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E130" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F130" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G130" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H130" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I130" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J130" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K130" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L130" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M130" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N130" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>17.3(f)</t>
-        </is>
-      </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>IRO-01, IRO-04</t>
-        </is>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>Establish ICT-related incident response procedures to mitigate impacts and ensure that services become operational and secure in a timely manner.</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E131" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F131" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
-VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
-For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
-For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
-At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
-To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
-VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
-This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
-        </is>
-      </c>
-      <c r="G131" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H131" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
-Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
-Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
-Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
-For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
-These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
-        </is>
-      </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J131" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
-For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
-        </is>
-      </c>
-      <c r="K131" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L131" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M131" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N131" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>18.1(e)</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>IRO-02</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities shall classify ICT-related incidents and shall determine their impact based on the following criteria:</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E132" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F132" s="10" t="inlineStr">
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>The criticality of the services affected, including the financial entity's transactions and operations.</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
 For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
@@ -11392,12 +11558,12 @@
 While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
         </is>
       </c>
-      <c r="G132" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H132" s="10" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
 For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
@@ -11407,12 +11573,12 @@
 Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
         </is>
       </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J132" s="10" t="inlineStr">
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J137" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
 Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
@@ -11421,22 +11587,22 @@
 PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
         </is>
       </c>
-      <c r="K132" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L132" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M132" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N132" s="10" t="inlineStr">
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L137" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M137" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N137" s="10" t="inlineStr">
         <is>
           <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
 For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
@@ -11448,481 +11614,6 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>18.1(a)</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>IRO-02</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>The number and/or relevance of clients or financial counterparts affected, amount/number of transactions affected, and reputational impact.</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F133" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
-        </is>
-      </c>
-      <c r="G133" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J133" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
-        </is>
-      </c>
-      <c r="K133" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L133" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M133" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N133" s="10" t="inlineStr">
-        <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>18.1(b)</t>
-        </is>
-      </c>
-      <c r="B134" s="10" t="inlineStr">
-        <is>
-          <t>IRO-02</t>
-        </is>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
-        <is>
-          <t>The duration of the ICT-related incident, including the service downtime.</t>
-        </is>
-      </c>
-      <c r="D134" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E134" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F134" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
-        </is>
-      </c>
-      <c r="G134" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H134" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
-        </is>
-      </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J134" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
-        </is>
-      </c>
-      <c r="K134" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L134" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M134" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N134" s="10" t="inlineStr">
-        <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>18.1(c)</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>IRO-02</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>The geographical spread with regard to the areas affected by the ICT-related incident, particularly if it affects more than two Member States.</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E135" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F135" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
-        </is>
-      </c>
-      <c r="G135" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H135" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
-        </is>
-      </c>
-      <c r="I135" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J135" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
-        </is>
-      </c>
-      <c r="K135" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L135" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M135" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N135" s="10" t="inlineStr">
-        <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>18.1(d)</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>IRO-02</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>The data losses that the ICT-related incident entails, in relation to availability, authenticity, integrity or confidentiality of data.</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E136" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F136" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
-        </is>
-      </c>
-      <c r="G136" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H136" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
-        </is>
-      </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J136" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
-        </is>
-      </c>
-      <c r="K136" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L136" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M136" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N136" s="10" t="inlineStr">
-        <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>18.1(e)</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>IRO-02</t>
-        </is>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>The criticality of the services affected, including the financial entity's transactions and operations.</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
-        </is>
-      </c>
-      <c r="G137" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H137" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
-        </is>
-      </c>
-      <c r="K137" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L137" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M137" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N137" s="10" t="inlineStr">
-        <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
-        </is>
-      </c>
-    </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
@@ -11941,54 +11632,37 @@
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K138" s="10" t="inlineStr">
@@ -12003,18 +11677,12 @@
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N138" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -12036,54 +11704,37 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K139" s="10" t="inlineStr">
@@ -12098,18 +11749,12 @@
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N139" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -12945,15 +12590,231 @@
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J151" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K151" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L151" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N151" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>BCD-04</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities, other than microenterprises, shall ensure that tests are undertaken by independent parties, whether internal or external; if internal, sufficient resources and avoidance of conflicts of interest are required.</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K152" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L152" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N152" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>BCD-04</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities, other than microenterprises, shall establish procedures and policies to prioritise, classify and remedy all issues revealed throughout the tests, and establish internal validation methodologies.</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F153" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K153" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L153" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N153" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>BCD-04</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Financial entities, other than microenterprises, shall ensure, at least yearly, that appropriate tests are conducted on all ICT systems and applications supporting critical or important functions.</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F154" s="10" t="inlineStr">
         <is>
           <t>VCF provides several infrastructure-level capabilities that support an organization's contingency plan testing and exercise program, though the planning, scheduling, execution, and evaluation of formal contingency tests remains an organizational responsibility.
 VCF includes built-in recovery and high-availability mechanisms that organizations can exercise during contingency tests. vSAN stretched clusters can be exercised by simulating site failures through host maintenance mode operations, validating that the surviving availability zone continues storage and compute operations. A vSAN stretched cluster continues to function if a failure or scheduled maintenance occurs at one zone, and with local fault protection enabled, the cluster can perform repairs on missing or broken components in the available site. vSphere HA can be tested by deliberately failing hosts to observe VM restart behavior and confirm that admission control policies reserve sufficient capacity. vSphere HA uses admission control so that a cluster has sufficient resources to support virtual machine recovery when a host fails.
@@ -12965,22 +12826,22 @@
 Organizations deploying VCF should establish a formal contingency plan testing program that includes scheduled DR drills, failover exercises, backup restoration validation, and tabletop exercises. VCF's recovery mechanisms, what-if analysis, and pre-check capabilities can inform and support these activities, but the test plan itself, its schedule, success criteria, scenario design, evaluation criteria, and after-action review process must be defined and managed by the organization.</t>
         </is>
       </c>
-      <c r="G151" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H151" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J151" s="10" t="inlineStr">
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J154" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides non-disruptive testing of disaster recovery plans as a core operational capability. Recovery plans organize protected workloads into sequenced, dependency-aware execution groups, and these plans can be tested without affecting production operations on either the protected or recovery site.
 Testing a recovery plan in PNR validates that virtual machines recover correctly to the recovery site and exercises nearly every aspect of a recovery plan to validate disaster recovery readiness. Testing has no lasting effects on either the protected or recovery site, which means exercises can be repeated at any frequency without risk to production workloads. PNR requires that recovery plans be tested before use for planned migration or disaster recovery operations. Recovery plan tests can be canceled at any time; however, a successful cleanup operation must be completed before running a failover or initiating another test.
@@ -12989,255 +12850,6 @@
 The organizational elements of contingency plan testing, including exercise scheduling, scenario design, evaluation criteria, and after-action reviews, are outside PNR's scope. Recovery plan testing supports two distinct pre-production rehearsal modes: test recovery, which validates failover into an isolated environment without disrupting production, and planned migration, which performs an orderly, validated move of workloads. Tests can be used to verify that recovery time and recovery point objectives are met, and can be run unattended through the VCF Operations Orchestrator plug-in and the REST API for scheduled or scripted execution.</t>
         </is>
       </c>
-      <c r="K151" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L151" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M151" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N151" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="B152" s="10" t="inlineStr">
-        <is>
-          <t>BCD-04</t>
-        </is>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities, other than microenterprises, shall ensure that tests are undertaken by independent parties, whether internal or external; if internal, sufficient resources and avoidance of conflicts of interest are required.</t>
-        </is>
-      </c>
-      <c r="D152" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E152" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F152" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides several infrastructure-level capabilities that support an organization's contingency plan testing and exercise program, though the planning, scheduling, execution, and evaluation of formal contingency tests remains an organizational responsibility.
-VCF includes built-in recovery and high-availability mechanisms that organizations can exercise during contingency tests. vSAN stretched clusters can be exercised by simulating site failures through host maintenance mode operations, validating that the surviving availability zone continues storage and compute operations. A vSAN stretched cluster continues to function if a failure or scheduled maintenance occurs at one zone, and with local fault protection enabled, the cluster can perform repairs on missing or broken components in the available site. vSphere HA can be tested by deliberately failing hosts to observe VM restart behavior and confirm that admission control policies reserve sufficient capacity. vSphere HA uses admission control so that a cluster has sufficient resources to support virtual machine recovery when a host fails.
-VCF Operations HCX supports workload migrations between sites through Mobility Groups, allowing organizations to exercise mobility procedures and validate that workloads can be moved to alternate processing locations. Migration activity, progress, and history are tracked through the Migration Planning interface, providing visibility into the results of migration exercises.
-Management component backup and restore procedures can be tested by performing restore operations for VCF Operations, VMware vCenter, and NSX components. VCF documents the prerequisites and sequencing for file-based restore of these components, allowing organizations to validate their recovery procedures against documented expectations. Changed Block Tracking (CBT) enables incremental backups through VADP-integrated solutions that can be tested independently, and VADP-based backup partner solutions can perform backup, full restore, and registration of VM Service VMs on a Supervisor.
-VCF Operations includes a What-If Analysis capability under its capacity planning module that allows administrators to model hypothetical scenarios against current infrastructure. Administrators can create, save, and run scenarios cumulatively to evaluate the demand and supply for capacity on resources and assess potential risk to current capacity. This supports both Traditional and Hyperconverged deployment models. Scenarios can be committed as planning tools for capacity analysis, helping organizations with separate capacity management and operations teams understand current capacity and upcoming capacity requirements. These what-if scenarios can be used as part of contingency testing to model failover capacity needs, validate that sufficient resources exist to absorb relocated workloads, and verify that planned recovery configurations are viable before an actual event occurs.
-To support the separation of test and production environments during contingency exercises, VCF Operations allows administrators to configure custom groups with differentiated alert thresholds and capacity calculations. This allows a test environment to operate under different operational policies than production, which is useful when conducting DR drills or failover exercises that temporarily shift workloads between sites or clusters.
-VCF also provides built-in pre-check and validation capabilities that verify component connectivity, version compatibility, and component status among other environment readiness checks. These pre-checks run automatically during lifecycle operations such as upgrades and remediation, and they help confirm that the environment is in a known-good state before changes are applied. While these are not contingency plan tests in themselves, they contribute to readiness assessment by confirming that infrastructure components are healthy and correctly configured before and after contingency exercises.
-Organizations deploying VCF should establish a formal contingency plan testing program that includes scheduled DR drills, failover exercises, backup restoration validation, and tabletop exercises. VCF's recovery mechanisms, what-if analysis, and pre-check capabilities can inform and support these activities, but the test plan itself, its schedule, success criteria, scenario design, evaluation criteria, and after-action review process must be defined and managed by the organization.</t>
-        </is>
-      </c>
-      <c r="G152" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H152" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I152" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J152" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides non-disruptive testing of disaster recovery plans as a core operational capability. Recovery plans organize protected workloads into sequenced, dependency-aware execution groups, and these plans can be tested without affecting production operations on either the protected or recovery site.
-Testing a recovery plan in PNR validates that virtual machines recover correctly to the recovery site and exercises nearly every aspect of a recovery plan to validate disaster recovery readiness. Testing has no lasting effects on either the protected or recovery site, which means exercises can be repeated at any frequency without risk to production workloads. PNR requires that recovery plans be tested before use for planned migration or disaster recovery operations. Recovery plan tests can be canceled at any time; however, a successful cleanup operation must be completed before running a failover or initiating another test.
-Recovery plan test execution is tracked through the Test task in Recent Tasks, which monitors overall progress of the test operation. Recovery plans support two types of custom steps: Test Steps that run during recovery plan testing, and Recovery Steps that run during planned migration or disaster recovery operations. The Configure Test Networks step in the recovery plan workflow supports using a separate test network at the recovery site to keep test VMs isolated from production network segments during testing.
-Recovery plan testing can be automated through the VCF Operations orchestrator Plug-In for Protection and Recovery. The Initiate Test Recovery Plan workflow starts a test of a selected recovery plan and performs a state check to verify the recovery plan is in ready state before allowing test execution. The Initiate Cleanup Recovery Plan workflow cleans up a test when the recovery plan is in needsCleanup state.
-The organizational elements of contingency plan testing, including exercise scheduling, scenario design, evaluation criteria, and after-action reviews, are outside PNR's scope. Recovery plan testing supports two distinct pre-production rehearsal modes: test recovery, which validates failover into an isolated environment without disrupting production, and planned migration, which performs an orderly, validated move of workloads. Tests can be used to verify that recovery time and recovery point objectives are met, and can be run unattended through the VCF Operations Orchestrator plug-in and the REST API for scheduled or scripted execution.</t>
-        </is>
-      </c>
-      <c r="K152" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L152" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M152" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N152" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>BCD-04</t>
-        </is>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities, other than microenterprises, shall establish procedures and policies to prioritise, classify and remedy all issues revealed throughout the tests, and establish internal validation methodologies.</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E153" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F153" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides several infrastructure-level capabilities that support an organization's contingency plan testing and exercise program, though the planning, scheduling, execution, and evaluation of formal contingency tests remains an organizational responsibility.
-VCF includes built-in recovery and high-availability mechanisms that organizations can exercise during contingency tests. vSAN stretched clusters can be exercised by simulating site failures through host maintenance mode operations, validating that the surviving availability zone continues storage and compute operations. A vSAN stretched cluster continues to function if a failure or scheduled maintenance occurs at one zone, and with local fault protection enabled, the cluster can perform repairs on missing or broken components in the available site. vSphere HA can be tested by deliberately failing hosts to observe VM restart behavior and confirm that admission control policies reserve sufficient capacity. vSphere HA uses admission control so that a cluster has sufficient resources to support virtual machine recovery when a host fails.
-VCF Operations HCX supports workload migrations between sites through Mobility Groups, allowing organizations to exercise mobility procedures and validate that workloads can be moved to alternate processing locations. Migration activity, progress, and history are tracked through the Migration Planning interface, providing visibility into the results of migration exercises.
-Management component backup and restore procedures can be tested by performing restore operations for VCF Operations, VMware vCenter, and NSX components. VCF documents the prerequisites and sequencing for file-based restore of these components, allowing organizations to validate their recovery procedures against documented expectations. Changed Block Tracking (CBT) enables incremental backups through VADP-integrated solutions that can be tested independently, and VADP-based backup partner solutions can perform backup, full restore, and registration of VM Service VMs on a Supervisor.
-VCF Operations includes a What-If Analysis capability under its capacity planning module that allows administrators to model hypothetical scenarios against current infrastructure. Administrators can create, save, and run scenarios cumulatively to evaluate the demand and supply for capacity on resources and assess potential risk to current capacity. This supports both Traditional and Hyperconverged deployment models. Scenarios can be committed as planning tools for capacity analysis, helping organizations with separate capacity management and operations teams understand current capacity and upcoming capacity requirements. These what-if scenarios can be used as part of contingency testing to model failover capacity needs, validate that sufficient resources exist to absorb relocated workloads, and verify that planned recovery configurations are viable before an actual event occurs.
-To support the separation of test and production environments during contingency exercises, VCF Operations allows administrators to configure custom groups with differentiated alert thresholds and capacity calculations. This allows a test environment to operate under different operational policies than production, which is useful when conducting DR drills or failover exercises that temporarily shift workloads between sites or clusters.
-VCF also provides built-in pre-check and validation capabilities that verify component connectivity, version compatibility, and component status among other environment readiness checks. These pre-checks run automatically during lifecycle operations such as upgrades and remediation, and they help confirm that the environment is in a known-good state before changes are applied. While these are not contingency plan tests in themselves, they contribute to readiness assessment by confirming that infrastructure components are healthy and correctly configured before and after contingency exercises.
-Organizations deploying VCF should establish a formal contingency plan testing program that includes scheduled DR drills, failover exercises, backup restoration validation, and tabletop exercises. VCF's recovery mechanisms, what-if analysis, and pre-check capabilities can inform and support these activities, but the test plan itself, its schedule, success criteria, scenario design, evaluation criteria, and after-action review process must be defined and managed by the organization.</t>
-        </is>
-      </c>
-      <c r="G153" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H153" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J153" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides non-disruptive testing of disaster recovery plans as a core operational capability. Recovery plans organize protected workloads into sequenced, dependency-aware execution groups, and these plans can be tested without affecting production operations on either the protected or recovery site.
-Testing a recovery plan in PNR validates that virtual machines recover correctly to the recovery site and exercises nearly every aspect of a recovery plan to validate disaster recovery readiness. Testing has no lasting effects on either the protected or recovery site, which means exercises can be repeated at any frequency without risk to production workloads. PNR requires that recovery plans be tested before use for planned migration or disaster recovery operations. Recovery plan tests can be canceled at any time; however, a successful cleanup operation must be completed before running a failover or initiating another test.
-Recovery plan test execution is tracked through the Test task in Recent Tasks, which monitors overall progress of the test operation. Recovery plans support two types of custom steps: Test Steps that run during recovery plan testing, and Recovery Steps that run during planned migration or disaster recovery operations. The Configure Test Networks step in the recovery plan workflow supports using a separate test network at the recovery site to keep test VMs isolated from production network segments during testing.
-Recovery plan testing can be automated through the VCF Operations orchestrator Plug-In for Protection and Recovery. The Initiate Test Recovery Plan workflow starts a test of a selected recovery plan and performs a state check to verify the recovery plan is in ready state before allowing test execution. The Initiate Cleanup Recovery Plan workflow cleans up a test when the recovery plan is in needsCleanup state.
-The organizational elements of contingency plan testing, including exercise scheduling, scenario design, evaluation criteria, and after-action reviews, are outside PNR's scope. Recovery plan testing supports two distinct pre-production rehearsal modes: test recovery, which validates failover into an isolated environment without disrupting production, and planned migration, which performs an orderly, validated move of workloads. Tests can be used to verify that recovery time and recovery point objectives are met, and can be run unattended through the VCF Operations Orchestrator plug-in and the REST API for scheduled or scripted execution.</t>
-        </is>
-      </c>
-      <c r="K153" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L153" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M153" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N153" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="10" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="B154" s="10" t="inlineStr">
-        <is>
-          <t>BCD-04</t>
-        </is>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
-        <is>
-          <t>Financial entities, other than microenterprises, shall ensure, at least yearly, that appropriate tests are conducted on all ICT systems and applications supporting critical or important functions.</t>
-        </is>
-      </c>
-      <c r="D154" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E154" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F154" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides several infrastructure-level capabilities that support an organization's contingency plan testing and exercise program, though the planning, scheduling, execution, and evaluation of formal contingency tests remains an organizational responsibility.
-VCF includes built-in recovery and high-availability mechanisms that organizations can exercise during contingency tests. vSAN stretched clusters can be exercised by simulating site failures through host maintenance mode operations, validating that the surviving availability zone continues storage and compute operations. A vSAN stretched cluster continues to function if a failure or scheduled maintenance occurs at one zone, and with local fault protection enabled, the cluster can perform repairs on missing or broken components in the available site. vSphere HA can be tested by deliberately failing hosts to observe VM restart behavior and confirm that admission control policies reserve sufficient capacity. vSphere HA uses admission control so that a cluster has sufficient resources to support virtual machine recovery when a host fails.
-VCF Operations HCX supports workload migrations between sites through Mobility Groups, allowing organizations to exercise mobility procedures and validate that workloads can be moved to alternate processing locations. Migration activity, progress, and history are tracked through the Migration Planning interface, providing visibility into the results of migration exercises.
-Management component backup and restore procedures can be tested by performing restore operations for VCF Operations, VMware vCenter, and NSX components. VCF documents the prerequisites and sequencing for file-based restore of these components, allowing organizations to validate their recovery procedures against documented expectations. Changed Block Tracking (CBT) enables incremental backups through VADP-integrated solutions that can be tested independently, and VADP-based backup partner solutions can perform backup, full restore, and registration of VM Service VMs on a Supervisor.
-VCF Operations includes a What-If Analysis capability under its capacity planning module that allows administrators to model hypothetical scenarios against current infrastructure. Administrators can create, save, and run scenarios cumulatively to evaluate the demand and supply for capacity on resources and assess potential risk to current capacity. This supports both Traditional and Hyperconverged deployment models. Scenarios can be committed as planning tools for capacity analysis, helping organizations with separate capacity management and operations teams understand current capacity and upcoming capacity requirements. These what-if scenarios can be used as part of contingency testing to model failover capacity needs, validate that sufficient resources exist to absorb relocated workloads, and verify that planned recovery configurations are viable before an actual event occurs.
-To support the separation of test and production environments during contingency exercises, VCF Operations allows administrators to configure custom groups with differentiated alert thresholds and capacity calculations. This allows a test environment to operate under different operational policies than production, which is useful when conducting DR drills or failover exercises that temporarily shift workloads between sites or clusters.
-VCF also provides built-in pre-check and validation capabilities that verify component connectivity, version compatibility, and component status among other environment readiness checks. These pre-checks run automatically during lifecycle operations such as upgrades and remediation, and they help confirm that the environment is in a known-good state before changes are applied. While these are not contingency plan tests in themselves, they contribute to readiness assessment by confirming that infrastructure components are healthy and correctly configured before and after contingency exercises.
-Organizations deploying VCF should establish a formal contingency plan testing program that includes scheduled DR drills, failover exercises, backup restoration validation, and tabletop exercises. VCF's recovery mechanisms, what-if analysis, and pre-check capabilities can inform and support these activities, but the test plan itself, its schedule, success criteria, scenario design, evaluation criteria, and after-action review process must be defined and managed by the organization.</t>
-        </is>
-      </c>
-      <c r="G154" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H154" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I154" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J154" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides non-disruptive testing of disaster recovery plans as a core operational capability. Recovery plans organize protected workloads into sequenced, dependency-aware execution groups, and these plans can be tested without affecting production operations on either the protected or recovery site.
-Testing a recovery plan in PNR validates that virtual machines recover correctly to the recovery site and exercises nearly every aspect of a recovery plan to validate disaster recovery readiness. Testing has no lasting effects on either the protected or recovery site, which means exercises can be repeated at any frequency without risk to production workloads. PNR requires that recovery plans be tested before use for planned migration or disaster recovery operations. Recovery plan tests can be canceled at any time; however, a successful cleanup operation must be completed before running a failover or initiating another test.
-Recovery plan test execution is tracked through the Test task in Recent Tasks, which monitors overall progress of the test operation. Recovery plans support two types of custom steps: Test Steps that run during recovery plan testing, and Recovery Steps that run during planned migration or disaster recovery operations. The Configure Test Networks step in the recovery plan workflow supports using a separate test network at the recovery site to keep test VMs isolated from production network segments during testing.
-Recovery plan testing can be automated through the VCF Operations orchestrator Plug-In for Protection and Recovery. The Initiate Test Recovery Plan workflow starts a test of a selected recovery plan and performs a state check to verify the recovery plan is in ready state before allowing test execution. The Initiate Cleanup Recovery Plan workflow cleans up a test when the recovery plan is in needsCleanup state.
-The organizational elements of contingency plan testing, including exercise scheduling, scenario design, evaluation criteria, and after-action reviews, are outside PNR's scope. Recovery plan testing supports two distinct pre-production rehearsal modes: test recovery, which validates failover into an isolated environment without disrupting production, and planned migration, which performs an orderly, validated move of workloads. Tests can be used to verify that recovery time and recovery point objectives are met, and can be run unattended through the VCF Operations Orchestrator plug-in and the REST API for scheduled or scripted execution.</t>
-        </is>
-      </c>
       <c r="K154" s="10" t="inlineStr">
         <is>
           <t>Not Applicable</t>
@@ -13286,6 +12898,194 @@
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides several built-in capabilities that support routine vulnerability scanning and configuration error detection across the infrastructure stack, though a complete vulnerability management program requires integration with dedicated scanning tools for guest operating systems and applications.
+VCF Operations includes a diagnostics engine that automatically detects known issues and critical vulnerabilities within the VCF software stack. The engine scans the platform against VMware best practices, logs, and properties to identify diagnostic findings that match known issues, providing detailed descriptions, root cause insights, and actionable remediation steps. The Diagnostic Findings feature provides a consolidated view of known product issues, VMware Security Advisory (VMSA)-based security exposures, and best-practice recommendations across the environment. The Findings Catalog displays the complete list of diagnostic signatures checked at any given time, allowing administrators to see exactly what conditions are being evaluated. Administrators can manage diagnostics parameters through a JSON solution configuration file to customize which rules are active, adjust defaults, and control how findings are handled. These diagnostics build on the capabilities of several legacy tools and operational data to provide integrated issue detection and remediation.
+VCF Operations also supports advanced query capabilities that can identify virtual machines running vulnerable operating systems, including specific detection for end-of-life platforms such as Microsoft Windows Server 2003, Microsoft Windows Server 2008, Red Hat Enterprise Linux 5 and 6, and SUSE Linux Enterprise 10. These queries can group results by VLAN for security assessment and compliance monitoring purposes.
+The Security Operations dashboard consolidates user and infrastructure security elements into a single view, helping administrators identify areas that require attention. This dashboard highlights security-relevant findings across the VCF environment, providing a centralized starting point for security posture review.
+For configuration error detection, VCF Operations monitors configuration errors generated from infrastructure components such as NSX networking, grouping findings by hostname. Alert definitions can be created to monitor virtual machines and hosts with custom symptom parameters, enabling identification of configuration problems before users encounter them. The Configuration Drifts feature in VCF Operations provides proactive monitoring of configuration changes across vCenter instances and vSphere clusters, comparing current values against configuration templates to identify drift. vSphere Configuration Profiles must be enabled on clusters to view drift status. Configuration drift detection compares each vCenter instance's current configuration against the defined template values, and the Configuration Drift dashboard allows administrators to view and monitor drift statuses across the environment.
+For patch compliance scanning, vSphere Lifecycle Manager manages all hosts in a cluster collectively with a single image and tracks the current state of each host against the desired cluster image specification, reporting compliance status. The compliance check capability compares the current image on a host against the desired image and reports compatibility status. PowerCLI provides cmdlets for scanning virtual machines and hosts against defined baselines, including the Test-Compliance command to scan entities against downloaded patches and identify which hosts or components are missing security updates. Dynamic baselines update automatically based on specified criteria each time new patches are downloaded, allowing ongoing comparison of system state against current patch levels. The vCenter appliance can also be configured to perform automatic checks for available patches from a configured repository URL, enabling timely awareness of patch availability for the management plane itself. This automatic checking is configured through the vCenter Management Interface (the Check-for-updates-automatically setting) and supports proxy server configuration for environments without direct repository access.
+VMware releases security advisories (VMSAs) for critical known vulnerabilities with step-by-step remediation instructions. VCF Operations Diagnostic Findings provides a consolidated view of VMSA-based security exposures alongside best-practice recommendations, connecting advisory information directly to the operational environment.
+The DISA STIG Viewer tool provides automated checking of system configurations against STIG requirements, helping identify security vulnerabilities and configuration deviations for environments that follow DISA hardening guidance. This offers a structured approach to configuration compliance scanning against industry-standard best practices.
+While VCF provides vulnerability detection and compliance scanning for its own infrastructure stack, scanning of guest operating systems and applications running on VCF requires integration with third-party vulnerability scanning tools. VCF's REST APIs and PowerCLI support enable integration with external scanners and security information and event management platforms to extend scanning coverage beyond the infrastructure layer.</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to vulnerability awareness through Security Services Platform analytics and IDS/IPS threat detection, though it does not perform host-based or authenticated application-layer vulnerability scanning.
+The Security Services Platform generates Security Segmentation Reports and Blast Radius Reports as part of the vDefend Security Assessment workflow. The Security Segmentation Report assesses security posture by analyzing network traffic over a configurable time range, identifying workloads running obsolete operating systems and using risky protocols, and providing specific improvement recommendations. Blast Radius Reports break down at-risk workloads, communication chains, and network flows to support protection planning. The Security Services Platform also provides an application monitoring view that displays information about running applications and identifies potential security risks, enabling assessment and remediation planning.
+The IDS/IPS subsystem contributes vulnerability-specific context by detecting exploitation attempts against known vulnerabilities. IDS/IPS event monitoring records Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by active exploits. Administrators can search the signature library by specific CVE IDs to assess whether detection coverage is in place for known vulnerabilities. The Security Services Platform provides IDS/IPS performance metrics to monitor detection readiness across the environment.
+Because vDefend operates at the network layer, dedicated host-based and authenticated application-layer scanning tools are required to fully satisfy this control. Coverage remains at Contributes.</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J155" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K155" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L155" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides patch management and monitoring capabilities that support an organization's vulnerability management program as it applies to the database services DSM manages.
+For patch management, DSM exposes a Maintenance Policy that administrators configure in the vSphere Client. The Maintenance Policy controls when and for how long the platform applies automatic minor software updates to DSM appliances. Configurable settings include the start date (maintenance-policy-start-date), start time in hours and minutes (maintenance-policy-start-time), and duration of the update window (maintenance-policy-duration). The default maintenance window starts each Saturday at 23:59 with a six-hour duration, and administrators should always set a future date and time when configuring the policy. Upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements. Per-database maintenance windows follow the same structure and can be adjusted during database creation or subsequent operations.
+DSM requires that at least one complete chain of software updates for appliances be attempted, irrespective of the configured maintenance window duration. Patch cycles cannot be indefinitely deferred through policy configuration alone. Within the configured maintenance duration, plug-in software updates attempt up to three times with a 10-minute interval between attempts. The maintenance policy can be edited during the 10-minute interval between attempts, which cancels the next scheduled attempt and applies the newly configured policy. Administrators can view available upgrades and the upgrade history through the Version &amp; Upgrade interface, accessible from the vSphere Client under the VMware vCenter Configure tab. The vSphere Administrator role is explicitly responsible for managing DSM VM updates and creating and managing infrastructure policies, which supports assigning patch management responsibilities to designated personnel. Both a vSphere administrator and a DSM user in the admin role can manage plug-in and database template software updates.
+The DSM controller manages feature dependencies through status monitoring and automated remediation. When an upgrade requires resolution of VKS release dependencies, the controller automatically resumes the provisioning process after those dependencies are resolved, helping maintain patch state consistency during VCF environment upgrades.
+DSM also provides monitoring capabilities that help identify conditions requiring remediation. The Global Alerts page, accessible in both the plug-in UI and the standalone UI, displays non-catastrophic alerts and system status. The Administrator UI Dashboard surfaces the same Global Alerts view for environment-wide visibility. DSM generates alerts for authentication failures, backup and restore corruptions, and certificate errors. The monitoring framework supports metrics-based and status-condition-based alerts covering conditions such as database engine degradation, non-operational status, and backup failure. Administrators and database users can configure alert thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections, each with separate warning and critical thresholds. DSM supports webhook-based alerting for database monitoring events triggered by threshold violations. DSM also provides mitigation suggestions alongside database alerts to help administrators resolve issues without disrupting database services. SQL Server administrators can define maintenance windows for operating system patching of SQL Server instances.
+For diagnostics, DSM generates system support bundles containing system logs and diagnostic information, with a configurable retention duration before the system automatically deletes them. The Monitoring tab in the DSM UI displays monitoring data for individual database instances, including an Alerts pane and an Operations view for tracking operations targeted on database VMs. DSM can also be monitored using VCF Operations for troubleshooting and status visibility, with VCF Operations providing a view of PostgreSQL and MySQL cluster health within the DSM environment.
+The overall vulnerability management program, including scanning, prioritization, remediation timelines, and organizational governance, is an organizational responsibility outside DSM's scope. DSM contributes by providing the update scheduling mechanisms and monitoring visibility needed to act on vulnerability management decisions within the scope of the database services it manages.</t>
+        </is>
+      </c>
+      <c r="M155" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N155" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) supports vulnerability detection for web applications through its Web Application Firewall (WAF) Dynamic Application Security Testing (DAST) integration. The Avi SDK includes a DAST vulnerability scanner script, delivered in the DAST directory on the Avi Controller, which integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning to assess web application vulnerabilities and drive virtual patching. When a DAST scan identifies vulnerabilities, the avi-iwaf-vpatch.py tool automates virtual patch creation by generating Positive Security location rules for each vulnerable URL and Positive Security rules for each supported issue type. This allows the WAF to block requests targeting known vulnerable application paths while underlying code remediation proceeds.
+In 9.1, the Avi Cloud Console adds an Application Rules service that provides rules specifically designed to block attacks on known application vulnerabilities, many correlated with CVE identifiers, and automatically updates those rules on the Avi Controller. This complements DAST-driven virtual patching with a continuously refreshed, CVE-mapped rule set covering known application vulnerability classes.
+The DAST integration has acknowledged limitations: it does not detect all cookie-related security issues, and some flagged vulnerabilities may require manual remediation rather than automated virtual patching. Organizations should validate scan results and supplement Avi's application-layer DAST capability with platform-level scanning of the Avi Controller infrastructure through VCF platform vulnerability management tooling.
+Avi also supports configuration error detection through its inventory fault monitoring system. The Controller's inventoryfaultconfig setting allows independent tracking of license faults, migration faults, backup scheduler faults, SSL profile faults, and deprecated API version faults, with alert generation on configured conditions. This supports detection of misconfigured components before they affect application delivery.
+The Avi Application Security Report consolidates security findings for a selected virtual service. The report includes ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking IP addresses, and trend summaries showing total and flagged requests. Reports can be generated through the Avi UI or the Avi Controller CLI and downloaded in PDF format, supporting auditor review and periodic vulnerability assessment documentation workflows.
+Organizations running Avi on VCF should also lock the Avi Controller Linux OS to a specific version to reduce false-positive CVE scanner findings that arise from inactive OS package versions present on the system but no longer in active use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>VPM-01, VPM-06</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Central securities depositories and central counterparties shall perform vulnerability assessments before any deployment or redeployment of new or existing applications and infrastructure components, and ICT services supporting critical or important functions of the financial entity.</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E156" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F156" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides several built-in capabilities that support routine vulnerability scanning and configuration error detection across the infrastructure stack, though a complete vulnerability management program requires integration with dedicated scanning tools for guest operating systems and applications.
+VCF Operations includes a diagnostics engine that automatically detects known issues and critical vulnerabilities within the VCF software stack. The engine scans the platform against VMware best practices, logs, and properties to identify diagnostic findings that match known issues, providing detailed descriptions, root cause insights, and actionable remediation steps. The Diagnostic Findings feature provides a consolidated view of known product issues, VMware Security Advisory (VMSA)-based security exposures, and best-practice recommendations across the environment. The Findings Catalog displays the complete list of diagnostic signatures checked at any given time, allowing administrators to see exactly what conditions are being evaluated. Administrators can manage diagnostics parameters through a JSON solution configuration file to customize which rules are active, adjust defaults, and control how findings are handled. These diagnostics build on the capabilities of several legacy tools and operational data to provide integrated issue detection and remediation.
+VCF Operations also supports advanced query capabilities that can identify virtual machines running vulnerable operating systems, including specific detection for end-of-life platforms such as Microsoft Windows Server 2003, Microsoft Windows Server 2008, Red Hat Enterprise Linux 5 and 6, and SUSE Linux Enterprise 10. These queries can group results by VLAN for security assessment and compliance monitoring purposes.
+The Security Operations dashboard consolidates user and infrastructure security elements into a single view, helping administrators identify areas that require attention. This dashboard highlights security-relevant findings across the VCF environment, providing a centralized starting point for security posture review.
+For configuration error detection, VCF Operations monitors configuration errors generated from infrastructure components such as NSX networking, grouping findings by hostname. Alert definitions can be created to monitor virtual machines and hosts with custom symptom parameters, enabling identification of configuration problems before users encounter them. The Configuration Drifts feature in VCF Operations provides proactive monitoring of configuration changes across vCenter instances and vSphere clusters, comparing current values against configuration templates to identify drift. vSphere Configuration Profiles must be enabled on clusters to view drift status. Configuration drift detection compares each vCenter instance's current configuration against the defined template values, and the Configuration Drift dashboard allows administrators to view and monitor drift statuses across the environment.
+For patch compliance scanning, vSphere Lifecycle Manager manages all hosts in a cluster collectively with a single image and tracks the current state of each host against the desired cluster image specification, reporting compliance status. The compliance check capability compares the current image on a host against the desired image and reports compatibility status. PowerCLI provides cmdlets for scanning virtual machines and hosts against defined baselines, including the Test-Compliance command to scan entities against downloaded patches and identify which hosts or components are missing security updates. Dynamic baselines update automatically based on specified criteria each time new patches are downloaded, allowing ongoing comparison of system state against current patch levels. The vCenter appliance can also be configured to perform automatic checks for available patches from a configured repository URL, enabling timely awareness of patch availability for the management plane itself. This automatic checking is configured through the vCenter Management Interface (the Check-for-updates-automatically setting) and supports proxy server configuration for environments without direct repository access.
+VMware releases security advisories (VMSAs) for critical known vulnerabilities with step-by-step remediation instructions. VCF Operations Diagnostic Findings provides a consolidated view of VMSA-based security exposures alongside best-practice recommendations, connecting advisory information directly to the operational environment.
+The DISA STIG Viewer tool provides automated checking of system configurations against STIG requirements, helping identify security vulnerabilities and configuration deviations for environments that follow DISA hardening guidance. This offers a structured approach to configuration compliance scanning against industry-standard best practices.
+While VCF provides vulnerability detection and compliance scanning for its own infrastructure stack, scanning of guest operating systems and applications running on VCF requires integration with third-party vulnerability scanning tools. VCF's REST APIs and PowerCLI support enable integration with external scanners and security information and event management platforms to extend scanning coverage beyond the infrastructure layer.</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to vulnerability awareness through Security Services Platform analytics and IDS/IPS threat detection, though it does not perform host-based or authenticated application-layer vulnerability scanning.
+The Security Services Platform generates Security Segmentation Reports and Blast Radius Reports as part of the vDefend Security Assessment workflow. The Security Segmentation Report assesses security posture by analyzing network traffic over a configurable time range, identifying workloads running obsolete operating systems and using risky protocols, and providing specific improvement recommendations. Blast Radius Reports break down at-risk workloads, communication chains, and network flows to support protection planning. The Security Services Platform also provides an application monitoring view that displays information about running applications and identifies potential security risks, enabling assessment and remediation planning.
+The IDS/IPS subsystem contributes vulnerability-specific context by detecting exploitation attempts against known vulnerabilities. IDS/IPS event monitoring records Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by active exploits. Administrators can search the signature library by specific CVE IDs to assess whether detection coverage is in place for known vulnerabilities. The Security Services Platform provides IDS/IPS performance metrics to monitor detection readiness across the environment.
+Because vDefend operates at the network layer, dedicated host-based and authenticated application-layer scanning tools are required to fully satisfy this control. Coverage remains at Contributes.</t>
+        </is>
+      </c>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J156" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K156" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L156" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides patch management and monitoring capabilities that support an organization's vulnerability management program as it applies to the database services DSM manages.
+For patch management, DSM exposes a Maintenance Policy that administrators configure in the vSphere Client. The Maintenance Policy controls when and for how long the platform applies automatic minor software updates to DSM appliances. Configurable settings include the start date (maintenance-policy-start-date), start time in hours and minutes (maintenance-policy-start-time), and duration of the update window (maintenance-policy-duration). The default maintenance window starts each Saturday at 23:59 with a six-hour duration, and administrators should always set a future date and time when configuring the policy. Upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements. Per-database maintenance windows follow the same structure and can be adjusted during database creation or subsequent operations.
+DSM requires that at least one complete chain of software updates for appliances be attempted, irrespective of the configured maintenance window duration. Patch cycles cannot be indefinitely deferred through policy configuration alone. Within the configured maintenance duration, plug-in software updates attempt up to three times with a 10-minute interval between attempts. The maintenance policy can be edited during the 10-minute interval between attempts, which cancels the next scheduled attempt and applies the newly configured policy. Administrators can view available upgrades and the upgrade history through the Version &amp; Upgrade interface, accessible from the vSphere Client under the VMware vCenter Configure tab. The vSphere Administrator role is explicitly responsible for managing DSM VM updates and creating and managing infrastructure policies, which supports assigning patch management responsibilities to designated personnel. Both a vSphere administrator and a DSM user in the admin role can manage plug-in and database template software updates.
+The DSM controller manages feature dependencies through status monitoring and automated remediation. When an upgrade requires resolution of VKS release dependencies, the controller automatically resumes the provisioning process after those dependencies are resolved, helping maintain patch state consistency during VCF environment upgrades.
+DSM also provides monitoring capabilities that help identify conditions requiring remediation. The Global Alerts page, accessible in both the plug-in UI and the standalone UI, displays non-catastrophic alerts and system status. The Administrator UI Dashboard surfaces the same Global Alerts view for environment-wide visibility. DSM generates alerts for authentication failures, backup and restore corruptions, and certificate errors. The monitoring framework supports metrics-based and status-condition-based alerts covering conditions such as database engine degradation, non-operational status, and backup failure. Administrators and database users can configure alert thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections, each with separate warning and critical thresholds. DSM supports webhook-based alerting for database monitoring events triggered by threshold violations. DSM also provides mitigation suggestions alongside database alerts to help administrators resolve issues without disrupting database services. SQL Server administrators can define maintenance windows for operating system patching of SQL Server instances.
+For diagnostics, DSM generates system support bundles containing system logs and diagnostic information, with a configurable retention duration before the system automatically deletes them. The Monitoring tab in the DSM UI displays monitoring data for individual database instances, including an Alerts pane and an Operations view for tracking operations targeted on database VMs. DSM can also be monitored using VCF Operations for troubleshooting and status visibility, with VCF Operations providing a view of PostgreSQL and MySQL cluster health within the DSM environment.
+The overall vulnerability management program, including scanning, prioritization, remediation timelines, and organizational governance, is an organizational responsibility outside DSM's scope. DSM contributes by providing the update scheduling mechanisms and monitoring visibility needed to act on vulnerability management decisions within the scope of the database services it manages.</t>
+        </is>
+      </c>
+      <c r="M156" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N156" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) supports vulnerability detection for web applications through its Web Application Firewall (WAF) Dynamic Application Security Testing (DAST) integration. The Avi SDK includes a DAST vulnerability scanner script, delivered in the DAST directory on the Avi Controller, which integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning to assess web application vulnerabilities and drive virtual patching. When a DAST scan identifies vulnerabilities, the avi-iwaf-vpatch.py tool automates virtual patch creation by generating Positive Security location rules for each vulnerable URL and Positive Security rules for each supported issue type. This allows the WAF to block requests targeting known vulnerable application paths while underlying code remediation proceeds.
+In 9.1, the Avi Cloud Console adds an Application Rules service that provides rules specifically designed to block attacks on known application vulnerabilities, many correlated with CVE identifiers, and automatically updates those rules on the Avi Controller. This complements DAST-driven virtual patching with a continuously refreshed, CVE-mapped rule set covering known application vulnerability classes.
+The DAST integration has acknowledged limitations: it does not detect all cookie-related security issues, and some flagged vulnerabilities may require manual remediation rather than automated virtual patching. Organizations should validate scan results and supplement Avi's application-layer DAST capability with platform-level scanning of the Avi Controller infrastructure through VCF platform vulnerability management tooling.
+Avi also supports configuration error detection through its inventory fault monitoring system. The Controller's inventoryfaultconfig setting allows independent tracking of license faults, migration faults, backup scheduler faults, SSL profile faults, and deprecated API version faults, with alert generation on configured conditions. This supports detection of misconfigured components before they affect application delivery.
+The Avi Application Security Report consolidates security findings for a selected virtual service. The report includes ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking IP addresses, and trend summaries showing total and flagged requests. Reports can be generated through the Avi UI or the Avi Controller CLI and downloaded in PDF format, supporting auditor review and periodic vulnerability assessment documentation workflows.
+Organizations running Avi on VCF should also lock the Avi Controller Linux OS to a specific version to reduce false-positive CVE scanner findings that arise from inactive OS package versions present on the system but no longer in active use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>VPM-01, VPM-06</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Microenterprises shall perform the tests referred to in paragraph 1 by combining a risk-based approach with a strategic planning of ICT testing, by duly considering the need to maintain a balanced approach between the scale of resources and the time to be allocated to the ICT testing provided for in this Article, on the one hand, and the urgency, type of risk, criticality of information assets and of services provided, as well as any other relevant factor, including the financial entity's ability to take calculated risks, on the other hand.</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr">
         <is>
           <t>VCF provides integrated vulnerability and patch management capabilities across its infrastructure stack, addressing both the implementation and monitoring aspects of this control.
 VCF includes built-in lifecycle management that automates the process of applying updates and patches to software components within the stack. Patch releases provide time-sensitive fixes to security and critical issues and can be applied selectively to individual components without requiring synchronized updates across all VCF components. VCF Operations includes a patch planner that identifies available updates for VCF core components, downloads binaries from online depots (or stages them for offline environments), and orchestrates installation across the stack. Pre-update validation runs health checks and compatibility verification before applying changes. VCF Operations automatically backs up components during the patch process to provide a recovery point in case of failure. For vCenter appliance patching, an LVM snapshot is automatically created before the patching process begins; if patching fails, the orchestrator offers the option to roll back to that snapshot or continue after addressing the underlying issue. Lifecycle management also provides tools for planning updates so that administrators can schedule maintenance windows and coordinate changes with minimal disruption to services.
@@ -13298,12 +13098,12 @@
 Broadcom publishes security advisories (VMSAs) for VCF vulnerabilities and releases patches to address them.</t>
         </is>
       </c>
-      <c r="G155" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H155" s="10" t="inlineStr">
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to vulnerability management through network-layer detection, virtual patching, and security posture monitoring capabilities that complement traditional patch management workflows.
 vDefend Distributed IDS/IPS provides signature-based detection of vulnerability exploitation attempts across east-west traffic within the data center. When a new vulnerability is disclosed, administrators can deploy custom IDS/IPS signatures to detect and block exploitation attempts before official patches are available, a practice commonly referred to as virtual patching. In 9.1, IDS/IPS event monitoring displays Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by exploits, giving security teams direct visibility into which specific vulnerabilities are being actively targeted in their environment. The IDS/IPS dashboard provides monitoring and analysis of intrusion events, and Security Services Platform collects metrics to monitor IDS/IPS readiness and performance across the environment. Malicious IP reputation feeds, managed centrally through the Global Manager, automatically update threat intelligence so that known attacker infrastructure is blocked without manual intervention.
@@ -13313,22 +13113,22 @@
 These capabilities address the detection and monitoring dimensions of vulnerability management. Patch deployment and software lifecycle management are handled by other VCF components such as VCF Operations and vSphere Lifecycle Manager.</t>
         </is>
       </c>
-      <c r="I155" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J155" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K155" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L155" s="10" t="inlineStr">
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J157" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K157" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L157" s="10" t="inlineStr">
         <is>
           <t>VMware Data Services Manager (DSM) provides patch management and monitoring capabilities that support an organization's vulnerability management program as it applies to the database services DSM manages.
 For patch management, DSM exposes a Maintenance Policy that administrators configure in the vSphere Client. The Maintenance Policy controls when and for how long the platform applies automatic minor software updates to DSM appliances. Configurable settings include the start date (maintenance-policy-start-date), start time in hours and minutes (maintenance-policy-start-time), and duration of the update window (maintenance-policy-duration). The default maintenance window starts each Saturday at 23:59 with a six-hour duration, and administrators should always set a future date and time when configuring the policy. Upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements. Per-database maintenance windows follow the same structure and can be adjusted during database creation or subsequent operations.
@@ -13339,194 +13139,6 @@
 The overall vulnerability management program, including scanning, prioritization, remediation timelines, and organizational governance, is an organizational responsibility outside DSM's scope. DSM contributes by providing the update scheduling mechanisms and monitoring visibility needed to act on vulnerability management decisions within the scope of the database services it manages.</t>
         </is>
       </c>
-      <c r="M155" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N155" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides a structured patch management lifecycle for both the Controller and Service Engine groups, supporting the application delivery layer's contribution to an organizational vulnerability management program. The CLI patch command offers distinct patching modes (Controller Patch, SE Group Patch, Disruptive Patch, and System Patch), giving administrators flexibility to apply patches to specific components or across the entire system without requiring a full upgrade cycle. The documentation recommends applying patches only to the Service Engine groups that require them, based on Service Engine group segmentation. Patch images are uploaded to the Controller and verified for inclusion in the image bundle before any upgrade operation proceeds.
-Rollback capability is available for patch releases via CLI. The `rollbackpatch controller` command reverts the Controller to the previous patch version, while `rollbackpatch system` rolls back the Controller and all Service Engine groups simultaneously. Rollback transitions the system to the version without the specific patch and does not roll back to the previous major version. The Avi for VCF documentation recommends planning a remediation strategy before re-attempting an upgrade following a rollback. On restore operations, the Controller checks for patches applied as part of the restore to maintain version consistency.
-For application-layer vulnerability management, Avi Load Balancer supports virtual patching through two complementary mechanisms. The Web Application Firewall (WAF) integrates with Dynamic Application Security Testing (DAST) scanners; the Avi SDK integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning, allowing scan results to be imported and used to identify application vulnerabilities and apply WAF-based protections while permanent code fixes are developed and deployed. The Live Security Threat Intelligence service, available through the Cloud Console, extends virtual patching coverage with an Application Rules service providing rules designed to block attacks on known application vulnerabilities, including many with associated CVEs. These rules cover over 5,000 applications including WordPress, Drupal, and Apache, and are automatically updated through continuous Application Rules Database synchronization, keeping WAF protections current.
-An Application Security Report provides a downloadable PDF documenting security findings and pre-check results, supporting vulnerability management reporting and documentation. The alert automation infrastructure supports ControlScripts that alert actions can invoke to automatically add offending client IP addresses to a blocklist attached to a network security policy, enabling automated response to detected threats.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="B156" s="10" t="inlineStr">
-        <is>
-          <t>VPM-01, VPM-06</t>
-        </is>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
-        <is>
-          <t>Central securities depositories and central counterparties shall perform vulnerability assessments before any deployment or redeployment of new or existing applications and infrastructure components, and ICT services supporting critical or important functions of the financial entity.</t>
-        </is>
-      </c>
-      <c r="D156" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E156" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F156" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides integrated vulnerability and patch management capabilities across its infrastructure stack, addressing both the implementation and monitoring aspects of this control.
-VCF includes built-in lifecycle management that automates the process of applying updates and patches to software components within the stack. Patch releases provide time-sensitive fixes to security and critical issues and can be applied selectively to individual components without requiring synchronized updates across all VCF components. VCF Operations includes a patch planner that identifies available updates for VCF core components, downloads binaries from online depots (or stages them for offline environments), and orchestrates installation across the stack. Pre-update validation runs health checks and compatibility verification before applying changes. VCF Operations automatically backs up components during the patch process to provide a recovery point in case of failure. For vCenter appliance patching, an LVM snapshot is automatically created before the patching process begins; if patching fails, the orchestrator offers the option to roll back to that snapshot or continue after addressing the underlying issue. Lifecycle management also provides tools for planning updates so that administrators can schedule maintenance windows and coordinate changes with minimal disruption to services.
-vSphere Lifecycle Manager (vLCM) manages the desired-state configuration for ESX hosts, including firmware and drivers through Hardware Support Manager (HSM) plugins provided by OEM vendors. vLCM images consist of a base image, vendor add-ons, components, and firmware add-ons that can be independently retrieved and applied to hosts. vLCM scans hosts against the desired image specification, flags deviations, and remediates non-compliant hosts. vSphere Lifecycle Manager also supports Live Patch for applicable updates, enabling patches to be applied to ESX hosts without requiring them to enter maintenance mode. It works with three types of software depots (online, offline, and UMDS) to provide flexibility in how patches are sourced and distributed. Update Manager supports dynamic baselines that automatically adjust their patch data based on specified criteria each time new patches are downloaded, allowing administrators to define patching policies that stay current without manual intervention. The Update Manager PowerCLI module provides cmdlets for downloading software patches, creating and modifying baselines, and scanning and remediating virtual machines and hosts, enabling automation of patching workflows.
-For the VMware Kubernetes Service (VKS) and vSphere Supervisor layer, Security Technical Implementation Guides (STIGs) are available for Supervisor and VMware Kubernetes Release (VKr) components through Tanzu STIG Hardening, providing a structured security configuration baseline against which VKS deployments can be assessed and remediated. VKr components and Standard Packages are updated using the VCF CLI `vcf package installed update` command, which upgrades a package installation to a newer version and applies new configuration values, giving administrators a structured mechanism for applying package-level updates to components running in the Supervisor environment. VCF building-block services have independent lifecycles, enabling components to be updated individually without affecting the broader environment. The Node Problem Detector can be deployed within VKS clusters to monitor node health and report infrastructure-level problems through configurable detection rules, supporting the monitoring dimension of vulnerability management at the workload tier.
-For container workloads running on VKS, Harbor is available as a deployable Standard Package with built-in vulnerability scanning using the Trivy database, which can be configured to use a custom or mirrored repository for air-gapped deployments. Harbor also provides content trust features that support image signing and policy-based replication, giving operations teams mechanisms to detect and restrict deployment of images containing known vulnerabilities. Harbor packages are updated using the `vcf package installed update harbor` command. Kubernetes guidance recommends that container images be regularly scanned during creation and in deployment, with known vulnerable software patched before workloads reach the runtime environment. Kubernetes security vulnerabilities are tracked and announced through the Kubernetes Security Response Committee, which maintains an official list of known CVEs and publishes security-related announcements to the kubernetes-announce mailing list. For CI/CD pipelines running on VCF, Harness CI/CD is available as a Supervisor Service with integrated Security Testing Orchestration (STO) that incorporates the Wiz CLI to automate vulnerability management throughout the pipeline, performing infrastructure-as-code (IaC) and secret detection scans and container image scans against artifacts stored in JFrog Artifactory. Vulnerability scan findings from Wiz are reported to the Harness security dashboard, and Harness STO automatically deduplicates findings and displays them on the vulnerabilities tab of each pipeline execution for review.
-VCF Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing detailed descriptions, root cause insights, and actionable remediation steps. The Security Operations dashboard in VCF Operations provides a consolidated view of security posture, helping administrators identify areas requiring attention. VCF Operations compliance management continuously monitors infrastructure for policy violations, highlights risk areas, and provides actionable remediation recommendations. When VCF Operations detects non-compliance with a policy, it can generate alerts or notifications, and depending on the severity of the non-compliance, automated remediation actions can be configured to bring the object back into compliance.
-Configuration drift monitoring provides an additional layer of ongoing assurance. VCF Operations provides unified configuration management that supports scheduled drift detection for vCenter and cluster objects. It detects deviations from assigned configuration template values, displays drift results across all configuration templates, and allows administrators to compare changes against desired values. This helps identify unauthorized or unintended changes to the infrastructure that could introduce vulnerabilities.
-Patching operations are governed by role-based access controls. Editing remediation settings in vSphere Lifecycle Manager requires specific privileges (VcIntegrity.lifecycleSettings.Read and VcIntegrity.lifecycleSettings.Write), and image remediation operations require a separate set of API privileges.
-Broadcom publishes security advisories (VMSAs) for VCF vulnerabilities and releases patches to address them.</t>
-        </is>
-      </c>
-      <c r="G156" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H156" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to vulnerability management through network-layer detection, virtual patching, and security posture monitoring capabilities that complement traditional patch management workflows.
-vDefend Distributed IDS/IPS provides signature-based detection of vulnerability exploitation attempts across east-west traffic within the data center. When a new vulnerability is disclosed, administrators can deploy custom IDS/IPS signatures to detect and block exploitation attempts before official patches are available, a practice commonly referred to as virtual patching. In 9.1, IDS/IPS event monitoring displays Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by exploits, giving security teams direct visibility into which specific vulnerabilities are being actively targeted in their environment. The IDS/IPS dashboard provides monitoring and analysis of intrusion events, and Security Services Platform collects metrics to monitor IDS/IPS readiness and performance across the environment. Malicious IP reputation feeds, managed centrally through the Global Manager, automatically update threat intelligence so that known attacker infrastructure is blocked without manual intervention.
-The Threat Event Monitoring dashboard in Security Services Platform displays the top IPs on which an intrusion was attempted and the top VMs based on Vulnerability Severity criteria. The Threat Event Monitoring tab on the Security Overview dashboard surfaces key insights about the current state of various security issues in the data center, helping security teams understand network activity and prioritize focus areas.
-Security Intelligence, a feature within Security Services Platform, provides posture assessment and segmentation monitoring capabilities. Administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment traffic. The Security Posture dashboard presents information that can be used to plan and implement additional security policies. The Security Explorer provides a visual representation of workloads, their traffic flows, and connection status, which helps identify workloads that may be exposed to unpatched vulnerabilities. Security Services Platform also generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and traffic flows, providing the visibility needed to plan subsequent protection stages. The Security Operator role in Security Services Platform is designated to monitor security systems and respond to security incidents, supporting the operational dimension of vulnerability management monitoring.
-vDefend Advanced Threat Prevention extends detection capabilities to include behavioral analysis and sandboxing, identifying malware and exploit attempts that signature-based detection might miss. The Security Overview dashboard in Security Services Platform displays file inspection statistics organized by different ranges of threat score, giving security teams a quantitative view of file-based threats detected in their environment. This provides an additional layer of protection for systems awaiting patches.
-These capabilities address the detection and monitoring dimensions of vulnerability management. Patch deployment and software lifecycle management are handled by other VCF components such as VCF Operations and vSphere Lifecycle Manager.</t>
-        </is>
-      </c>
-      <c r="I156" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J156" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K156" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L156" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides patch management and monitoring capabilities that support an organization's vulnerability management program as it applies to the database services DSM manages.
-For patch management, DSM exposes a Maintenance Policy that administrators configure in the vSphere Client. The Maintenance Policy controls when and for how long the platform applies automatic minor software updates to DSM appliances. Configurable settings include the start date (maintenance-policy-start-date), start time in hours and minutes (maintenance-policy-start-time), and duration of the update window (maintenance-policy-duration). The default maintenance window starts each Saturday at 23:59 with a six-hour duration, and administrators should always set a future date and time when configuring the policy. Upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements. Per-database maintenance windows follow the same structure and can be adjusted during database creation or subsequent operations.
-DSM requires that at least one complete chain of software updates for appliances be attempted, irrespective of the configured maintenance window duration. Patch cycles cannot be indefinitely deferred through policy configuration alone. Within the configured maintenance duration, plug-in software updates attempt up to three times with a 10-minute interval between attempts. The maintenance policy can be edited during the 10-minute interval between attempts, which cancels the next scheduled attempt and applies the newly configured policy. Administrators can view available upgrades and the upgrade history through the Version &amp; Upgrade interface, accessible from the vSphere Client under the VMware vCenter Configure tab. The vSphere Administrator role is explicitly responsible for managing DSM VM updates and creating and managing infrastructure policies, which supports assigning patch management responsibilities to designated personnel. Both a vSphere administrator and a DSM user in the admin role can manage plug-in and database template software updates.
-The DSM controller manages feature dependencies through status monitoring and automated remediation. When an upgrade requires resolution of VKS release dependencies, the controller automatically resumes the provisioning process after those dependencies are resolved, helping maintain patch state consistency during VCF environment upgrades.
-DSM also provides monitoring capabilities that help identify conditions requiring remediation. The Global Alerts page, accessible in both the plug-in UI and the standalone UI, displays non-catastrophic alerts and system status. The Administrator UI Dashboard surfaces the same Global Alerts view for environment-wide visibility. DSM generates alerts for authentication failures, backup and restore corruptions, and certificate errors. The monitoring framework supports metrics-based and status-condition-based alerts covering conditions such as database engine degradation, non-operational status, and backup failure. Administrators and database users can configure alert thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections, each with separate warning and critical thresholds. DSM supports webhook-based alerting for database monitoring events triggered by threshold violations. DSM also provides mitigation suggestions alongside database alerts to help administrators resolve issues without disrupting database services. SQL Server administrators can define maintenance windows for operating system patching of SQL Server instances.
-For diagnostics, DSM generates system support bundles containing system logs and diagnostic information, with a configurable retention duration before the system automatically deletes them. The Monitoring tab in the DSM UI displays monitoring data for individual database instances, including an Alerts pane and an Operations view for tracking operations targeted on database VMs. DSM can also be monitored using VCF Operations for troubleshooting and status visibility, with VCF Operations providing a view of PostgreSQL and MySQL cluster health within the DSM environment.
-The overall vulnerability management program, including scanning, prioritization, remediation timelines, and organizational governance, is an organizational responsibility outside DSM's scope. DSM contributes by providing the update scheduling mechanisms and monitoring visibility needed to act on vulnerability management decisions within the scope of the database services it manages.</t>
-        </is>
-      </c>
-      <c r="M156" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N156" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides a structured patch management lifecycle for both the Controller and Service Engine groups, supporting the application delivery layer's contribution to an organizational vulnerability management program. The CLI patch command offers distinct patching modes (Controller Patch, SE Group Patch, Disruptive Patch, and System Patch), giving administrators flexibility to apply patches to specific components or across the entire system without requiring a full upgrade cycle. The documentation recommends applying patches only to the Service Engine groups that require them, based on Service Engine group segmentation. Patch images are uploaded to the Controller and verified for inclusion in the image bundle before any upgrade operation proceeds.
-Rollback capability is available for patch releases via CLI. The `rollbackpatch controller` command reverts the Controller to the previous patch version, while `rollbackpatch system` rolls back the Controller and all Service Engine groups simultaneously. Rollback transitions the system to the version without the specific patch and does not roll back to the previous major version. The Avi for VCF documentation recommends planning a remediation strategy before re-attempting an upgrade following a rollback. On restore operations, the Controller checks for patches applied as part of the restore to maintain version consistency.
-For application-layer vulnerability management, Avi Load Balancer supports virtual patching through two complementary mechanisms. The Web Application Firewall (WAF) integrates with Dynamic Application Security Testing (DAST) scanners; the Avi SDK integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning, allowing scan results to be imported and used to identify application vulnerabilities and apply WAF-based protections while permanent code fixes are developed and deployed. The Live Security Threat Intelligence service, available through the Cloud Console, extends virtual patching coverage with an Application Rules service providing rules designed to block attacks on known application vulnerabilities, including many with associated CVEs. These rules cover over 5,000 applications including WordPress, Drupal, and Apache, and are automatically updated through continuous Application Rules Database synchronization, keeping WAF protections current.
-An Application Security Report provides a downloadable PDF documenting security findings and pre-check results, supporting vulnerability management reporting and documentation. The alert automation infrastructure supports ControlScripts that alert actions can invoke to automatically add offending client IP addresses to a blocklist attached to a network security policy, enabling automated response to detected threats.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="B157" s="10" t="inlineStr">
-        <is>
-          <t>VPM-01, VPM-06</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
-        <is>
-          <t>Microenterprises shall perform the tests referred to in paragraph 1 by combining a risk-based approach with a strategic planning of ICT testing, by duly considering the need to maintain a balanced approach between the scale of resources and the time to be allocated to the ICT testing provided for in this Article, on the one hand, and the urgency, type of risk, criticality of information assets and of services provided, as well as any other relevant factor, including the financial entity's ability to take calculated risks, on the other hand.</t>
-        </is>
-      </c>
-      <c r="D157" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E157" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F157" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides integrated vulnerability and patch management capabilities across its infrastructure stack, addressing both the implementation and monitoring aspects of this control.
-VCF includes built-in lifecycle management that automates the process of applying updates and patches to software components within the stack. Patch releases provide time-sensitive fixes to security and critical issues and can be applied selectively to individual components without requiring synchronized updates across all VCF components. VCF Operations includes a patch planner that identifies available updates for VCF core components, downloads binaries from online depots (or stages them for offline environments), and orchestrates installation across the stack. Pre-update validation runs health checks and compatibility verification before applying changes. VCF Operations automatically backs up components during the patch process to provide a recovery point in case of failure. For vCenter appliance patching, an LVM snapshot is automatically created before the patching process begins; if patching fails, the orchestrator offers the option to roll back to that snapshot or continue after addressing the underlying issue. Lifecycle management also provides tools for planning updates so that administrators can schedule maintenance windows and coordinate changes with minimal disruption to services.
-vSphere Lifecycle Manager (vLCM) manages the desired-state configuration for ESX hosts, including firmware and drivers through Hardware Support Manager (HSM) plugins provided by OEM vendors. vLCM images consist of a base image, vendor add-ons, components, and firmware add-ons that can be independently retrieved and applied to hosts. vLCM scans hosts against the desired image specification, flags deviations, and remediates non-compliant hosts. vSphere Lifecycle Manager also supports Live Patch for applicable updates, enabling patches to be applied to ESX hosts without requiring them to enter maintenance mode. It works with three types of software depots (online, offline, and UMDS) to provide flexibility in how patches are sourced and distributed. Update Manager supports dynamic baselines that automatically adjust their patch data based on specified criteria each time new patches are downloaded, allowing administrators to define patching policies that stay current without manual intervention. The Update Manager PowerCLI module provides cmdlets for downloading software patches, creating and modifying baselines, and scanning and remediating virtual machines and hosts, enabling automation of patching workflows.
-For the VMware Kubernetes Service (VKS) and vSphere Supervisor layer, Security Technical Implementation Guides (STIGs) are available for Supervisor and VMware Kubernetes Release (VKr) components through Tanzu STIG Hardening, providing a structured security configuration baseline against which VKS deployments can be assessed and remediated. VKr components and Standard Packages are updated using the VCF CLI `vcf package installed update` command, which upgrades a package installation to a newer version and applies new configuration values, giving administrators a structured mechanism for applying package-level updates to components running in the Supervisor environment. VCF building-block services have independent lifecycles, enabling components to be updated individually without affecting the broader environment. The Node Problem Detector can be deployed within VKS clusters to monitor node health and report infrastructure-level problems through configurable detection rules, supporting the monitoring dimension of vulnerability management at the workload tier.
-For container workloads running on VKS, Harbor is available as a deployable Standard Package with built-in vulnerability scanning using the Trivy database, which can be configured to use a custom or mirrored repository for air-gapped deployments. Harbor also provides content trust features that support image signing and policy-based replication, giving operations teams mechanisms to detect and restrict deployment of images containing known vulnerabilities. Harbor packages are updated using the `vcf package installed update harbor` command. Kubernetes guidance recommends that container images be regularly scanned during creation and in deployment, with known vulnerable software patched before workloads reach the runtime environment. Kubernetes security vulnerabilities are tracked and announced through the Kubernetes Security Response Committee, which maintains an official list of known CVEs and publishes security-related announcements to the kubernetes-announce mailing list. For CI/CD pipelines running on VCF, Harness CI/CD is available as a Supervisor Service with integrated Security Testing Orchestration (STO) that incorporates the Wiz CLI to automate vulnerability management throughout the pipeline, performing infrastructure-as-code (IaC) and secret detection scans and container image scans against artifacts stored in JFrog Artifactory. Vulnerability scan findings from Wiz are reported to the Harness security dashboard, and Harness STO automatically deduplicates findings and displays them on the vulnerabilities tab of each pipeline execution for review.
-VCF Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing detailed descriptions, root cause insights, and actionable remediation steps. The Security Operations dashboard in VCF Operations provides a consolidated view of security posture, helping administrators identify areas requiring attention. VCF Operations compliance management continuously monitors infrastructure for policy violations, highlights risk areas, and provides actionable remediation recommendations. When VCF Operations detects non-compliance with a policy, it can generate alerts or notifications, and depending on the severity of the non-compliance, automated remediation actions can be configured to bring the object back into compliance.
-Configuration drift monitoring provides an additional layer of ongoing assurance. VCF Operations provides unified configuration management that supports scheduled drift detection for vCenter and cluster objects. It detects deviations from assigned configuration template values, displays drift results across all configuration templates, and allows administrators to compare changes against desired values. This helps identify unauthorized or unintended changes to the infrastructure that could introduce vulnerabilities.
-Patching operations are governed by role-based access controls. Editing remediation settings in vSphere Lifecycle Manager requires specific privileges (VcIntegrity.lifecycleSettings.Read and VcIntegrity.lifecycleSettings.Write), and image remediation operations require a separate set of API privileges.
-Broadcom publishes security advisories (VMSAs) for VCF vulnerabilities and releases patches to address them.</t>
-        </is>
-      </c>
-      <c r="G157" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H157" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to vulnerability management through network-layer detection, virtual patching, and security posture monitoring capabilities that complement traditional patch management workflows.
-vDefend Distributed IDS/IPS provides signature-based detection of vulnerability exploitation attempts across east-west traffic within the data center. When a new vulnerability is disclosed, administrators can deploy custom IDS/IPS signatures to detect and block exploitation attempts before official patches are available, a practice commonly referred to as virtual patching. In 9.1, IDS/IPS event monitoring displays Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by exploits, giving security teams direct visibility into which specific vulnerabilities are being actively targeted in their environment. The IDS/IPS dashboard provides monitoring and analysis of intrusion events, and Security Services Platform collects metrics to monitor IDS/IPS readiness and performance across the environment. Malicious IP reputation feeds, managed centrally through the Global Manager, automatically update threat intelligence so that known attacker infrastructure is blocked without manual intervention.
-The Threat Event Monitoring dashboard in Security Services Platform displays the top IPs on which an intrusion was attempted and the top VMs based on Vulnerability Severity criteria. The Threat Event Monitoring tab on the Security Overview dashboard surfaces key insights about the current state of various security issues in the data center, helping security teams understand network activity and prioritize focus areas.
-Security Intelligence, a feature within Security Services Platform, provides posture assessment and segmentation monitoring capabilities. Administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment traffic. The Security Posture dashboard presents information that can be used to plan and implement additional security policies. The Security Explorer provides a visual representation of workloads, their traffic flows, and connection status, which helps identify workloads that may be exposed to unpatched vulnerabilities. Security Services Platform also generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and traffic flows, providing the visibility needed to plan subsequent protection stages. The Security Operator role in Security Services Platform is designated to monitor security systems and respond to security incidents, supporting the operational dimension of vulnerability management monitoring.
-vDefend Advanced Threat Prevention extends detection capabilities to include behavioral analysis and sandboxing, identifying malware and exploit attempts that signature-based detection might miss. The Security Overview dashboard in Security Services Platform displays file inspection statistics organized by different ranges of threat score, giving security teams a quantitative view of file-based threats detected in their environment. This provides an additional layer of protection for systems awaiting patches.
-These capabilities address the detection and monitoring dimensions of vulnerability management. Patch deployment and software lifecycle management are handled by other VCF components such as VCF Operations and vSphere Lifecycle Manager.</t>
-        </is>
-      </c>
-      <c r="I157" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J157" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K157" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L157" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides patch management and monitoring capabilities that support an organization's vulnerability management program as it applies to the database services DSM manages.
-For patch management, DSM exposes a Maintenance Policy that administrators configure in the vSphere Client. The Maintenance Policy controls when and for how long the platform applies automatic minor software updates to DSM appliances. Configurable settings include the start date (maintenance-policy-start-date), start time in hours and minutes (maintenance-policy-start-time), and duration of the update window (maintenance-policy-duration). The default maintenance window starts each Saturday at 23:59 with a six-hour duration, and administrators should always set a future date and time when configuring the policy. Upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements. Per-database maintenance windows follow the same structure and can be adjusted during database creation or subsequent operations.
-DSM requires that at least one complete chain of software updates for appliances be attempted, irrespective of the configured maintenance window duration. Patch cycles cannot be indefinitely deferred through policy configuration alone. Within the configured maintenance duration, plug-in software updates attempt up to three times with a 10-minute interval between attempts. The maintenance policy can be edited during the 10-minute interval between attempts, which cancels the next scheduled attempt and applies the newly configured policy. Administrators can view available upgrades and the upgrade history through the Version &amp; Upgrade interface, accessible from the vSphere Client under the VMware vCenter Configure tab. The vSphere Administrator role is explicitly responsible for managing DSM VM updates and creating and managing infrastructure policies, which supports assigning patch management responsibilities to designated personnel. Both a vSphere administrator and a DSM user in the admin role can manage plug-in and database template software updates.
-The DSM controller manages feature dependencies through status monitoring and automated remediation. When an upgrade requires resolution of VKS release dependencies, the controller automatically resumes the provisioning process after those dependencies are resolved, helping maintain patch state consistency during VCF environment upgrades.
-DSM also provides monitoring capabilities that help identify conditions requiring remediation. The Global Alerts page, accessible in both the plug-in UI and the standalone UI, displays non-catastrophic alerts and system status. The Administrator UI Dashboard surfaces the same Global Alerts view for environment-wide visibility. DSM generates alerts for authentication failures, backup and restore corruptions, and certificate errors. The monitoring framework supports metrics-based and status-condition-based alerts covering conditions such as database engine degradation, non-operational status, and backup failure. Administrators and database users can configure alert thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections, each with separate warning and critical thresholds. DSM supports webhook-based alerting for database monitoring events triggered by threshold violations. DSM also provides mitigation suggestions alongside database alerts to help administrators resolve issues without disrupting database services. SQL Server administrators can define maintenance windows for operating system patching of SQL Server instances.
-For diagnostics, DSM generates system support bundles containing system logs and diagnostic information, with a configurable retention duration before the system automatically deletes them. The Monitoring tab in the DSM UI displays monitoring data for individual database instances, including an Alerts pane and an Operations view for tracking operations targeted on database VMs. DSM can also be monitored using VCF Operations for troubleshooting and status visibility, with VCF Operations providing a view of PostgreSQL and MySQL cluster health within the DSM environment.
-The overall vulnerability management program, including scanning, prioritization, remediation timelines, and organizational governance, is an organizational responsibility outside DSM's scope. DSM contributes by providing the update scheduling mechanisms and monitoring visibility needed to act on vulnerability management decisions within the scope of the database services it manages.</t>
-        </is>
-      </c>
       <c r="M157" s="10" t="inlineStr">
         <is>
           <t>Contributes</t>
@@ -13534,10 +13146,12 @@
       </c>
       <c r="N157" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides a structured patch management lifecycle for both the Controller and Service Engine groups, supporting the application delivery layer's contribution to an organizational vulnerability management program. The CLI patch command offers distinct patching modes (Controller Patch, SE Group Patch, Disruptive Patch, and System Patch), giving administrators flexibility to apply patches to specific components or across the entire system without requiring a full upgrade cycle. The documentation recommends applying patches only to the Service Engine groups that require them, based on Service Engine group segmentation. Patch images are uploaded to the Controller and verified for inclusion in the image bundle before any upgrade operation proceeds.
-Rollback capability is available for patch releases via CLI. The `rollbackpatch controller` command reverts the Controller to the previous patch version, while `rollbackpatch system` rolls back the Controller and all Service Engine groups simultaneously. Rollback transitions the system to the version without the specific patch and does not roll back to the previous major version. The Avi for VCF documentation recommends planning a remediation strategy before re-attempting an upgrade following a rollback. On restore operations, the Controller checks for patches applied as part of the restore to maintain version consistency.
-For application-layer vulnerability management, Avi Load Balancer supports virtual patching through two complementary mechanisms. The Web Application Firewall (WAF) integrates with Dynamic Application Security Testing (DAST) scanners; the Avi SDK integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning, allowing scan results to be imported and used to identify application vulnerabilities and apply WAF-based protections while permanent code fixes are developed and deployed. The Live Security Threat Intelligence service, available through the Cloud Console, extends virtual patching coverage with an Application Rules service providing rules designed to block attacks on known application vulnerabilities, including many with associated CVEs. These rules cover over 5,000 applications including WordPress, Drupal, and Apache, and are automatically updated through continuous Application Rules Database synchronization, keeping WAF protections current.
-An Application Security Report provides a downloadable PDF documenting security findings and pre-check results, supporting vulnerability management reporting and documentation. The alert automation infrastructure supports ControlScripts that alert actions can invoke to automatically add offending client IP addresses to a blocklist attached to a network security policy, enabling automated response to detected threats.</t>
+          <t>VMware Avi Load Balancer (Avi) supports vulnerability detection for web applications through its Web Application Firewall (WAF) Dynamic Application Security Testing (DAST) integration. The Avi SDK includes a DAST vulnerability scanner script, delivered in the DAST directory on the Avi Controller, which integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning to assess web application vulnerabilities and drive virtual patching. When a DAST scan identifies vulnerabilities, the avi-iwaf-vpatch.py tool automates virtual patch creation by generating Positive Security location rules for each vulnerable URL and Positive Security rules for each supported issue type. This allows the WAF to block requests targeting known vulnerable application paths while underlying code remediation proceeds.
+In 9.1, the Avi Cloud Console adds an Application Rules service that provides rules specifically designed to block attacks on known application vulnerabilities, many correlated with CVE identifiers, and automatically updates those rules on the Avi Controller. This complements DAST-driven virtual patching with a continuously refreshed, CVE-mapped rule set covering known application vulnerability classes.
+The DAST integration has acknowledged limitations: it does not detect all cookie-related security issues, and some flagged vulnerabilities may require manual remediation rather than automated virtual patching. Organizations should validate scan results and supplement Avi's application-layer DAST capability with platform-level scanning of the Avi Controller infrastructure through VCF platform vulnerability management tooling.
+Avi also supports configuration error detection through its inventory fault monitoring system. The Controller's inventoryfaultconfig setting allows independent tracking of license faults, migration faults, backup scheduler faults, SSL profile faults, and deprecated API version faults, with alert generation on configured conditions. This supports detection of misconfigured components before they affect application delivery.
+The Avi Application Security Report consolidates security findings for a selected virtual service. The report includes ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking IP addresses, and trend summaries showing total and flagged requests. Reports can be generated through the Avi UI or the Avi Controller CLI and downloaded in PDF format, supporting auditor review and periodic vulnerability assessment documentation workflows.
+Organizations running Avi on VCF should also lock the Avi Controller Linux OS to a specific version to reduce false-positive CVE scanner findings that arise from inactive OS package versions present on the system but no longer in active use.</t>
         </is>
       </c>
     </row>
@@ -16943,47 +16557,27 @@
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E205" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F205" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of access control, identity federation, tenant isolation, and monitoring to mitigate risks associated with third-party access to infrastructure assets, applications, services, and data.
-VCF SSO integrates with federated identity providers through standards-based protocols, supporting SAML 2.0, OIDC, and AD/LDAP as authentication sources. LDAP-based directory services such as Active Directory are supported for identity management across the platform, including NSX Manager, which supports both Active Directory over LDAP and Open LDAP as identity sources. This allows organizations to extend their existing identity governance to VCF rather than maintaining separate credential stores for third-party users.
-Role-based access control enforces least-privilege principles across the platform. VCF local accounts support configurable roles such as superAdmin, and VCF Automation assigns host switch-level permissions through the Cloud Administrator group (Cloudadmin role). The administrators role in VCF Operations is restricted to specific users who need access to objects and actions across the entire environment. For Kubernetes workloads, vSphere Supervisor namespaces support role-based access control with EDIT, VIEW, and OWNER roles that grant specific privileges to users or groups. The Namespace Owner/Edit/View role scopes consumers of a vSphere Namespace to provisioning VKS clusters and vSphere Pods using kubectl, while vSphere Administrator and Supervisor Administrator roles have broader access to cluster and namespace resources. This layered role model restricts third-party access to specific workload boundaries.
-VCF Automation implements a provider-and-consumer model that separates the operators of services from the organizations that consume them. Partner services from external vendors are integrated through this model, where providers manage services and organizations consume the resulting business outcomes such as self-service provisioning of Kubernetes clusters, databases, and other resources. Service providers control the publication scope of service instances to selected organizations and decide which roles, rights bundles, and UI plug-ins to include when publishing services. Provider Consumption Organizations offer additional administrative capabilities on top of standard organizations, allowing provider administrators to provision workloads while maintaining separation from consumer tenants. This architectural separation limits third-party visibility and access to only the resources they need to operate.
-For third-party application integration, VCF Automation supports dedicated service accounts that automate access for third-party applications. Organizations can generate and issue API access tokens that applications use on their behalf, providing a controlled mechanism for programmatic access rather than requiring shared user credentials. The VCF Operations orchestrator presents an open architecture for plugging in external third-party applications, with integration points managed through the platform rather than through direct infrastructure access.
-Tenant isolation is enforced through VCF Automation Organizations, which provide secure infrastructure isolation, quotas, and chargeback across multiple tenants. Within each organization, further isolation exists at the project and namespace levels. IT teams and cloud service providers can monitor resource usage, control permissions, and provide managed services through these organizations while network isolation at the NSX segment level restricts lateral movement between tenants. An Enterprise Admin can share resources with projects in a controlled manner, making objects available for consumption only within designated boundaries. App isolation policies in VCF Automation allow deployments that require on-demand security groups to enforce vDefend firewall rules at the application level. Data-in-transit communications default to TLS encryption for platform services.
-VCF Operations monitors resource usage and policy compliance across the environment, providing visibility into third-party activity. VCF Operations supports firewall hardening that restricts network access to internal services, limiting the network paths available to third-party integrations. Service Discovery identifies permanent listening TCP ports and established UDP connections, and service discovery dashboards provide ongoing visibility into the services operating in the environment. VCF also provides capabilities to discover objects that are not compliant with a security standard, supporting ongoing risk identification for configurations affected by third-party access.
-VMware Private AI Services (PAIS) provides technical mechanisms that contribute to mitigating risks associated with third-party access to AI-related assets, services, and data. These mechanisms operate at the trust validation, authentication, authorization, and content approval layers.
-Trust Establishment for External Integrations
-PAIS uses a CA trust bundle to establish secure HTTPS communication with external services and databases. Administrators must import CA trust bundles for the OIDC provider, Private Harbor registry, content management systems used as data sources in Data Indexing and Retrieval, MCP servers providing tools for agents, and the database server when those entities are not supplied at activation. Without an explicitly configured CA trust bundle, PAIS will not establish connections to those services, so third-party integrations require deliberate administrative action rather than automatic open access. PAIS supports updating certificate content for trusted entities through the same trust bundle mechanism, allowing administrators to refresh trust material as provider certificates change.
-Access Control for Services and Data
-PAIS access is controlled through OIDC group-based authorization. User accounts must be members of specified authorized groups (configured via the authorizedGroups setting) to access the service, and the oidc-groups-claim setting controls which OIDC claim is consulted for group identification in the organization namespace. PAIS requires HTTPS-based communication for OIDC provider integration. SharePoint data sources used as Knowledge Base inputs require user name and password authentication, with support limited to SharePoint On-Premises deployments, so the credential and connectivity posture for that integration is explicit rather than implicit.
-Harbor Access and Model Storage
-The Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. These controls help administrators scope which users and workloads can push to or pull from a registry used by PAIS.
-Model Validation Before Deployment
-Before uploading a model to a PAIS Model Gallery, the platform recommends evaluating the model's performance and safety for the intended business use case, including examining inference requests for malicious behavior and performing hands-on functional tests. PAIS guidance directs administrators to distribute models within the organization that have been validated on a Deep Learning VM rather than models pulled from the Internet, which could contain malicious code or be tuned for malicious behavior. This workflow helps administrators verify third-party or externally sourced models before they become available for production use.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G205" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to mitigating risks from third-party access to organizational technology assets, applications, services, and data through network-level access controls, threat detection, and security posture reporting. Identity governance, authentication, and administrative access controls are handled by other VCF components (VMware vCenter, VCF SSO). vDefend enforces the network security boundary that constrains what third parties can reach once they have been granted access.
-vDefend enforces microsegmentation policies at the vNIC level, allowing administrators to define granular network access rules that restrict third-party workloads or connections to only the specific application tiers and services they require. Context-aware rules allow policies to incorporate workload-level attributes, limiting the network reach of third-party connections to defined sets of addresses, ports, and protocols. In multi-tenant VCF environments, the VPC Isolation with Essential Services strategy allows enterprise administrators to enforce strict inter-project isolation at the Distributed Firewall level while delegating more granular control to application owners within each project. This architecture is suited to environments where third-party development teams or external service providers operate within shared infrastructure, because Distributed Firewall policy at the project boundary can be set independently of what individual tenants configure inside their own VPCs.
-vDefend provides north-south traffic filtering at the perimeter of logical network segments. Enterprise administrators can enforce isolation between projects by denying inter-project communication except for specified infrastructure protocols, adding an enforcement point for controlling inbound and outbound access from external or third-party networks. This policy layer applies regardless of what routing exists at the NSX level, giving security teams a dedicated control plane for third-party network boundaries.
-vDefend IDS/IPS monitors east-west and north-south traffic for malicious activity, detecting exploitation attempts that may arise from compromised third-party connections. Signature rules support storing TLS and SSL certificates on disk for forensic analysis and threat investigation. Custom signature sources, including those derived from cybersecurity advisories, can be deployed to address threats specific to proprietary or custom applications that third parties introduce into the environment.
-Security Services Platform Security Segmentation capabilities identify risky application protocols, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP, in use across the environment. This flags workloads, including those operated by third parties, that transport data without encryption, and allows administrators to restrict or block them as part of the security baseline. The Security Segmentation Report identifies at-risk workloads across categories including Public Traffic, Obsolete OS, Risky Application Protocols, and Inter VDI Server Connections, providing a structured view of workload-level risk that is directly relevant to understanding the exposure introduced by third-party access. Application monitoring in Security Services Platform surfaces security risks identified across workloads, allowing administrators to take targeted remediation steps against risky or non-compliant third-party workloads.
-Security Services Platform certificate management supports importing CA bundles and web proxy certificates to establish trust for external service connections, including those used by the Malware Prevention Service. This controls which external services the platform can reach and provides a configuration point for managing trust relationships with third-party service endpoints.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
